--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L234"/>
+  <dimension ref="A1:L235"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -11487,6 +11487,49 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" s="50" t="n">
+        <v>100300007</v>
+      </c>
+      <c r="B235" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C235" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D235" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E235" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F235" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="G235" s="50" t="n">
+        <v>100300007</v>
+      </c>
+      <c r="H235" s="50" t="inlineStr">
+        <is>
+          <t>100310112</t>
+        </is>
+      </c>
+      <c r="J235" s="50" t="inlineStr">
+        <is>
+          <t>100,200,400,800,1500,2500,4000,6000,9000,15000</t>
+        </is>
+      </c>
+      <c r="K235" s="50" t="n">
+        <v>100300007</v>
+      </c>
+      <c r="L235" s="50" t="inlineStr">
+        <is>
+          <t>是魔王就挑战100勇士-出现概率+10%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="521">
   <si>
     <t>id</t>
   </si>
@@ -129,7 +129,7 @@
     <t>500</t>
   </si>
   <si>
-    <t>1000,2000,3000,4000,5000,</t>
+    <t>500,1000,2000,4000,8000,</t>
   </si>
   <si>
     <t>进阶设施+1</t>
@@ -381,1062 +381,1077 @@
     <t>100310113</t>
   </si>
   <si>
+    <t>剑与魔法：征服难度4</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>100310114</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>剑与魔法：征服难度5</t>
+  </si>
+  <si>
+    <t>640</t>
+  </si>
+  <si>
+    <t>100310115</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>剑与魔法：征服难度6</t>
+  </si>
+  <si>
     <t>800</t>
   </si>
   <si>
-    <t>剑与魔法：征服难度4</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>100310114</t>
+    <t>100310116</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>剑与魔法：征服难度7</t>
+  </si>
+  <si>
+    <t>960</t>
+  </si>
+  <si>
+    <t>100310117</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
+    <t>剑与魔法：征服难度8</t>
+  </si>
+  <si>
+    <t>-158</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>100310118</t>
+  </si>
+  <si>
+    <t>32000</t>
+  </si>
+  <si>
+    <t>剑与魔法：征服难度9</t>
+  </si>
+  <si>
+    <t>1280</t>
+  </si>
+  <si>
+    <t>100310119</t>
+  </si>
+  <si>
+    <t>64000</t>
+  </si>
+  <si>
+    <t>剑与魔法：征服难度10</t>
+  </si>
+  <si>
+    <t>ui_research_66</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount1:1</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度1-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount2:1</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度2-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount3:1</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度3-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount4:1</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度4-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount5:1</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度5-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount6:1</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度6-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount7:1</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度7-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount8:1</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度8-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount9:1</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度9-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>100310120</t>
+  </si>
+  <si>
+    <t>World1ConquerCompleteCount10:1</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度10-加快进攻节奏</t>
+  </si>
+  <si>
+    <t>ui_research_94</t>
+  </si>
+  <si>
+    <t>100310130</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度1-2倍速游戏</t>
+  </si>
+  <si>
+    <t>100310131</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度2-2倍速游戏</t>
+  </si>
+  <si>
+    <t>100310132</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度3-2倍速游戏</t>
+  </si>
+  <si>
+    <t>100310133</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度4-2倍速游戏</t>
+  </si>
+  <si>
+    <t>100310134</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度5-2倍速游戏</t>
+  </si>
+  <si>
+    <t>100310135</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度6-2倍速游戏</t>
+  </si>
+  <si>
+    <t>100310136</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度7-2倍速游戏</t>
+  </si>
+  <si>
+    <t>100310137</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度8-2倍速游戏</t>
+  </si>
+  <si>
+    <t>100310138</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度9-2倍速游戏</t>
+  </si>
+  <si>
+    <t>100310139</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度10-2倍速游戏</t>
+  </si>
+  <si>
+    <t>ui_research_57</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>开启孕育功能</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>孕育可跳过</t>
+  </si>
+  <si>
+    <t>100400000</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：R</t>
+  </si>
+  <si>
+    <t>-200</t>
+  </si>
+  <si>
+    <t>100*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：R 概率+1%</t>
+  </si>
+  <si>
+    <t>100401000,100401001,</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：SR</t>
+  </si>
+  <si>
+    <t>1000*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：SR 概率+1%</t>
+  </si>
+  <si>
+    <t>100402000,100402001,</t>
+  </si>
+  <si>
+    <t>解锁孕育稀有度：SSR</t>
+  </si>
+  <si>
+    <t>10000*1</t>
+  </si>
+  <si>
+    <t>孕育稀有度：SSR 概率+1%</t>
+  </si>
+  <si>
+    <t>ui_research_18</t>
+  </si>
+  <si>
+    <t>开启成就系统</t>
+  </si>
+  <si>
+    <t>ui_research_65</t>
+  </si>
+  <si>
+    <t>-6</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>开启魔汁机</t>
+  </si>
+  <si>
+    <t>-156</t>
+  </si>
+  <si>
+    <t>100600001</t>
+  </si>
+  <si>
+    <t>10000,20000,30000,40000,50000,60000,70000,80000,90000,100000,</t>
+  </si>
+  <si>
+    <t>魔汁机投入数量+1</t>
+  </si>
+  <si>
+    <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000</t>
+  </si>
+  <si>
+    <t>阵容上限+1</t>
+  </si>
+  <si>
+    <t>ui_research_6</t>
+  </si>
+  <si>
+    <t>200000001</t>
+  </si>
+  <si>
+    <t>100,200,300,400,</t>
+  </si>
+  <si>
+    <t>解锁第二阵容</t>
+  </si>
+  <si>
+    <t>ui_research_60</t>
+  </si>
+  <si>
+    <t>100,500,1000,5000,10000,50000</t>
+  </si>
+  <si>
+    <t>魔晶掉落存在时长+5秒</t>
+  </si>
+  <si>
+    <t>ui_research_61</t>
+  </si>
+  <si>
+    <t>200400001</t>
+  </si>
+  <si>
+    <t>50,100,200,500,1000,5000,10000,50000,100000,500000</t>
+  </si>
+  <si>
+    <t>魔王魔力上限+10</t>
+  </si>
+  <si>
+    <t>魔王魔力恢复速度+1/s</t>
+  </si>
+  <si>
+    <t>ui_research_62</t>
+  </si>
+  <si>
+    <t>100,500,1000,5000,10000</t>
+  </si>
+  <si>
+    <t>深渊馈赠刷新次数+1</t>
+  </si>
+  <si>
+    <t>100,1000,10000</t>
+  </si>
+  <si>
+    <t>空格突进</t>
+  </si>
+  <si>
+    <t>200600001</t>
+  </si>
+  <si>
+    <t>200,2000,20000,200000</t>
+  </si>
+  <si>
+    <t>突进冷却</t>
+  </si>
+  <si>
+    <t>200*1</t>
+  </si>
+  <si>
+    <t>魔王自动拾取魔晶</t>
+  </si>
+  <si>
+    <t>200800001</t>
+  </si>
+  <si>
+    <t>500*1</t>
+  </si>
+  <si>
+    <t>每次拾取魔晶+1</t>
+  </si>
+  <si>
+    <t>200100001</t>
+  </si>
+  <si>
+    <t>阵容重命名</t>
+  </si>
+  <si>
+    <t>ui_research_36</t>
+  </si>
+  <si>
+    <t>解锁种族：人类</t>
+  </si>
+  <si>
+    <t>ui_research_43</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>解锁职业：人类战士</t>
+  </si>
+  <si>
+    <t>ui_research_42</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>解锁职业：人类弓箭手</t>
+  </si>
+  <si>
+    <t>ui_research_48</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>解锁职业：人类魔法师（火）</t>
+  </si>
+  <si>
+    <t>ui_research_47</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>解锁职业：人类魔法师（冰）</t>
+  </si>
+  <si>
+    <t>ui_research_33</t>
+  </si>
+  <si>
+    <t>300100001|300100002|300100003|300100004|</t>
+  </si>
+  <si>
+    <t>孕育人类x5</t>
+  </si>
+  <si>
+    <t>ui_research_34</t>
+  </si>
+  <si>
+    <t>孕育人类x10</t>
+  </si>
+  <si>
+    <t>100200001,300100000,</t>
+  </si>
+  <si>
+    <t>可转生为人类</t>
+  </si>
+  <si>
+    <t>ui_research_58</t>
+  </si>
+  <si>
+    <t>300100000,</t>
+  </si>
+  <si>
+    <t>奖励-可获取人类装备</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount1001:99</t>
+  </si>
+  <si>
+    <t>孕育人类战士x1</t>
+  </si>
+  <si>
+    <t>孕育人类战士x5</t>
+  </si>
+  <si>
+    <t>孕育人类战士x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount1002:99</t>
+  </si>
+  <si>
+    <t>孕育人类弓箭手x1</t>
+  </si>
+  <si>
+    <t>孕育人类弓箭手x5</t>
+  </si>
+  <si>
+    <t>孕育人类弓箭手x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount1003:99</t>
+  </si>
+  <si>
+    <t>孕育人类魔法师（火）x1</t>
+  </si>
+  <si>
+    <t>孕育人类魔法师（火）x5</t>
+  </si>
+  <si>
+    <t>孕育人类魔法师（火）x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount1004:99</t>
+  </si>
+  <si>
+    <t>孕育人类魔法师（冰）x1</t>
+  </si>
+  <si>
+    <t>孕育人类魔法师（冰）x5</t>
+  </si>
+  <si>
+    <t>孕育人类魔法师（冰）x10</t>
+  </si>
+  <si>
+    <t>ui_research_35</t>
+  </si>
+  <si>
+    <t>解锁种族：骷髅</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>解锁职业：骷髅战士</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>解锁职业：骷髅投手</t>
+  </si>
+  <si>
+    <t>解锁职业：骷髅魔法师（火）</t>
+  </si>
+  <si>
+    <t>解锁职业：骷髅魔法师（冰）</t>
+  </si>
+  <si>
+    <t>300200001|300200002|300200003|300200004|</t>
+  </si>
+  <si>
+    <t>孕育骷髅x5</t>
+  </si>
+  <si>
+    <t>孕育骷髅x10</t>
+  </si>
+  <si>
+    <t>100200001,300200000,</t>
+  </si>
+  <si>
+    <t>可转生为骷髅</t>
+  </si>
+  <si>
+    <t>300200000,</t>
+  </si>
+  <si>
+    <t>奖励-可获取骷髅装备</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount2001:99</t>
+  </si>
+  <si>
+    <t>孕育骷髅战士x1</t>
+  </si>
+  <si>
+    <t>孕育骷髅战士x5</t>
+  </si>
+  <si>
+    <t>孕育骷髅战士x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount2002:99</t>
+  </si>
+  <si>
+    <t>孕育骷髅投手x1</t>
+  </si>
+  <si>
+    <t>孕育骷髅投手x5</t>
+  </si>
+  <si>
+    <t>孕育骷髅投手x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount2003:99</t>
+  </si>
+  <si>
+    <t>孕育骷髅魔法师（火）x1</t>
+  </si>
+  <si>
+    <t>孕育骷髅魔法师（火）x5</t>
+  </si>
+  <si>
+    <t>孕育骷髅魔法师（火）x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount2004:99</t>
+  </si>
+  <si>
+    <t>孕育骷髅魔法师（冰）x1</t>
+  </si>
+  <si>
+    <t>孕育骷髅魔法师（冰）x5</t>
+  </si>
+  <si>
+    <t>孕育骷髅魔法师（冰）x10</t>
+  </si>
+  <si>
+    <t>ui_research_37</t>
+  </si>
+  <si>
+    <t>解锁种族：史莱姆</t>
+  </si>
+  <si>
+    <t>ui_research_51</t>
+  </si>
+  <si>
+    <t>-1100</t>
+  </si>
+  <si>
+    <t>解锁职业：守护史莱姆</t>
+  </si>
+  <si>
+    <t>ui_research_54</t>
+  </si>
+  <si>
+    <t>-950</t>
+  </si>
+  <si>
+    <t>解锁职业：自爆史莱姆</t>
+  </si>
+  <si>
+    <t>-650</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>解锁职业：烂泥史莱姆</t>
+  </si>
+  <si>
+    <t>ui_research_53</t>
+  </si>
+  <si>
+    <t>解锁职业：毒液史莱姆</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>300300001|300300002|300300003|300300004|</t>
+  </si>
+  <si>
+    <t>孕育史莱姆x5</t>
+  </si>
+  <si>
+    <t>孕育史莱姆x10</t>
+  </si>
+  <si>
+    <t>100200001,300300000,</t>
+  </si>
+  <si>
+    <t>可转生为史莱姆</t>
+  </si>
+  <si>
+    <t>300300000,</t>
+  </si>
+  <si>
+    <t>奖励-可获取史莱姆装备</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount3001:99</t>
+  </si>
+  <si>
+    <t>孕育守护史莱姆x1</t>
+  </si>
+  <si>
+    <t>孕育守护史莱姆x5</t>
+  </si>
+  <si>
+    <t>孕育守护史莱姆x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount3002:99</t>
+  </si>
+  <si>
+    <t>孕育自爆史莱姆x1</t>
+  </si>
+  <si>
+    <t>孕育自爆史莱姆x5</t>
+  </si>
+  <si>
+    <t>孕育自爆史莱姆x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount3003:99</t>
+  </si>
+  <si>
+    <t>孕育烂泥史莱姆x1</t>
+  </si>
+  <si>
+    <t>孕育烂泥史莱姆x5</t>
+  </si>
+  <si>
+    <t>孕育烂泥史莱姆x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount3004:99</t>
+  </si>
+  <si>
+    <t>孕育毒液史莱姆x1</t>
+  </si>
+  <si>
+    <t>孕育毒液史莱姆x5</t>
+  </si>
+  <si>
+    <t>孕育毒液史莱姆x10</t>
+  </si>
+  <si>
+    <t>ui_research_41</t>
+  </si>
+  <si>
+    <t>-2400</t>
+  </si>
+  <si>
+    <t>解锁种族：魅魔</t>
+  </si>
+  <si>
+    <t>-2700</t>
+  </si>
+  <si>
+    <t>解锁职业：战之魅魔</t>
+  </si>
+  <si>
+    <t>ui_research_45</t>
+  </si>
+  <si>
+    <t>-2550</t>
+  </si>
+  <si>
+    <t>解锁职业：愈之魅魔</t>
+  </si>
+  <si>
+    <t>ui_research_52</t>
+  </si>
+  <si>
+    <t>解锁职业：惑之魅魔</t>
+  </si>
+  <si>
+    <t>ui_research_49</t>
+  </si>
+  <si>
+    <t>-2250</t>
+  </si>
+  <si>
+    <t>解锁职业：奥之魅魔</t>
+  </si>
+  <si>
+    <t>-2100</t>
+  </si>
+  <si>
+    <t>解锁职业：盾之魅魔</t>
+  </si>
+  <si>
+    <t>300400001|300400002|300400003|300400004|300400005|</t>
+  </si>
+  <si>
+    <t>孕育魅魔x5</t>
+  </si>
+  <si>
+    <t>孕育魅魔x10</t>
+  </si>
+  <si>
+    <t>100200001,300400000,</t>
+  </si>
+  <si>
+    <t>可转生为魅魔</t>
+  </si>
+  <si>
+    <t>300400000,</t>
+  </si>
+  <si>
+    <t>奖励-可获取魅魔装备</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount4001:99</t>
+  </si>
+  <si>
+    <t>孕育战之魅魔x1</t>
+  </si>
+  <si>
+    <t>孕育战之魅魔x5</t>
+  </si>
+  <si>
+    <t>孕育战之魅魔x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount4002:99</t>
+  </si>
+  <si>
+    <t>孕育愈之魅魔x1</t>
+  </si>
+  <si>
+    <t>孕育愈之魅魔x5</t>
+  </si>
+  <si>
+    <t>孕育愈之魅魔x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount4003:99</t>
+  </si>
+  <si>
+    <t>孕育惑之魅魔x1</t>
+  </si>
+  <si>
+    <t>孕育惑之魅魔x5</t>
+  </si>
+  <si>
+    <t>孕育惑之魅魔x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount4004:99</t>
+  </si>
+  <si>
+    <t>孕育奥之魅魔x1</t>
+  </si>
+  <si>
+    <t>孕育奥之魅魔x5</t>
+  </si>
+  <si>
+    <t>孕育奥之魅魔x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount4005:99</t>
+  </si>
+  <si>
+    <t>孕育盾之魅魔x1</t>
+  </si>
+  <si>
+    <t>孕育盾之魅魔x5</t>
+  </si>
+  <si>
+    <t>孕育盾之魅魔x10</t>
+  </si>
+  <si>
+    <t>ui_research_40</t>
+  </si>
+  <si>
+    <t>2400</t>
+  </si>
+  <si>
+    <t>解锁种族：牛头人</t>
+  </si>
+  <si>
+    <t>2175</t>
+  </si>
+  <si>
+    <t>解锁职业：牛头人战士</t>
+  </si>
+  <si>
+    <t>2325</t>
+  </si>
+  <si>
+    <t>解锁职业：牛头人投手</t>
+  </si>
+  <si>
+    <t>2475</t>
+  </si>
+  <si>
+    <t>解锁职业：牛头人魔法师（火）</t>
+  </si>
+  <si>
+    <t>2625</t>
+  </si>
+  <si>
+    <t>解锁职业：牛头人魔法师（冰）</t>
+  </si>
+  <si>
+    <t>300500001|300500002|300500003|300500004|</t>
+  </si>
+  <si>
+    <t>孕育牛头人x5</t>
+  </si>
+  <si>
+    <t>孕育牛头人x10</t>
+  </si>
+  <si>
+    <t>2550</t>
+  </si>
+  <si>
+    <t>100200001,300500000,</t>
+  </si>
+  <si>
+    <t>可转生为牛头人</t>
+  </si>
+  <si>
+    <t>300500000,</t>
+  </si>
+  <si>
+    <t>奖励-可获取牛头人装备</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount5001:99</t>
+  </si>
+  <si>
+    <t>孕育牛头人战士x1</t>
+  </si>
+  <si>
+    <t>孕育牛头人战士x5</t>
+  </si>
+  <si>
+    <t>孕育牛头人战士x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount5002:99</t>
+  </si>
+  <si>
+    <t>孕育牛头人投手x1</t>
+  </si>
+  <si>
+    <t>孕育牛头人投手x5</t>
+  </si>
+  <si>
+    <t>孕育牛头人投手x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount5003:99</t>
+  </si>
+  <si>
+    <t>孕育牛头人魔法师（火）x1</t>
+  </si>
+  <si>
+    <t>孕育牛头人魔法师（火）x5</t>
+  </si>
+  <si>
+    <t>孕育牛头人魔法师（火）x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount5004:99</t>
+  </si>
+  <si>
+    <t>孕育牛头人魔法师（冰）x1</t>
+  </si>
+  <si>
+    <t>孕育牛头人魔法师（冰）x5</t>
+  </si>
+  <si>
+    <t>孕育牛头人魔法师（冰）x10</t>
+  </si>
+  <si>
+    <t>ui_research_39</t>
+  </si>
+  <si>
+    <t>-1600</t>
+  </si>
+  <si>
+    <t>解锁种族：哥布林</t>
+  </si>
+  <si>
+    <t>ui_research_44</t>
+  </si>
+  <si>
+    <t>-1900</t>
+  </si>
+  <si>
+    <t>解锁职业：哥布林刺客</t>
+  </si>
+  <si>
+    <t>-1750</t>
+  </si>
+  <si>
+    <t>解锁职业：哥布林弓箭手</t>
+  </si>
+  <si>
+    <t>解锁职业：哥布林敢死队</t>
+  </si>
+  <si>
+    <t>-1450</t>
+  </si>
+  <si>
+    <t>解锁职业：哥布林魔法师（火）</t>
+  </si>
+  <si>
+    <t>-1300</t>
+  </si>
+  <si>
+    <t>解锁职业：哥布林魔法师（冰）</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>300600001|300600002|300600003|300600004|300600005</t>
+  </si>
+  <si>
+    <t>孕育哥布林x5</t>
+  </si>
+  <si>
+    <t>孕育哥布林x10</t>
+  </si>
+  <si>
+    <t>100200001,300600000,</t>
+  </si>
+  <si>
+    <t>可转生为哥布林</t>
+  </si>
+  <si>
+    <t>300600000,</t>
+  </si>
+  <si>
+    <t>奖励-可获取哥布林装备</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount6001:99</t>
+  </si>
+  <si>
+    <t>孕育哥布林刺客x1</t>
+  </si>
+  <si>
+    <t>孕育哥布林刺客x5</t>
+  </si>
+  <si>
+    <t>孕育哥布林刺客x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount6002:99</t>
+  </si>
+  <si>
+    <t>孕育哥布林弓箭手x1</t>
+  </si>
+  <si>
+    <t>孕育哥布林弓箭手x5</t>
+  </si>
+  <si>
+    <t>孕育哥布林弓箭手x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount6003:99</t>
+  </si>
+  <si>
+    <t>孕育哥布林敢死队x1</t>
+  </si>
+  <si>
+    <t>孕育哥布林敢死队x5</t>
+  </si>
+  <si>
+    <t>孕育哥布林敢死队x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount6004:99</t>
+  </si>
+  <si>
+    <t>孕育哥布林魔法师（火）x1</t>
+  </si>
+  <si>
+    <t>孕育哥布林魔法师（火）x5</t>
+  </si>
+  <si>
+    <t>孕育哥布林魔法师（火）x10</t>
+  </si>
+  <si>
+    <t>GashaponCreatureDrawCount6005:99</t>
+  </si>
+  <si>
+    <t>孕育哥布林魔法师（冰）x1</t>
+  </si>
+  <si>
+    <t>孕育哥布林魔法师（冰）x5</t>
+  </si>
+  <si>
+    <t>孕育哥布林魔法师（冰）x10</t>
+  </si>
+  <si>
+    <t>ui_research_38</t>
   </si>
   <si>
     <t>1600</t>
   </si>
   <si>
-    <t>剑与魔法：征服难度5</t>
-  </si>
-  <si>
-    <t>640</t>
-  </si>
-  <si>
-    <t>100310115</t>
-  </si>
-  <si>
-    <t>3200</t>
-  </si>
-  <si>
-    <t>剑与魔法：征服难度6</t>
-  </si>
-  <si>
-    <t>100310116</t>
-  </si>
-  <si>
-    <t>6400</t>
-  </si>
-  <si>
-    <t>剑与魔法：征服难度7</t>
-  </si>
-  <si>
-    <t>960</t>
-  </si>
-  <si>
-    <t>100310117</t>
-  </si>
-  <si>
-    <t>12800</t>
-  </si>
-  <si>
-    <t>剑与魔法：征服难度8</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>100310118</t>
-  </si>
-  <si>
-    <t>25600</t>
-  </si>
-  <si>
-    <t>剑与魔法：征服难度9</t>
-  </si>
-  <si>
-    <t>1280</t>
-  </si>
-  <si>
-    <t>100310119</t>
-  </si>
-  <si>
-    <t>51200</t>
-  </si>
-  <si>
-    <t>剑与魔法：征服难度10</t>
-  </si>
-  <si>
-    <t>ui_research_66</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount1:1</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度1-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount2:1</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度2-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount3:1</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度3-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount4:1</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度4-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount5:1</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度5-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount6:1</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度6-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount7:1</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度7-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount8:1</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度8-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount9:1</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度9-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>100310120</t>
-  </si>
-  <si>
-    <t>World1ConquerCompleteCount10:1</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度10-加快进攻节奏</t>
-  </si>
-  <si>
-    <t>ui_research_94</t>
-  </si>
-  <si>
-    <t>100310130</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度1-2倍速游戏</t>
-  </si>
-  <si>
-    <t>100310131</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度2-2倍速游戏</t>
-  </si>
-  <si>
-    <t>100310132</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度3-2倍速游戏</t>
-  </si>
-  <si>
-    <t>100310133</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度4-2倍速游戏</t>
-  </si>
-  <si>
-    <t>100310134</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度5-2倍速游戏</t>
-  </si>
-  <si>
-    <t>100310135</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度6-2倍速游戏</t>
-  </si>
-  <si>
-    <t>100310136</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度7-2倍速游戏</t>
-  </si>
-  <si>
-    <t>100310137</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度8-2倍速游戏</t>
-  </si>
-  <si>
-    <t>100310138</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度9-2倍速游戏</t>
-  </si>
-  <si>
-    <t>100310139</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度10-2倍速游戏</t>
-  </si>
-  <si>
-    <t>ui_research_57</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>开启孕育功能</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>孕育可跳过</t>
-  </si>
-  <si>
-    <t>100400000</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：R</t>
-  </si>
-  <si>
-    <t>-200</t>
-  </si>
-  <si>
-    <t>100*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：R 概率+1%</t>
-  </si>
-  <si>
-    <t>100401000,100401001,</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：SR</t>
-  </si>
-  <si>
-    <t>1000*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：SR 概率+1%</t>
-  </si>
-  <si>
-    <t>100402000,100402001,</t>
-  </si>
-  <si>
-    <t>解锁孕育稀有度：SSR</t>
-  </si>
-  <si>
-    <t>10000*1</t>
-  </si>
-  <si>
-    <t>孕育稀有度：SSR 概率+1%</t>
-  </si>
-  <si>
-    <t>ui_research_18</t>
-  </si>
-  <si>
-    <t>开启成就系统</t>
-  </si>
-  <si>
-    <t>ui_research_65</t>
-  </si>
-  <si>
-    <t>-6</t>
-  </si>
-  <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>开启魔汁机</t>
-  </si>
-  <si>
-    <t>-156</t>
-  </si>
-  <si>
-    <t>100600001</t>
-  </si>
-  <si>
-    <t>10000,20000,30000,40000,50000,60000,70000,80000,90000,100000,</t>
-  </si>
-  <si>
-    <t>魔汁机投入数量+1</t>
-  </si>
-  <si>
-    <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000</t>
-  </si>
-  <si>
-    <t>阵容上限+1</t>
-  </si>
-  <si>
-    <t>ui_research_6</t>
-  </si>
-  <si>
-    <t>200000001</t>
-  </si>
-  <si>
-    <t>100,200,300,400,</t>
-  </si>
-  <si>
-    <t>解锁第二阵容</t>
-  </si>
-  <si>
-    <t>ui_research_60</t>
-  </si>
-  <si>
-    <t>100,500,1000,5000,10000,50000</t>
-  </si>
-  <si>
-    <t>魔晶掉落存在时长+5秒</t>
-  </si>
-  <si>
-    <t>ui_research_61</t>
-  </si>
-  <si>
-    <t>200400001</t>
-  </si>
-  <si>
-    <t>50,100,200,500,1000,5000,10000,50000,100000,500000</t>
-  </si>
-  <si>
-    <t>魔王魔力上限+10</t>
-  </si>
-  <si>
-    <t>魔王魔力恢复速度+1/s</t>
-  </si>
-  <si>
-    <t>ui_research_62</t>
-  </si>
-  <si>
-    <t>100,500,1000,5000,10000</t>
-  </si>
-  <si>
-    <t>深渊馈赠刷新次数+1</t>
-  </si>
-  <si>
-    <t>100,1000,10000</t>
-  </si>
-  <si>
-    <t>空格突进</t>
-  </si>
-  <si>
-    <t>200600001</t>
-  </si>
-  <si>
-    <t>200,2000,20000,200000</t>
-  </si>
-  <si>
-    <t>突进冷却</t>
-  </si>
-  <si>
-    <t>200*1</t>
-  </si>
-  <si>
-    <t>魔王自动拾取魔晶</t>
-  </si>
-  <si>
-    <t>200800001</t>
-  </si>
-  <si>
-    <t>500*1</t>
-  </si>
-  <si>
-    <t>每次拾取魔晶+1</t>
-  </si>
-  <si>
-    <t>200100001</t>
-  </si>
-  <si>
-    <t>阵容重命名</t>
-  </si>
-  <si>
-    <t>ui_research_36</t>
-  </si>
-  <si>
-    <t>解锁种族：人类</t>
-  </si>
-  <si>
-    <t>ui_research_43</t>
-  </si>
-  <si>
-    <t>解锁职业：人类战士</t>
-  </si>
-  <si>
-    <t>ui_research_42</t>
-  </si>
-  <si>
-    <t>650</t>
-  </si>
-  <si>
-    <t>解锁职业：人类弓箭手</t>
-  </si>
-  <si>
-    <t>ui_research_48</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>解锁职业：人类魔法师（火）</t>
-  </si>
-  <si>
-    <t>ui_research_47</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>解锁职业：人类魔法师（冰）</t>
-  </si>
-  <si>
-    <t>ui_research_33</t>
-  </si>
-  <si>
-    <t>300100001|300100002|300100003|300100004|</t>
-  </si>
-  <si>
-    <t>孕育人类x5</t>
-  </si>
-  <si>
-    <t>ui_research_34</t>
-  </si>
-  <si>
-    <t>孕育人类x10</t>
-  </si>
-  <si>
-    <t>100200001,300100000,</t>
-  </si>
-  <si>
-    <t>可转生为人类</t>
-  </si>
-  <si>
-    <t>ui_research_58</t>
-  </si>
-  <si>
-    <t>300100000,</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>奖励-可获取人类装备</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount1001:99</t>
-  </si>
-  <si>
-    <t>孕育人类战士x1</t>
-  </si>
-  <si>
-    <t>孕育人类战士x5</t>
-  </si>
-  <si>
-    <t>孕育人类战士x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount1002:99</t>
-  </si>
-  <si>
-    <t>孕育人类弓箭手x1</t>
-  </si>
-  <si>
-    <t>孕育人类弓箭手x5</t>
-  </si>
-  <si>
-    <t>孕育人类弓箭手x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount1003:99</t>
-  </si>
-  <si>
-    <t>孕育人类魔法师（火）x1</t>
-  </si>
-  <si>
-    <t>孕育人类魔法师（火）x5</t>
-  </si>
-  <si>
-    <t>孕育人类魔法师（火）x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount1004:99</t>
-  </si>
-  <si>
-    <t>孕育人类魔法师（冰）x1</t>
-  </si>
-  <si>
-    <t>孕育人类魔法师（冰）x5</t>
-  </si>
-  <si>
-    <t>孕育人类魔法师（冰）x10</t>
-  </si>
-  <si>
-    <t>ui_research_35</t>
-  </si>
-  <si>
-    <t>解锁种族：骷髅</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>解锁职业：骷髅战士</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>解锁职业：骷髅投手</t>
-  </si>
-  <si>
-    <t>解锁职业：骷髅魔法师（火）</t>
-  </si>
-  <si>
-    <t>解锁职业：骷髅魔法师（冰）</t>
-  </si>
-  <si>
-    <t>300200001|300200002|300200003|300200004|</t>
-  </si>
-  <si>
-    <t>孕育骷髅x5</t>
-  </si>
-  <si>
-    <t>孕育骷髅x10</t>
-  </si>
-  <si>
-    <t>100200001,300200000,</t>
-  </si>
-  <si>
-    <t>可转生为骷髅</t>
-  </si>
-  <si>
-    <t>300200000,</t>
-  </si>
-  <si>
-    <t>奖励-可获取骷髅装备</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount2001:99</t>
-  </si>
-  <si>
-    <t>孕育骷髅战士x1</t>
-  </si>
-  <si>
-    <t>孕育骷髅战士x5</t>
-  </si>
-  <si>
-    <t>孕育骷髅战士x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount2002:99</t>
-  </si>
-  <si>
-    <t>孕育骷髅投手x1</t>
-  </si>
-  <si>
-    <t>孕育骷髅投手x5</t>
-  </si>
-  <si>
-    <t>孕育骷髅投手x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount2003:99</t>
-  </si>
-  <si>
-    <t>孕育骷髅魔法师（火）x1</t>
-  </si>
-  <si>
-    <t>孕育骷髅魔法师（火）x5</t>
-  </si>
-  <si>
-    <t>孕育骷髅魔法师（火）x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount2004:99</t>
-  </si>
-  <si>
-    <t>孕育骷髅魔法师（冰）x1</t>
-  </si>
-  <si>
-    <t>孕育骷髅魔法师（冰）x5</t>
-  </si>
-  <si>
-    <t>孕育骷髅魔法师（冰）x10</t>
-  </si>
-  <si>
-    <t>ui_research_37</t>
-  </si>
-  <si>
-    <t>解锁种族：史莱姆</t>
-  </si>
-  <si>
-    <t>ui_research_51</t>
-  </si>
-  <si>
-    <t>-1100</t>
-  </si>
-  <si>
-    <t>解锁职业：守护史莱姆</t>
-  </si>
-  <si>
-    <t>ui_research_54</t>
-  </si>
-  <si>
-    <t>-950</t>
-  </si>
-  <si>
-    <t>解锁职业：自爆史莱姆</t>
-  </si>
-  <si>
-    <t>-650</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>解锁职业：烂泥史莱姆</t>
-  </si>
-  <si>
-    <t>ui_research_53</t>
-  </si>
-  <si>
-    <t>解锁职业：毒液史莱姆</t>
-  </si>
-  <si>
-    <t>300300001|300300002|300300003|300300004|</t>
-  </si>
-  <si>
-    <t>孕育史莱姆x5</t>
-  </si>
-  <si>
-    <t>孕育史莱姆x10</t>
-  </si>
-  <si>
-    <t>100200001,300300000,</t>
-  </si>
-  <si>
-    <t>可转生为史莱姆</t>
-  </si>
-  <si>
-    <t>300300000,</t>
-  </si>
-  <si>
-    <t>奖励-可获取史莱姆装备</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount3001:99</t>
-  </si>
-  <si>
-    <t>孕育守护史莱姆x1</t>
-  </si>
-  <si>
-    <t>孕育守护史莱姆x5</t>
-  </si>
-  <si>
-    <t>孕育守护史莱姆x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount3002:99</t>
-  </si>
-  <si>
-    <t>孕育自爆史莱姆x1</t>
-  </si>
-  <si>
-    <t>孕育自爆史莱姆x5</t>
-  </si>
-  <si>
-    <t>孕育自爆史莱姆x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount3003:99</t>
-  </si>
-  <si>
-    <t>孕育烂泥史莱姆x1</t>
-  </si>
-  <si>
-    <t>孕育烂泥史莱姆x5</t>
-  </si>
-  <si>
-    <t>孕育烂泥史莱姆x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount3004:99</t>
-  </si>
-  <si>
-    <t>孕育毒液史莱姆x1</t>
-  </si>
-  <si>
-    <t>孕育毒液史莱姆x5</t>
-  </si>
-  <si>
-    <t>孕育毒液史莱姆x10</t>
-  </si>
-  <si>
-    <t>ui_research_41</t>
-  </si>
-  <si>
-    <t>-2400</t>
-  </si>
-  <si>
-    <t>解锁种族：魅魔</t>
-  </si>
-  <si>
-    <t>-2700</t>
-  </si>
-  <si>
-    <t>解锁职业：战之魅魔</t>
-  </si>
-  <si>
-    <t>ui_research_45</t>
-  </si>
-  <si>
-    <t>-2550</t>
-  </si>
-  <si>
-    <t>解锁职业：愈之魅魔</t>
-  </si>
-  <si>
-    <t>ui_research_52</t>
-  </si>
-  <si>
-    <t>解锁职业：惑之魅魔</t>
-  </si>
-  <si>
-    <t>ui_research_49</t>
-  </si>
-  <si>
-    <t>-2250</t>
-  </si>
-  <si>
-    <t>解锁职业：奥之魅魔</t>
-  </si>
-  <si>
-    <t>-2100</t>
-  </si>
-  <si>
-    <t>解锁职业：盾之魅魔</t>
-  </si>
-  <si>
-    <t>300400001|300400002|300400003|300400004|300400005|</t>
-  </si>
-  <si>
-    <t>孕育魅魔x5</t>
-  </si>
-  <si>
-    <t>孕育魅魔x10</t>
-  </si>
-  <si>
-    <t>100200001,300400000,</t>
-  </si>
-  <si>
-    <t>可转生为魅魔</t>
-  </si>
-  <si>
-    <t>300400000,</t>
-  </si>
-  <si>
-    <t>奖励-可获取魅魔装备</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount4001:99</t>
-  </si>
-  <si>
-    <t>孕育战之魅魔x1</t>
-  </si>
-  <si>
-    <t>孕育战之魅魔x5</t>
-  </si>
-  <si>
-    <t>孕育战之魅魔x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount4002:99</t>
-  </si>
-  <si>
-    <t>孕育愈之魅魔x1</t>
-  </si>
-  <si>
-    <t>孕育愈之魅魔x5</t>
-  </si>
-  <si>
-    <t>孕育愈之魅魔x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount4003:99</t>
-  </si>
-  <si>
-    <t>孕育惑之魅魔x1</t>
-  </si>
-  <si>
-    <t>孕育惑之魅魔x5</t>
-  </si>
-  <si>
-    <t>孕育惑之魅魔x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount4004:99</t>
-  </si>
-  <si>
-    <t>孕育奥之魅魔x1</t>
-  </si>
-  <si>
-    <t>孕育奥之魅魔x5</t>
-  </si>
-  <si>
-    <t>孕育奥之魅魔x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount4005:99</t>
-  </si>
-  <si>
-    <t>孕育盾之魅魔x1</t>
-  </si>
-  <si>
-    <t>孕育盾之魅魔x5</t>
-  </si>
-  <si>
-    <t>孕育盾之魅魔x10</t>
-  </si>
-  <si>
-    <t>ui_research_40</t>
-  </si>
-  <si>
-    <t>2400</t>
-  </si>
-  <si>
-    <t>解锁种族：牛头人</t>
-  </si>
-  <si>
-    <t>2175</t>
-  </si>
-  <si>
-    <t>解锁职业：牛头人战士</t>
-  </si>
-  <si>
-    <t>2325</t>
-  </si>
-  <si>
-    <t>解锁职业：牛头人投手</t>
-  </si>
-  <si>
-    <t>2475</t>
-  </si>
-  <si>
-    <t>解锁职业：牛头人魔法师（火）</t>
-  </si>
-  <si>
-    <t>2625</t>
-  </si>
-  <si>
-    <t>解锁职业：牛头人魔法师（冰）</t>
-  </si>
-  <si>
-    <t>300500001|300500002|300500003|300500004|</t>
-  </si>
-  <si>
-    <t>孕育牛头人x5</t>
-  </si>
-  <si>
-    <t>孕育牛头人x10</t>
-  </si>
-  <si>
-    <t>2550</t>
-  </si>
-  <si>
-    <t>100200001,300500000,</t>
-  </si>
-  <si>
-    <t>可转生为牛头人</t>
-  </si>
-  <si>
-    <t>300500000,</t>
-  </si>
-  <si>
-    <t>奖励-可获取牛头人装备</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount5001:99</t>
-  </si>
-  <si>
-    <t>孕育牛头人战士x1</t>
-  </si>
-  <si>
-    <t>孕育牛头人战士x5</t>
-  </si>
-  <si>
-    <t>孕育牛头人战士x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount5002:99</t>
-  </si>
-  <si>
-    <t>孕育牛头人投手x1</t>
-  </si>
-  <si>
-    <t>孕育牛头人投手x5</t>
-  </si>
-  <si>
-    <t>孕育牛头人投手x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount5003:99</t>
-  </si>
-  <si>
-    <t>孕育牛头人魔法师（火）x1</t>
-  </si>
-  <si>
-    <t>孕育牛头人魔法师（火）x5</t>
-  </si>
-  <si>
-    <t>孕育牛头人魔法师（火）x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount5004:99</t>
-  </si>
-  <si>
-    <t>孕育牛头人魔法师（冰）x1</t>
-  </si>
-  <si>
-    <t>孕育牛头人魔法师（冰）x5</t>
-  </si>
-  <si>
-    <t>孕育牛头人魔法师（冰）x10</t>
-  </si>
-  <si>
-    <t>ui_research_39</t>
-  </si>
-  <si>
-    <t>-1600</t>
-  </si>
-  <si>
-    <t>解锁种族：哥布林</t>
-  </si>
-  <si>
-    <t>ui_research_44</t>
-  </si>
-  <si>
-    <t>-1900</t>
-  </si>
-  <si>
-    <t>解锁职业：哥布林刺客</t>
-  </si>
-  <si>
-    <t>-1750</t>
-  </si>
-  <si>
-    <t>解锁职业：哥布林弓箭手</t>
-  </si>
-  <si>
-    <t>解锁职业：哥布林敢死队</t>
-  </si>
-  <si>
-    <t>-1450</t>
-  </si>
-  <si>
-    <t>解锁职业：哥布林魔法师（火）</t>
-  </si>
-  <si>
-    <t>-1300</t>
-  </si>
-  <si>
-    <t>解锁职业：哥布林魔法师（冰）</t>
-  </si>
-  <si>
-    <t>300600001|300600002|300600003|300600004|300600005</t>
-  </si>
-  <si>
-    <t>孕育哥布林x5</t>
-  </si>
-  <si>
-    <t>孕育哥布林x10</t>
-  </si>
-  <si>
-    <t>100200001,300600000,</t>
-  </si>
-  <si>
-    <t>可转生为哥布林</t>
-  </si>
-  <si>
-    <t>300600000,</t>
-  </si>
-  <si>
-    <t>奖励-可获取哥布林装备</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount6001:99</t>
-  </si>
-  <si>
-    <t>孕育哥布林刺客x1</t>
-  </si>
-  <si>
-    <t>孕育哥布林刺客x5</t>
-  </si>
-  <si>
-    <t>孕育哥布林刺客x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount6002:99</t>
-  </si>
-  <si>
-    <t>孕育哥布林弓箭手x1</t>
-  </si>
-  <si>
-    <t>孕育哥布林弓箭手x5</t>
-  </si>
-  <si>
-    <t>孕育哥布林弓箭手x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount6003:99</t>
-  </si>
-  <si>
-    <t>孕育哥布林敢死队x1</t>
-  </si>
-  <si>
-    <t>孕育哥布林敢死队x5</t>
-  </si>
-  <si>
-    <t>孕育哥布林敢死队x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount6004:99</t>
-  </si>
-  <si>
-    <t>孕育哥布林魔法师（火）x1</t>
-  </si>
-  <si>
-    <t>孕育哥布林魔法师（火）x5</t>
-  </si>
-  <si>
-    <t>孕育哥布林魔法师（火）x10</t>
-  </si>
-  <si>
-    <t>GashaponCreatureDrawCount6005:99</t>
-  </si>
-  <si>
-    <t>孕育哥布林魔法师（冰）x1</t>
-  </si>
-  <si>
-    <t>孕育哥布林魔法师（冰）x5</t>
-  </si>
-  <si>
-    <t>孕育哥布林魔法师（冰）x10</t>
-  </si>
-  <si>
-    <t>ui_research_38</t>
-  </si>
-  <si>
     <t>解锁种族：兽人</t>
   </si>
   <si>
@@ -1552,6 +1567,15 @@
   </si>
   <si>
     <t>无尽模式-出现概率+10%/级</t>
+  </si>
+  <si>
+    <t>100300007</t>
+  </si>
+  <si>
+    <t>100,200,400,800</t>
+  </si>
+  <si>
+    <t>真勇者挑战(挑战100勇士-BOSS挑战)出现概率+10%/级(基础10%,满级50%)</t>
   </si>
 </sst>
 </file>
@@ -2705,7 +2729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M245"/>
+  <dimension ref="A1:M246"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="37.75" customWidth="1" style="51"/>
@@ -4159,13 +4183,13 @@
         <v>121</v>
       </c>
       <c r="J40" s="50" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="K40" s="50">
         <v>100310114</v>
       </c>
       <c r="M40" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41">
@@ -4185,22 +4209,22 @@
         <v>116</v>
       </c>
       <c r="F41" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G41" s="50">
         <v>100310115</v>
       </c>
       <c r="H41" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="J41" s="50" t="s">
         <v>125</v>
-      </c>
-      <c r="J41" s="50" t="s">
-        <v>126</v>
       </c>
       <c r="K41" s="50">
         <v>100310115</v>
       </c>
       <c r="M41" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42">
@@ -4220,22 +4244,22 @@
         <v>116</v>
       </c>
       <c r="F42" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G42" s="50">
         <v>100310116</v>
       </c>
       <c r="H42" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="J42" s="50" t="s">
         <v>129</v>
-      </c>
-      <c r="J42" s="50" t="s">
-        <v>130</v>
       </c>
       <c r="K42" s="50">
         <v>100310116</v>
       </c>
       <c r="M42" s="50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43">
@@ -4255,7 +4279,7 @@
         <v>116</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G43" s="50">
         <v>100310117</v>
@@ -4322,25 +4346,25 @@
         <v>1</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G45" s="50">
         <v>100310119</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J45" s="50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K45" s="50">
         <v>100310119</v>
       </c>
       <c r="M45" s="50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46">
@@ -4360,22 +4384,22 @@
         <v>116</v>
       </c>
       <c r="F46" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G46" s="50">
         <v>100310120</v>
       </c>
       <c r="H46" s="50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J46" s="50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K46" s="50">
         <v>100310120</v>
       </c>
       <c r="M46" s="50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47">
@@ -4386,7 +4410,7 @@
         <v>4</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D47" s="50">
         <v>1</v>
@@ -4402,7 +4426,7 @@
       </c>
       <c r="H47" s="50"/>
       <c r="I47" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J47" s="50" t="s">
         <v>71</v>
@@ -4411,7 +4435,7 @@
         <v>100310130</v>
       </c>
       <c r="M47" s="50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48">
@@ -4422,7 +4446,7 @@
         <v>4</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D48" s="50">
         <v>1</v>
@@ -4440,16 +4464,16 @@
         <v>98</v>
       </c>
       <c r="I48" s="50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J48" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K48" s="50">
         <v>100310131</v>
       </c>
       <c r="M48" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49">
@@ -4460,7 +4484,7 @@
         <v>4</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D49" s="50">
         <v>1</v>
@@ -4478,7 +4502,7 @@
         <v>121</v>
       </c>
       <c r="I49" s="50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J49" s="50" t="s">
         <v>61</v>
@@ -4487,7 +4511,7 @@
         <v>100310132</v>
       </c>
       <c r="M49" s="50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50">
@@ -4498,7 +4522,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D50" s="50">
         <v>1</v>
@@ -4513,10 +4537,10 @@
         <v>100310133</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I50" s="50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J50" s="50" t="s">
         <v>71</v>
@@ -4525,7 +4549,7 @@
         <v>100310133</v>
       </c>
       <c r="M50" s="50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51">
@@ -4536,7 +4560,7 @@
         <v>4</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D51" s="50">
         <v>1</v>
@@ -4545,16 +4569,16 @@
         <v>118</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G51" s="50">
         <v>100310134</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J51" s="50" t="s">
         <v>71</v>
@@ -4563,7 +4587,7 @@
         <v>100310134</v>
       </c>
       <c r="M51" s="50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52">
@@ -4574,7 +4598,7 @@
         <v>4</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D52" s="50">
         <v>1</v>
@@ -4583,7 +4607,7 @@
         <v>118</v>
       </c>
       <c r="F52" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G52" s="50">
         <v>100310135</v>
@@ -4592,7 +4616,7 @@
         <v>132</v>
       </c>
       <c r="I52" s="50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J52" s="50" t="s">
         <v>71</v>
@@ -4601,7 +4625,7 @@
         <v>100310135</v>
       </c>
       <c r="M52" s="50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53">
@@ -4612,7 +4636,7 @@
         <v>4</v>
       </c>
       <c r="C53" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D53" s="50">
         <v>1</v>
@@ -4621,7 +4645,7 @@
         <v>118</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G53" s="50">
         <v>100310136</v>
@@ -4630,7 +4654,7 @@
         <v>136</v>
       </c>
       <c r="I53" s="50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J53" s="50" t="s">
         <v>71</v>
@@ -4639,7 +4663,7 @@
         <v>100310136</v>
       </c>
       <c r="M53" s="50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54">
@@ -4650,7 +4674,7 @@
         <v>4</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D54" s="50">
         <v>1</v>
@@ -4665,10 +4689,10 @@
         <v>100310137</v>
       </c>
       <c r="H54" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I54" s="50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J54" s="50" t="s">
         <v>71</v>
@@ -4677,7 +4701,7 @@
         <v>100310137</v>
       </c>
       <c r="M54" s="50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55">
@@ -4688,7 +4712,7 @@
         <v>4</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D55" s="50">
         <v>1</v>
@@ -4697,16 +4721,16 @@
         <v>118</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="G55" s="50">
         <v>100310138</v>
       </c>
       <c r="H55" s="50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I55" s="50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J55" s="50" t="s">
         <v>71</v>
@@ -4715,7 +4739,7 @@
         <v>100310138</v>
       </c>
       <c r="M55" s="50" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56">
@@ -4726,7 +4750,7 @@
         <v>4</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D56" s="50">
         <v>1</v>
@@ -4735,16 +4759,16 @@
         <v>118</v>
       </c>
       <c r="F56" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G56" s="50">
         <v>100310139</v>
       </c>
       <c r="H56" s="50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I56" s="50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J56" s="50" t="s">
         <v>71</v>
@@ -4753,7 +4777,7 @@
         <v>100310139</v>
       </c>
       <c r="M56" s="50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57">
@@ -4764,13 +4788,13 @@
         <v>4</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D57" s="50">
         <v>1</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F57" s="50" t="s">
         <v>116</v>
@@ -4779,7 +4803,7 @@
         <v>100310140</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J57" s="50" t="s">
         <v>71</v>
@@ -4788,7 +4812,7 @@
         <v>100310140</v>
       </c>
       <c r="M57" s="50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4799,13 +4823,13 @@
         <v>4</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D58" s="50">
         <v>1</v>
       </c>
       <c r="E58" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F58" s="50" t="s">
         <v>82</v>
@@ -4814,16 +4838,16 @@
         <v>100310141</v>
       </c>
       <c r="H58" s="50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J58" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K58" s="50">
         <v>100310141</v>
       </c>
       <c r="M58" s="50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4834,13 +4858,13 @@
         <v>4</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D59" s="50">
         <v>1</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F59" s="50" t="s">
         <v>118</v>
@@ -4849,7 +4873,7 @@
         <v>100310142</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J59" s="50" t="s">
         <v>61</v>
@@ -4858,7 +4882,7 @@
         <v>100310142</v>
       </c>
       <c r="M59" s="50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4869,13 +4893,13 @@
         <v>4</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D60" s="50">
         <v>1</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>120</v>
@@ -4884,7 +4908,7 @@
         <v>100310143</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J60" s="50" t="s">
         <v>71</v>
@@ -4893,7 +4917,7 @@
         <v>100310143</v>
       </c>
       <c r="M60" s="50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4904,22 +4928,22 @@
         <v>4</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D61" s="50">
         <v>1</v>
       </c>
       <c r="E61" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F61" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G61" s="50">
         <v>100310144</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J61" s="50" t="s">
         <v>71</v>
@@ -4928,7 +4952,7 @@
         <v>100310144</v>
       </c>
       <c r="M61" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4939,22 +4963,22 @@
         <v>4</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D62" s="50">
         <v>1</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F62" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G62" s="50">
         <v>100310145</v>
       </c>
       <c r="H62" s="50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J62" s="50" t="s">
         <v>71</v>
@@ -4963,7 +4987,7 @@
         <v>100310145</v>
       </c>
       <c r="M62" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" ht="12" customHeight="1" s="51" customFormat="1">
@@ -4974,22 +4998,22 @@
         <v>4</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D63" s="50">
         <v>1</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G63" s="50">
         <v>100310146</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J63" s="50" t="s">
         <v>71</v>
@@ -4998,7 +5022,7 @@
         <v>100310146</v>
       </c>
       <c r="M63" s="50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" ht="12" customHeight="1" s="51" customFormat="1">
@@ -5009,13 +5033,13 @@
         <v>4</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D64" s="50">
         <v>1</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F64" s="50" t="s">
         <v>135</v>
@@ -5024,7 +5048,7 @@
         <v>100310147</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J64" s="50" t="s">
         <v>71</v>
@@ -5033,7 +5057,7 @@
         <v>100310147</v>
       </c>
       <c r="M64" s="50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65">
@@ -5044,22 +5068,22 @@
         <v>4</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D65" s="50">
         <v>1</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="G65" s="50">
         <v>100310148</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J65" s="50" t="s">
         <v>71</v>
@@ -5068,7 +5092,7 @@
         <v>100310148</v>
       </c>
       <c r="M65" s="50" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66">
@@ -5079,22 +5103,22 @@
         <v>4</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D66" s="50">
         <v>1</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F66" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G66" s="50">
         <v>100310149</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J66" s="50" t="s">
         <v>71</v>
@@ -5103,7 +5127,7 @@
         <v>100310149</v>
       </c>
       <c r="M66" s="50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="51" customFormat="1">
@@ -5114,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D67" s="50">
         <v>1</v>
@@ -5123,7 +5147,7 @@
         <v>82</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G67" s="50">
         <v>100400000</v>
@@ -5132,13 +5156,13 @@
         <v>50</v>
       </c>
       <c r="J67" s="50" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K67" s="50">
         <v>100400000</v>
       </c>
       <c r="M67" s="50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="51" customFormat="1">
@@ -5149,7 +5173,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
@@ -5158,7 +5182,7 @@
         <v>71</v>
       </c>
       <c r="F68" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G68" s="50">
         <v>100400001</v>
@@ -5167,13 +5191,13 @@
         <v>100400000</v>
       </c>
       <c r="J68" s="50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K68" s="50">
         <v>100400001</v>
       </c>
       <c r="M68" s="50" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="51" customFormat="1">
@@ -5184,7 +5208,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D69" s="50">
         <v>1</v>
@@ -5193,13 +5217,13 @@
         <v>82</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G69" s="50">
         <v>100401000</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J69" s="50" t="s">
         <v>71</v>
@@ -5208,7 +5232,7 @@
         <v>100401000</v>
       </c>
       <c r="M69" s="50" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="51" customFormat="1">
@@ -5219,16 +5243,16 @@
         <v>1</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D70" s="50">
         <v>50</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F70" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G70" s="50">
         <v>100401001</v>
@@ -5237,7 +5261,7 @@
         <v>100401000</v>
       </c>
       <c r="J70" s="50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K70" s="50">
         <v>100401001</v>
@@ -5246,7 +5270,7 @@
         <v>900000008</v>
       </c>
       <c r="M70" s="50" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="51" customFormat="1">
@@ -5257,7 +5281,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D71" s="50">
         <v>1</v>
@@ -5266,13 +5290,13 @@
         <v>82</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G71" s="50">
         <v>100402000</v>
       </c>
       <c r="H71" s="50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J71" s="50">
         <v>1000</v>
@@ -5281,7 +5305,7 @@
         <v>100402000</v>
       </c>
       <c r="M71" s="50" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="51" customFormat="1">
@@ -5292,16 +5316,16 @@
         <v>1</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D72" s="50">
         <v>50</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F72" s="50" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G72" s="50">
         <v>100402001</v>
@@ -5310,7 +5334,7 @@
         <v>100402000</v>
       </c>
       <c r="J72" s="50" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K72" s="50">
         <v>100402001</v>
@@ -5319,7 +5343,7 @@
         <v>900000009</v>
       </c>
       <c r="M72" s="50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="51" customFormat="1">
@@ -5330,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D73" s="50">
         <v>1</v>
@@ -5345,7 +5369,7 @@
         <v>100403000</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J73" s="50">
         <v>10000</v>
@@ -5354,7 +5378,7 @@
         <v>100403000</v>
       </c>
       <c r="M73" s="50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="51" customFormat="1">
@@ -5365,13 +5389,13 @@
         <v>1</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D74" s="50">
         <v>50</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F74" s="50" t="s">
         <v>61</v>
@@ -5383,7 +5407,7 @@
         <v>100403000</v>
       </c>
       <c r="J74" s="50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K74" s="50">
         <v>100403001</v>
@@ -5392,7 +5416,7 @@
         <v>900000010</v>
       </c>
       <c r="M74" s="50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75">
@@ -5403,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D75" s="50">
         <v>1</v>
@@ -5425,7 +5449,7 @@
         <v>100500001</v>
       </c>
       <c r="M75" s="50" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="76">
@@ -5436,7 +5460,7 @@
         <v>1</v>
       </c>
       <c r="C76" s="50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D76" s="50">
         <v>1</v>
@@ -5445,7 +5469,7 @@
         <v>36</v>
       </c>
       <c r="F76" s="50" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G76" s="50">
         <v>100600001</v>
@@ -5454,13 +5478,13 @@
         <v>50</v>
       </c>
       <c r="J76" s="50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K76" s="50">
         <v>100600001</v>
       </c>
       <c r="M76" s="50" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77">
@@ -5471,7 +5495,7 @@
         <v>1</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D77" s="50">
         <v>10</v>
@@ -5480,16 +5504,16 @@
         <v>36</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G77" s="50">
         <v>100600002</v>
       </c>
       <c r="H77" s="50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J77" s="50" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K77" s="50">
         <v>100600002</v>
@@ -5498,7 +5522,7 @@
         <v>900000011</v>
       </c>
       <c r="M77" s="50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5525,7 +5549,7 @@
       </c>
       <c r="H78" s="50"/>
       <c r="J78" s="50" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K78" s="50">
         <v>200000001</v>
@@ -5534,7 +5558,7 @@
         <v>900000012</v>
       </c>
       <c r="M78" s="50" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5545,13 +5569,13 @@
         <v>2</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D79" s="50">
         <v>4</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F79" s="50" t="s">
         <v>82</v>
@@ -5560,10 +5584,10 @@
         <v>200100001</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J79" s="50" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K79" s="50">
         <v>200100001</v>
@@ -5572,7 +5596,7 @@
         <v>900000013</v>
       </c>
       <c r="M79" s="50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5583,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D80" s="50">
         <v>6</v>
@@ -5598,10 +5622,10 @@
         <v>200200001</v>
       </c>
       <c r="H80" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J80" s="50" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K80" s="50">
         <v>200200001</v>
@@ -5610,7 +5634,7 @@
         <v>900000014</v>
       </c>
       <c r="M80" s="50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5621,7 +5645,7 @@
         <v>2</v>
       </c>
       <c r="C81" s="50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D81" s="50">
         <v>10</v>
@@ -5636,10 +5660,10 @@
         <v>200300001</v>
       </c>
       <c r="H81" s="50" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J81" s="50" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K81" s="50">
         <v>200300001</v>
@@ -5648,7 +5672,7 @@
         <v>900000015</v>
       </c>
       <c r="M81" s="50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5659,7 +5683,7 @@
         <v>2</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D82" s="50">
         <v>10</v>
@@ -5674,10 +5698,10 @@
         <v>200400001</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J82" s="50" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K82" s="50">
         <v>200400001</v>
@@ -5686,7 +5710,7 @@
         <v>900000016</v>
       </c>
       <c r="M82" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="51" customFormat="1">
@@ -5697,7 +5721,7 @@
         <v>2</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D83" s="50">
         <v>5</v>
@@ -5712,10 +5736,10 @@
         <v>200500001</v>
       </c>
       <c r="H83" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J83" s="50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K83" s="50">
         <v>200500001</v>
@@ -5724,7 +5748,7 @@
         <v>900000017</v>
       </c>
       <c r="M83" s="50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="84">
@@ -5735,13 +5759,13 @@
         <v>2</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D84" s="50">
         <v>3</v>
       </c>
       <c r="E84" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F84" s="50" t="s">
         <v>71</v>
@@ -5750,10 +5774,10 @@
         <v>200600001</v>
       </c>
       <c r="H84" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J84" s="50" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K84" s="50">
         <v>200600001</v>
@@ -5762,7 +5786,7 @@
         <v>900000018</v>
       </c>
       <c r="M84" s="50" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85">
@@ -5773,7 +5797,7 @@
         <v>2</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D85" s="50">
         <v>4</v>
@@ -5782,16 +5806,16 @@
         <v>83</v>
       </c>
       <c r="F85" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G85" s="50">
         <v>200700001</v>
       </c>
       <c r="H85" s="50" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J85" s="50" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K85" s="50">
         <v>200700001</v>
@@ -5800,7 +5824,7 @@
         <v>900000019</v>
       </c>
       <c r="M85" s="50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="86">
@@ -5811,7 +5835,7 @@
         <v>2</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D86" s="50">
         <v>10</v>
@@ -5826,10 +5850,10 @@
         <v>200800001</v>
       </c>
       <c r="H86" s="50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J86" s="50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K86" s="50">
         <v>200800001</v>
@@ -5838,7 +5862,7 @@
         <v>900000020</v>
       </c>
       <c r="M86" s="50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="87">
@@ -5849,7 +5873,7 @@
         <v>2</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D87" s="50">
         <v>5</v>
@@ -5858,16 +5882,16 @@
         <v>82</v>
       </c>
       <c r="F87" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G87" s="50">
         <v>200900001</v>
       </c>
       <c r="H87" s="50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J87" s="50" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K87" s="50">
         <v>200900001</v>
@@ -5876,7 +5900,7 @@
         <v>900000021</v>
       </c>
       <c r="M87" s="50" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="88">
@@ -5902,7 +5926,7 @@
         <v>201000001</v>
       </c>
       <c r="H88" s="50" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J88" s="50" t="s">
         <v>71</v>
@@ -5911,7 +5935,7 @@
         <v>201000001</v>
       </c>
       <c r="M88" s="50" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="89">
@@ -5922,13 +5946,13 @@
         <v>3</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D89" s="50">
         <v>1</v>
       </c>
       <c r="E89" s="50" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F89" s="50" t="s">
         <v>82</v>
@@ -5946,7 +5970,7 @@
         <v>300100000</v>
       </c>
       <c r="M89" s="50" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="90">
@@ -5957,7 +5981,7 @@
         <v>3</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D90" s="50">
         <v>1</v>
@@ -5974,14 +5998,14 @@
       <c r="H90" s="50">
         <v>300100000</v>
       </c>
-      <c r="J90" s="50">
-        <v>100</v>
+      <c r="J90" s="50" t="s">
+        <v>254</v>
       </c>
       <c r="K90" s="50">
         <v>300100001</v>
       </c>
       <c r="M90" s="50" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="91">
@@ -5992,13 +6016,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D91" s="50">
         <v>1</v>
       </c>
       <c r="E91" s="50" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F91" s="50" t="s">
         <v>71</v>
@@ -6009,14 +6033,14 @@
       <c r="H91" s="50">
         <v>300100000</v>
       </c>
-      <c r="J91" s="50">
-        <v>100</v>
+      <c r="J91" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="K91" s="50">
         <v>300100002</v>
       </c>
       <c r="M91" s="50" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92">
@@ -6027,13 +6051,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D92" s="50">
         <v>1</v>
       </c>
       <c r="E92" s="50" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F92" s="50" t="s">
         <v>71</v>
@@ -6044,14 +6068,14 @@
       <c r="H92" s="50">
         <v>300100000</v>
       </c>
-      <c r="J92" s="50">
-        <v>100</v>
+      <c r="J92" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="K92" s="50">
         <v>300100003</v>
       </c>
       <c r="M92" s="50" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93">
@@ -6062,13 +6086,13 @@
         <v>3</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D93" s="50">
         <v>1</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F93" s="50" t="s">
         <v>71</v>
@@ -6079,14 +6103,14 @@
       <c r="H93" s="50">
         <v>300100000</v>
       </c>
-      <c r="J93" s="50">
-        <v>100</v>
+      <c r="J93" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="K93" s="50">
         <v>300100004</v>
       </c>
       <c r="M93" s="50" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94">
@@ -6097,31 +6121,31 @@
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D94" s="50">
         <v>1</v>
       </c>
       <c r="E94" s="50" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F94" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G94" s="50">
         <v>300100101</v>
       </c>
       <c r="H94" s="50" t="s">
-        <v>263</v>
-      </c>
-      <c r="J94" s="50">
-        <v>100</v>
+        <v>266</v>
+      </c>
+      <c r="J94" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="K94" s="50">
         <v>300100101</v>
       </c>
       <c r="M94" s="50" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="95">
@@ -6132,16 +6156,16 @@
         <v>3</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D95" s="50">
         <v>1</v>
       </c>
       <c r="E95" s="50" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F95" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G95" s="50">
         <v>300100102</v>
@@ -6149,14 +6173,14 @@
       <c r="H95" s="50">
         <v>300100101</v>
       </c>
-      <c r="J95" s="50">
-        <v>100</v>
+      <c r="J95" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="K95" s="50">
         <v>300100102</v>
       </c>
       <c r="M95" s="50" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="96">
@@ -6167,31 +6191,31 @@
         <v>3</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D96" s="50">
         <v>1</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G96" s="50">
         <v>300100201</v>
       </c>
       <c r="H96" s="50" t="s">
-        <v>267</v>
-      </c>
-      <c r="J96" s="50">
-        <v>100</v>
+        <v>270</v>
+      </c>
+      <c r="J96" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="K96" s="50">
         <v>300100201</v>
       </c>
       <c r="M96" s="50" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="97">
@@ -6202,31 +6226,31 @@
         <v>3</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D97" s="50">
         <v>1</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F97" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G97" s="50">
         <v>300100301</v>
       </c>
       <c r="H97" s="50" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="J97" s="50" t="s">
-        <v>271</v>
+        <v>37</v>
       </c>
       <c r="K97" s="50">
         <v>300100301</v>
       </c>
       <c r="M97" s="50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98">
@@ -6237,7 +6261,7 @@
         <v>3</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D98" s="50">
         <v>1</v>
@@ -6255,7 +6279,7 @@
         <v>300100102</v>
       </c>
       <c r="I98" s="50" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J98" s="50">
         <v>200</v>
@@ -6264,7 +6288,7 @@
         <v>300110011</v>
       </c>
       <c r="M98" s="50" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="99">
@@ -6275,7 +6299,7 @@
         <v>3</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D99" s="50">
         <v>1</v>
@@ -6299,7 +6323,7 @@
         <v>300110012</v>
       </c>
       <c r="M99" s="50" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="100">
@@ -6310,7 +6334,7 @@
         <v>3</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D100" s="50">
         <v>1</v>
@@ -6334,7 +6358,7 @@
         <v>300110013</v>
       </c>
       <c r="M100" s="50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="101">
@@ -6345,7 +6369,7 @@
         <v>3</v>
       </c>
       <c r="C101" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D101" s="50">
         <v>1</v>
@@ -6363,7 +6387,7 @@
         <v>300100102</v>
       </c>
       <c r="I101" s="50" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J101" s="50">
         <v>200</v>
@@ -6372,7 +6396,7 @@
         <v>300110021</v>
       </c>
       <c r="M101" s="50" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="102">
@@ -6383,7 +6407,7 @@
         <v>3</v>
       </c>
       <c r="C102" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D102" s="50">
         <v>1</v>
@@ -6407,7 +6431,7 @@
         <v>300110022</v>
       </c>
       <c r="M102" s="50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="103">
@@ -6418,7 +6442,7 @@
         <v>3</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D103" s="50">
         <v>1</v>
@@ -6442,7 +6466,7 @@
         <v>300110023</v>
       </c>
       <c r="M103" s="50" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="104">
@@ -6453,7 +6477,7 @@
         <v>3</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D104" s="50">
         <v>1</v>
@@ -6471,7 +6495,7 @@
         <v>300100102</v>
       </c>
       <c r="I104" s="50" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J104" s="50">
         <v>200</v>
@@ -6480,7 +6504,7 @@
         <v>300110031</v>
       </c>
       <c r="M104" s="50" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105">
@@ -6491,7 +6515,7 @@
         <v>3</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D105" s="50">
         <v>1</v>
@@ -6515,7 +6539,7 @@
         <v>300110032</v>
       </c>
       <c r="M105" s="50" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="106">
@@ -6526,7 +6550,7 @@
         <v>3</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D106" s="50">
         <v>1</v>
@@ -6550,7 +6574,7 @@
         <v>300110033</v>
       </c>
       <c r="M106" s="50" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="107">
@@ -6561,7 +6585,7 @@
         <v>3</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D107" s="50">
         <v>1</v>
@@ -6579,7 +6603,7 @@
         <v>300100102</v>
       </c>
       <c r="I107" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J107" s="50">
         <v>200</v>
@@ -6588,7 +6612,7 @@
         <v>300110041</v>
       </c>
       <c r="M107" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="108">
@@ -6599,7 +6623,7 @@
         <v>3</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D108" s="50">
         <v>1</v>
@@ -6623,7 +6647,7 @@
         <v>300110042</v>
       </c>
       <c r="M108" s="50" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="109">
@@ -6634,7 +6658,7 @@
         <v>3</v>
       </c>
       <c r="C109" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" s="50">
         <v>1</v>
@@ -6658,7 +6682,7 @@
         <v>300110043</v>
       </c>
       <c r="M109" s="50" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="110">
@@ -6669,7 +6693,7 @@
         <v>3</v>
       </c>
       <c r="C110" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D110" s="50">
         <v>1</v>
@@ -6691,7 +6715,7 @@
         <v>300200000</v>
       </c>
       <c r="M110" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="111">
@@ -6702,7 +6726,7 @@
         <v>3</v>
       </c>
       <c r="C111" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D111" s="50">
         <v>1</v>
@@ -6720,13 +6744,13 @@
         <v>300200000</v>
       </c>
       <c r="J111" s="50" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K111" s="50">
         <v>300200001</v>
       </c>
       <c r="M111" s="50" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="112">
@@ -6737,7 +6761,7 @@
         <v>3</v>
       </c>
       <c r="C112" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D112" s="50">
         <v>1</v>
@@ -6755,13 +6779,13 @@
         <v>300200000</v>
       </c>
       <c r="J112" s="50" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K112" s="50">
         <v>300200002</v>
       </c>
       <c r="M112" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="113">
@@ -6772,7 +6796,7 @@
         <v>3</v>
       </c>
       <c r="C113" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D113" s="50">
         <v>1</v>
@@ -6796,7 +6820,7 @@
         <v>300200003</v>
       </c>
       <c r="M113" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="114">
@@ -6807,7 +6831,7 @@
         <v>3</v>
       </c>
       <c r="C114" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" s="50">
         <v>1</v>
@@ -6831,7 +6855,7 @@
         <v>300200004</v>
       </c>
       <c r="M114" s="50" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="115" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6842,7 +6866,7 @@
         <v>3</v>
       </c>
       <c r="C115" s="50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D115" s="50">
         <v>1</v>
@@ -6851,22 +6875,22 @@
         <v>82</v>
       </c>
       <c r="F115" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G115" s="50">
         <v>300200101</v>
       </c>
       <c r="H115" s="50" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J115" s="50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K115" s="50">
         <v>300200101</v>
       </c>
       <c r="M115" s="50" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="116" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6877,7 +6901,7 @@
         <v>3</v>
       </c>
       <c r="C116" s="50" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D116" s="50">
         <v>1</v>
@@ -6886,7 +6910,7 @@
         <v>82</v>
       </c>
       <c r="F116" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G116" s="50">
         <v>300200102</v>
@@ -6901,7 +6925,7 @@
         <v>300200102</v>
       </c>
       <c r="M116" s="50" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="117" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6912,7 +6936,7 @@
         <v>3</v>
       </c>
       <c r="C117" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D117" s="50">
         <v>1</v>
@@ -6921,22 +6945,22 @@
         <v>92</v>
       </c>
       <c r="F117" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G117" s="50">
         <v>300200201</v>
       </c>
       <c r="H117" s="50" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J117" s="50" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="K117" s="50">
         <v>300200201</v>
       </c>
       <c r="M117" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="118" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6947,7 +6971,7 @@
         <v>3</v>
       </c>
       <c r="C118" s="50" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D118" s="50">
         <v>1</v>
@@ -6956,13 +6980,13 @@
         <v>82</v>
       </c>
       <c r="F118" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G118" s="50">
         <v>300200301</v>
       </c>
       <c r="H118" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J118" s="50" t="s">
         <v>84</v>
@@ -6971,7 +6995,7 @@
         <v>300200301</v>
       </c>
       <c r="M118" s="50" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="119" ht="12" customHeight="1" s="51" customFormat="1">
@@ -6982,7 +7006,7 @@
         <v>3</v>
       </c>
       <c r="C119" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D119" s="50">
         <v>1</v>
@@ -7000,7 +7024,7 @@
         <v>300200102</v>
       </c>
       <c r="I119" s="50" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J119" s="50">
         <v>200</v>
@@ -7009,7 +7033,7 @@
         <v>300210011</v>
       </c>
       <c r="M119" s="50" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="120" ht="12" customHeight="1" s="51" customFormat="1">
@@ -7020,7 +7044,7 @@
         <v>3</v>
       </c>
       <c r="C120" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D120" s="50">
         <v>1</v>
@@ -7044,7 +7068,7 @@
         <v>300210012</v>
       </c>
       <c r="M120" s="50" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="121" ht="12" customHeight="1" s="51" customFormat="1">
@@ -7055,7 +7079,7 @@
         <v>3</v>
       </c>
       <c r="C121" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D121" s="50">
         <v>1</v>
@@ -7079,7 +7103,7 @@
         <v>300210013</v>
       </c>
       <c r="M121" s="50" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="122" ht="12" customHeight="1" s="51" customFormat="1">
@@ -7090,7 +7114,7 @@
         <v>3</v>
       </c>
       <c r="C122" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D122" s="50">
         <v>1</v>
@@ -7108,7 +7132,7 @@
         <v>300200102</v>
       </c>
       <c r="I122" s="50" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J122" s="50">
         <v>200</v>
@@ -7117,7 +7141,7 @@
         <v>300210021</v>
       </c>
       <c r="M122" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="123" ht="12" customHeight="1" s="51" customFormat="1">
@@ -7128,7 +7152,7 @@
         <v>3</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D123" s="50">
         <v>1</v>
@@ -7152,7 +7176,7 @@
         <v>300210022</v>
       </c>
       <c r="M123" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="124">
@@ -7163,7 +7187,7 @@
         <v>3</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D124" s="50">
         <v>1</v>
@@ -7187,7 +7211,7 @@
         <v>300210023</v>
       </c>
       <c r="M124" s="50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="125">
@@ -7198,7 +7222,7 @@
         <v>3</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D125" s="50">
         <v>1</v>
@@ -7216,7 +7240,7 @@
         <v>300200102</v>
       </c>
       <c r="I125" s="50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J125" s="50">
         <v>200</v>
@@ -7225,7 +7249,7 @@
         <v>300210031</v>
       </c>
       <c r="M125" s="50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="126">
@@ -7236,7 +7260,7 @@
         <v>3</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D126" s="50">
         <v>1</v>
@@ -7260,7 +7284,7 @@
         <v>300210032</v>
       </c>
       <c r="M126" s="50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="127">
@@ -7271,7 +7295,7 @@
         <v>3</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D127" s="50">
         <v>1</v>
@@ -7296,7 +7320,7 @@
         <v>300210033</v>
       </c>
       <c r="M127" s="50" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="128">
@@ -7307,7 +7331,7 @@
         <v>3</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D128" s="50">
         <v>1</v>
@@ -7325,7 +7349,7 @@
         <v>300200102</v>
       </c>
       <c r="I128" s="50" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J128" s="50">
         <v>200</v>
@@ -7334,7 +7358,7 @@
         <v>300210041</v>
       </c>
       <c r="M128" s="50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="129">
@@ -7345,7 +7369,7 @@
         <v>3</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D129" s="50">
         <v>1</v>
@@ -7370,7 +7394,7 @@
         <v>300210042</v>
       </c>
       <c r="M129" s="50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="130">
@@ -7381,7 +7405,7 @@
         <v>3</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D130" s="50">
         <v>1</v>
@@ -7406,7 +7430,7 @@
         <v>300210043</v>
       </c>
       <c r="M130" s="50" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="131">
@@ -7417,7 +7441,7 @@
         <v>3</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D131" s="50">
         <v>1</v>
@@ -7436,13 +7460,13 @@
       </c>
       <c r="I131" s="50"/>
       <c r="J131" s="50" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="K131" s="50">
         <v>300300000</v>
       </c>
       <c r="M131" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="132">
@@ -7453,13 +7477,13 @@
         <v>3</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D132" s="50">
         <v>1</v>
       </c>
       <c r="E132" s="50" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F132" s="50" t="s">
         <v>71</v>
@@ -7478,7 +7502,7 @@
         <v>300300001</v>
       </c>
       <c r="M132" s="50" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="133">
@@ -7489,13 +7513,13 @@
         <v>3</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D133" s="50">
         <v>1</v>
       </c>
       <c r="E133" s="50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F133" s="50" t="s">
         <v>71</v>
@@ -7508,13 +7532,13 @@
       </c>
       <c r="I133" s="50"/>
       <c r="J133" s="50" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="K133" s="50">
         <v>300300002</v>
       </c>
       <c r="M133" s="50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="134">
@@ -7525,16 +7549,16 @@
         <v>3</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D134" s="50">
         <v>1</v>
       </c>
       <c r="E134" s="50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F134" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G134" s="50">
         <v>300300003</v>
@@ -7550,7 +7574,7 @@
         <v>300300003</v>
       </c>
       <c r="M134" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="135">
@@ -7561,7 +7585,7 @@
         <v>3</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D135" s="50">
         <v>1</v>
@@ -7586,7 +7610,7 @@
         <v>300300004</v>
       </c>
       <c r="M135" s="50" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="136">
@@ -7597,7 +7621,7 @@
         <v>3</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D136" s="50">
         <v>1</v>
@@ -7606,13 +7630,13 @@
         <v>86</v>
       </c>
       <c r="F136" s="50" t="s">
-        <v>151</v>
+        <v>335</v>
       </c>
       <c r="G136" s="50">
         <v>300300101</v>
       </c>
       <c r="H136" s="50" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="I136" s="50"/>
       <c r="J136" s="50" t="s">
@@ -7622,7 +7646,7 @@
         <v>300300101</v>
       </c>
       <c r="M136" s="50" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="137">
@@ -7633,7 +7657,7 @@
         <v>3</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D137" s="50">
         <v>1</v>
@@ -7642,7 +7666,7 @@
         <v>86</v>
       </c>
       <c r="F137" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G137" s="50">
         <v>300300102</v>
@@ -7657,7 +7681,7 @@
         <v>300300102</v>
       </c>
       <c r="M137" s="50" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="138">
@@ -7668,31 +7692,31 @@
         <v>3</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D138" s="50">
         <v>1</v>
       </c>
       <c r="E138" s="50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F138" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G138" s="50">
         <v>300300201</v>
       </c>
       <c r="H138" s="50" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J138" s="50" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="K138" s="50">
         <v>300300201</v>
       </c>
       <c r="M138" s="50" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="139">
@@ -7703,7 +7727,7 @@
         <v>3</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D139" s="50">
         <v>1</v>
@@ -7712,22 +7736,22 @@
         <v>86</v>
       </c>
       <c r="F139" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G139" s="50">
         <v>300300301</v>
       </c>
       <c r="H139" s="50" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J139" s="50" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="K139" s="50">
         <v>300300301</v>
       </c>
       <c r="M139" s="50" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="140">
@@ -7738,7 +7762,7 @@
         <v>3</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D140" s="50">
         <v>1</v>
@@ -7756,7 +7780,7 @@
         <v>300300102</v>
       </c>
       <c r="I140" s="50" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J140" s="50">
         <v>2000</v>
@@ -7765,7 +7789,7 @@
         <v>300310011</v>
       </c>
       <c r="M140" s="50" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="141">
@@ -7776,7 +7800,7 @@
         <v>3</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D141" s="50">
         <v>1</v>
@@ -7800,7 +7824,7 @@
         <v>300310012</v>
       </c>
       <c r="M141" s="50" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="142">
@@ -7811,7 +7835,7 @@
         <v>3</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D142" s="50">
         <v>1</v>
@@ -7835,7 +7859,7 @@
         <v>300310013</v>
       </c>
       <c r="M142" s="50" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="143">
@@ -7846,7 +7870,7 @@
         <v>3</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D143" s="50">
         <v>1</v>
@@ -7864,7 +7888,7 @@
         <v>300300102</v>
       </c>
       <c r="I143" s="50" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J143" s="50">
         <v>2000</v>
@@ -7873,7 +7897,7 @@
         <v>300310021</v>
       </c>
       <c r="M143" s="50" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="144">
@@ -7884,7 +7908,7 @@
         <v>3</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D144" s="50">
         <v>1</v>
@@ -7908,7 +7932,7 @@
         <v>300310022</v>
       </c>
       <c r="M144" s="50" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="145">
@@ -7919,7 +7943,7 @@
         <v>3</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D145" s="50">
         <v>1</v>
@@ -7943,7 +7967,7 @@
         <v>300310023</v>
       </c>
       <c r="M145" s="50" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="146">
@@ -7954,7 +7978,7 @@
         <v>3</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D146" s="50">
         <v>1</v>
@@ -7972,7 +7996,7 @@
         <v>300300102</v>
       </c>
       <c r="I146" s="50" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J146" s="50">
         <v>2000</v>
@@ -7981,7 +8005,7 @@
         <v>300310031</v>
       </c>
       <c r="M146" s="50" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="147">
@@ -7992,7 +8016,7 @@
         <v>3</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D147" s="50">
         <v>1</v>
@@ -8016,7 +8040,7 @@
         <v>300310032</v>
       </c>
       <c r="M147" s="50" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="148">
@@ -8027,7 +8051,7 @@
         <v>3</v>
       </c>
       <c r="C148" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D148" s="50">
         <v>1</v>
@@ -8051,7 +8075,7 @@
         <v>300310033</v>
       </c>
       <c r="M148" s="50" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="149">
@@ -8062,7 +8086,7 @@
         <v>3</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D149" s="50">
         <v>1</v>
@@ -8080,7 +8104,7 @@
         <v>300300102</v>
       </c>
       <c r="I149" s="50" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J149" s="50">
         <v>2000</v>
@@ -8089,7 +8113,7 @@
         <v>300310041</v>
       </c>
       <c r="M149" s="50" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="150">
@@ -8100,7 +8124,7 @@
         <v>3</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D150" s="50">
         <v>1</v>
@@ -8124,7 +8148,7 @@
         <v>300310042</v>
       </c>
       <c r="M150" s="50" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="151">
@@ -8135,7 +8159,7 @@
         <v>3</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D151" s="50">
         <v>1</v>
@@ -8159,7 +8183,7 @@
         <v>300310043</v>
       </c>
       <c r="M151" s="50" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="152">
@@ -8170,13 +8194,13 @@
         <v>3</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D152" s="50">
         <v>1</v>
       </c>
       <c r="E152" s="50" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F152" s="50" t="s">
         <v>82</v>
@@ -8194,7 +8218,7 @@
         <v>300400000</v>
       </c>
       <c r="M152" s="50" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="153">
@@ -8205,13 +8229,13 @@
         <v>3</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D153" s="50">
         <v>1</v>
       </c>
       <c r="E153" s="50" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F153" s="50" t="s">
         <v>71</v>
@@ -8229,7 +8253,7 @@
         <v>300400001</v>
       </c>
       <c r="M153" s="50" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="154">
@@ -8240,13 +8264,13 @@
         <v>3</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D154" s="50">
         <v>1</v>
       </c>
       <c r="E154" s="50" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F154" s="50" t="s">
         <v>71</v>
@@ -8264,7 +8288,7 @@
         <v>300400002</v>
       </c>
       <c r="M154" s="50" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="155">
@@ -8275,13 +8299,13 @@
         <v>3</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D155" s="50">
         <v>1</v>
       </c>
       <c r="E155" s="50" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F155" s="50" t="s">
         <v>71</v>
@@ -8299,7 +8323,7 @@
         <v>300400003</v>
       </c>
       <c r="M155" s="50" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="156">
@@ -8310,13 +8334,13 @@
         <v>3</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D156" s="50">
         <v>1</v>
       </c>
       <c r="E156" s="50" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F156" s="50" t="s">
         <v>71</v>
@@ -8334,7 +8358,7 @@
         <v>300400004</v>
       </c>
       <c r="M156" s="50" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="157">
@@ -8345,13 +8369,13 @@
         <v>3</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D157" s="50">
         <v>1</v>
       </c>
       <c r="E157" s="50" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F157" s="50" t="s">
         <v>71</v>
@@ -8369,7 +8393,7 @@
         <v>300400005</v>
       </c>
       <c r="M157" s="50" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="158">
@@ -8380,22 +8404,22 @@
         <v>3</v>
       </c>
       <c r="C158" s="50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D158" s="50">
         <v>1</v>
       </c>
       <c r="E158" s="50" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F158" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G158" s="50">
         <v>300400101</v>
       </c>
       <c r="H158" s="50" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J158" s="50">
         <v>100</v>
@@ -8404,7 +8428,7 @@
         <v>300400101</v>
       </c>
       <c r="M158" s="50" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="159">
@@ -8415,16 +8439,16 @@
         <v>3</v>
       </c>
       <c r="C159" s="50" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D159" s="50">
         <v>1</v>
       </c>
       <c r="E159" s="50" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F159" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G159" s="50">
         <v>300400102</v>
@@ -8439,7 +8463,7 @@
         <v>300400102</v>
       </c>
       <c r="M159" s="50" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="160">
@@ -8450,22 +8474,22 @@
         <v>3</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D160" s="50">
         <v>1</v>
       </c>
       <c r="E160" s="50" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F160" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G160" s="50">
         <v>300400201</v>
       </c>
       <c r="H160" s="50" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J160" s="50">
         <v>100</v>
@@ -8474,7 +8498,7 @@
         <v>300400201</v>
       </c>
       <c r="M160" s="50" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="161">
@@ -8485,22 +8509,22 @@
         <v>3</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D161" s="50">
         <v>1</v>
       </c>
       <c r="E161" s="50" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F161" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G161" s="50">
         <v>300400301</v>
       </c>
       <c r="H161" s="50" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J161" s="50">
         <v>100</v>
@@ -8509,7 +8533,7 @@
         <v>300400301</v>
       </c>
       <c r="M161" s="50" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="162">
@@ -8520,7 +8544,7 @@
         <v>3</v>
       </c>
       <c r="C162" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D162" s="50">
         <v>1</v>
@@ -8538,7 +8562,7 @@
         <v>300400102</v>
       </c>
       <c r="I162" s="50" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J162" s="50">
         <v>200</v>
@@ -8547,7 +8571,7 @@
         <v>300410011</v>
       </c>
       <c r="M162" s="50" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="163">
@@ -8558,7 +8582,7 @@
         <v>3</v>
       </c>
       <c r="C163" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D163" s="50">
         <v>1</v>
@@ -8582,7 +8606,7 @@
         <v>300410012</v>
       </c>
       <c r="M163" s="50" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="164">
@@ -8593,7 +8617,7 @@
         <v>3</v>
       </c>
       <c r="C164" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D164" s="50">
         <v>1</v>
@@ -8617,7 +8641,7 @@
         <v>300410013</v>
       </c>
       <c r="M164" s="50" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="165">
@@ -8628,7 +8652,7 @@
         <v>3</v>
       </c>
       <c r="C165" s="50" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D165" s="50">
         <v>1</v>
@@ -8646,7 +8670,7 @@
         <v>300400102</v>
       </c>
       <c r="I165" s="50" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J165" s="50">
         <v>200</v>
@@ -8655,7 +8679,7 @@
         <v>300410021</v>
       </c>
       <c r="M165" s="50" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="166">
@@ -8666,7 +8690,7 @@
         <v>3</v>
       </c>
       <c r="C166" s="50" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D166" s="50">
         <v>1</v>
@@ -8690,7 +8714,7 @@
         <v>300410022</v>
       </c>
       <c r="M166" s="50" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="167">
@@ -8701,7 +8725,7 @@
         <v>3</v>
       </c>
       <c r="C167" s="50" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D167" s="50">
         <v>1</v>
@@ -8725,7 +8749,7 @@
         <v>300410023</v>
       </c>
       <c r="M167" s="50" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="168">
@@ -8736,7 +8760,7 @@
         <v>3</v>
       </c>
       <c r="C168" s="50" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D168" s="50">
         <v>1</v>
@@ -8754,7 +8778,7 @@
         <v>300400102</v>
       </c>
       <c r="I168" s="50" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="J168" s="50">
         <v>200</v>
@@ -8763,7 +8787,7 @@
         <v>300410031</v>
       </c>
       <c r="M168" s="50" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="169">
@@ -8774,7 +8798,7 @@
         <v>3</v>
       </c>
       <c r="C169" s="50" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D169" s="50">
         <v>1</v>
@@ -8798,7 +8822,7 @@
         <v>300410032</v>
       </c>
       <c r="M169" s="50" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="170">
@@ -8809,7 +8833,7 @@
         <v>3</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D170" s="50">
         <v>1</v>
@@ -8833,7 +8857,7 @@
         <v>300410033</v>
       </c>
       <c r="M170" s="50" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="171">
@@ -8844,7 +8868,7 @@
         <v>3</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D171" s="50">
         <v>1</v>
@@ -8862,7 +8886,7 @@
         <v>300400102</v>
       </c>
       <c r="I171" s="50" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J171" s="50">
         <v>200</v>
@@ -8871,7 +8895,7 @@
         <v>300410041</v>
       </c>
       <c r="M171" s="50" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="172">
@@ -8882,7 +8906,7 @@
         <v>3</v>
       </c>
       <c r="C172" s="50" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D172" s="50">
         <v>1</v>
@@ -8906,7 +8930,7 @@
         <v>300410042</v>
       </c>
       <c r="M172" s="50" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="173">
@@ -8917,7 +8941,7 @@
         <v>3</v>
       </c>
       <c r="C173" s="50" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D173" s="50">
         <v>1</v>
@@ -8941,7 +8965,7 @@
         <v>300410043</v>
       </c>
       <c r="M173" s="50" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="174">
@@ -8952,7 +8976,7 @@
         <v>3</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D174" s="50">
         <v>1</v>
@@ -8970,7 +8994,7 @@
         <v>300400102</v>
       </c>
       <c r="I174" s="50" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="J174" s="50">
         <v>200</v>
@@ -8979,7 +9003,7 @@
         <v>300410051</v>
       </c>
       <c r="M174" s="50" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="175">
@@ -8990,7 +9014,7 @@
         <v>3</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D175" s="50">
         <v>1</v>
@@ -9014,7 +9038,7 @@
         <v>300410052</v>
       </c>
       <c r="M175" s="50" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="176">
@@ -9025,7 +9049,7 @@
         <v>3</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D176" s="50">
         <v>1</v>
@@ -9049,7 +9073,7 @@
         <v>300410053</v>
       </c>
       <c r="M176" s="50" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="177">
@@ -9060,13 +9084,13 @@
         <v>3</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D177" s="50">
         <v>1</v>
       </c>
       <c r="E177" s="50" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F177" s="50" t="s">
         <v>82</v>
@@ -9084,7 +9108,7 @@
         <v>300500000</v>
       </c>
       <c r="M177" s="50" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="178">
@@ -9095,13 +9119,13 @@
         <v>3</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D178" s="50">
         <v>1</v>
       </c>
       <c r="E178" s="50" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F178" s="50" t="s">
         <v>71</v>
@@ -9119,7 +9143,7 @@
         <v>300500001</v>
       </c>
       <c r="M178" s="50" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="179">
@@ -9130,13 +9154,13 @@
         <v>3</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D179" s="50">
         <v>1</v>
       </c>
       <c r="E179" s="50" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F179" s="50" t="s">
         <v>71</v>
@@ -9154,7 +9178,7 @@
         <v>300500002</v>
       </c>
       <c r="M179" s="50" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="180">
@@ -9165,13 +9189,13 @@
         <v>3</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D180" s="50">
         <v>1</v>
       </c>
       <c r="E180" s="50" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F180" s="50" t="s">
         <v>71</v>
@@ -9189,7 +9213,7 @@
         <v>300500003</v>
       </c>
       <c r="M180" s="50" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="181">
@@ -9200,13 +9224,13 @@
         <v>3</v>
       </c>
       <c r="C181" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D181" s="50">
         <v>1</v>
       </c>
       <c r="E181" s="50" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F181" s="50" t="s">
         <v>71</v>
@@ -9224,7 +9248,7 @@
         <v>300500004</v>
       </c>
       <c r="M181" s="50" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="182">
@@ -9235,22 +9259,22 @@
         <v>3</v>
       </c>
       <c r="C182" s="50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D182" s="50">
         <v>1</v>
       </c>
       <c r="E182" s="50" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F182" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G182" s="50">
         <v>300500101</v>
       </c>
       <c r="H182" s="50" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="J182" s="50">
         <v>100</v>
@@ -9259,7 +9283,7 @@
         <v>300500101</v>
       </c>
       <c r="M182" s="50" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="183">
@@ -9270,16 +9294,16 @@
         <v>3</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D183" s="50">
         <v>1</v>
       </c>
       <c r="E183" s="50" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F183" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G183" s="50">
         <v>300500102</v>
@@ -9294,7 +9318,7 @@
         <v>300500102</v>
       </c>
       <c r="M183" s="50" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="184">
@@ -9305,22 +9329,22 @@
         <v>3</v>
       </c>
       <c r="C184" s="50" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D184" s="50">
         <v>1</v>
       </c>
       <c r="E184" s="50" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F184" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G184" s="50">
         <v>300500201</v>
       </c>
       <c r="H184" s="50" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J184" s="50">
         <v>100</v>
@@ -9329,7 +9353,7 @@
         <v>300500201</v>
       </c>
       <c r="M184" s="50" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="185">
@@ -9340,22 +9364,22 @@
         <v>3</v>
       </c>
       <c r="C185" s="50" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D185" s="50">
         <v>1</v>
       </c>
       <c r="E185" s="50" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F185" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G185" s="50">
         <v>300500301</v>
       </c>
       <c r="H185" s="50" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J185" s="50">
         <v>100</v>
@@ -9364,7 +9388,7 @@
         <v>300500301</v>
       </c>
       <c r="M185" s="50" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="186">
@@ -9375,7 +9399,7 @@
         <v>3</v>
       </c>
       <c r="C186" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D186" s="50">
         <v>1</v>
@@ -9393,7 +9417,7 @@
         <v>300500102</v>
       </c>
       <c r="I186" s="50" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="J186" s="50">
         <v>200</v>
@@ -9402,7 +9426,7 @@
         <v>300510011</v>
       </c>
       <c r="M186" s="50" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="187">
@@ -9413,7 +9437,7 @@
         <v>3</v>
       </c>
       <c r="C187" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D187" s="50">
         <v>1</v>
@@ -9437,7 +9461,7 @@
         <v>300510012</v>
       </c>
       <c r="M187" s="50" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="188">
@@ -9448,7 +9472,7 @@
         <v>3</v>
       </c>
       <c r="C188" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D188" s="50">
         <v>1</v>
@@ -9472,7 +9496,7 @@
         <v>300510013</v>
       </c>
       <c r="M188" s="50" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="189">
@@ -9483,7 +9507,7 @@
         <v>3</v>
       </c>
       <c r="C189" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D189" s="50">
         <v>1</v>
@@ -9501,7 +9525,7 @@
         <v>300500102</v>
       </c>
       <c r="I189" s="50" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="J189" s="50">
         <v>200</v>
@@ -9510,7 +9534,7 @@
         <v>300510021</v>
       </c>
       <c r="M189" s="50" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190">
@@ -9521,7 +9545,7 @@
         <v>3</v>
       </c>
       <c r="C190" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D190" s="50">
         <v>1</v>
@@ -9545,7 +9569,7 @@
         <v>300510022</v>
       </c>
       <c r="M190" s="50" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="191">
@@ -9556,7 +9580,7 @@
         <v>3</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D191" s="50">
         <v>1</v>
@@ -9580,7 +9604,7 @@
         <v>300510023</v>
       </c>
       <c r="M191" s="50" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="192">
@@ -9591,7 +9615,7 @@
         <v>3</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D192" s="50">
         <v>1</v>
@@ -9609,7 +9633,7 @@
         <v>300500102</v>
       </c>
       <c r="I192" s="50" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="J192" s="50">
         <v>200</v>
@@ -9618,7 +9642,7 @@
         <v>300510031</v>
       </c>
       <c r="M192" s="50" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="193">
@@ -9629,7 +9653,7 @@
         <v>3</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D193" s="50">
         <v>1</v>
@@ -9653,7 +9677,7 @@
         <v>300510032</v>
       </c>
       <c r="M193" s="50" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="194">
@@ -9664,7 +9688,7 @@
         <v>3</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D194" s="50">
         <v>1</v>
@@ -9688,7 +9712,7 @@
         <v>300510033</v>
       </c>
       <c r="M194" s="50" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="195">
@@ -9699,7 +9723,7 @@
         <v>3</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" s="50">
         <v>1</v>
@@ -9717,7 +9741,7 @@
         <v>300500102</v>
       </c>
       <c r="I195" s="50" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="J195" s="50">
         <v>200</v>
@@ -9726,7 +9750,7 @@
         <v>300510041</v>
       </c>
       <c r="M195" s="50" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="196">
@@ -9737,7 +9761,7 @@
         <v>3</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D196" s="50">
         <v>1</v>
@@ -9761,7 +9785,7 @@
         <v>300510042</v>
       </c>
       <c r="M196" s="50" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="197">
@@ -9772,7 +9796,7 @@
         <v>3</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D197" s="50">
         <v>1</v>
@@ -9796,7 +9820,7 @@
         <v>300510043</v>
       </c>
       <c r="M197" s="50" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="198">
@@ -9807,13 +9831,13 @@
         <v>3</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D198" s="50">
         <v>1</v>
       </c>
       <c r="E198" s="50" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F198" s="50" t="s">
         <v>82</v>
@@ -9824,14 +9848,14 @@
       <c r="H198" s="50">
         <v>300300000</v>
       </c>
-      <c r="J198" s="50">
-        <v>100</v>
+      <c r="J198" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="K198" s="50">
         <v>300600000</v>
       </c>
       <c r="M198" s="50" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="199">
@@ -9842,13 +9866,13 @@
         <v>3</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D199" s="50">
         <v>1</v>
       </c>
       <c r="E199" s="50" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F199" s="50" t="s">
         <v>71</v>
@@ -9859,14 +9883,14 @@
       <c r="H199" s="50">
         <v>300600000</v>
       </c>
-      <c r="J199" s="50">
-        <v>100</v>
+      <c r="J199" s="50" t="s">
+        <v>254</v>
       </c>
       <c r="K199" s="50">
         <v>300600001</v>
       </c>
       <c r="M199" s="50" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200">
@@ -9877,13 +9901,13 @@
         <v>3</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D200" s="50">
         <v>1</v>
       </c>
       <c r="E200" s="50" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F200" s="50" t="s">
         <v>71</v>
@@ -9894,14 +9918,14 @@
       <c r="H200" s="50">
         <v>300600000</v>
       </c>
-      <c r="J200" s="50">
-        <v>100</v>
+      <c r="J200" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="K200" s="50">
         <v>300600002</v>
       </c>
       <c r="M200" s="50" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201">
@@ -9912,13 +9936,13 @@
         <v>3</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>253</v>
+        <v>327</v>
       </c>
       <c r="D201" s="50">
         <v>1</v>
       </c>
       <c r="E201" s="50" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F201" s="50" t="s">
         <v>71</v>
@@ -9929,14 +9953,14 @@
       <c r="H201" s="50">
         <v>300600000</v>
       </c>
-      <c r="J201" s="50">
-        <v>100</v>
+      <c r="J201" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="K201" s="50">
         <v>300600003</v>
       </c>
       <c r="M201" s="50" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202">
@@ -9947,13 +9971,13 @@
         <v>3</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D202" s="50">
         <v>1</v>
       </c>
       <c r="E202" s="50" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F202" s="50" t="s">
         <v>71</v>
@@ -9964,14 +9988,14 @@
       <c r="H202" s="50">
         <v>300600000</v>
       </c>
-      <c r="J202" s="50">
-        <v>100</v>
+      <c r="J202" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="K202" s="50">
         <v>300600004</v>
       </c>
       <c r="M202" s="50" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="203">
@@ -9982,13 +10006,13 @@
         <v>3</v>
       </c>
       <c r="C203" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" s="50">
         <v>1</v>
       </c>
       <c r="E203" s="50" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F203" s="50" t="s">
         <v>71</v>
@@ -9999,14 +10023,14 @@
       <c r="H203" s="50">
         <v>300600000</v>
       </c>
-      <c r="J203" s="50">
-        <v>100</v>
+      <c r="J203" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="K203" s="50">
         <v>300600005</v>
       </c>
       <c r="M203" s="50" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204">
@@ -10017,31 +10041,31 @@
         <v>3</v>
       </c>
       <c r="C204" s="50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D204" s="50">
         <v>1</v>
       </c>
       <c r="E204" s="50" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F204" s="50" t="s">
-        <v>151</v>
+        <v>449</v>
       </c>
       <c r="G204" s="50">
         <v>300600101</v>
       </c>
       <c r="H204" s="50" t="s">
-        <v>446</v>
-      </c>
-      <c r="J204" s="50">
-        <v>100</v>
+        <v>450</v>
+      </c>
+      <c r="J204" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="K204" s="50">
         <v>300600101</v>
       </c>
       <c r="M204" s="50" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="205">
@@ -10052,16 +10076,16 @@
         <v>3</v>
       </c>
       <c r="C205" s="50" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D205" s="50">
         <v>1</v>
       </c>
       <c r="E205" s="50" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F205" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G205" s="50">
         <v>300600102</v>
@@ -10069,14 +10093,14 @@
       <c r="H205" s="50">
         <v>300600101</v>
       </c>
-      <c r="J205" s="50">
-        <v>100</v>
+      <c r="J205" s="50" t="s">
+        <v>125</v>
       </c>
       <c r="K205" s="50">
         <v>300600102</v>
       </c>
       <c r="M205" s="50" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="206">
@@ -10087,31 +10111,31 @@
         <v>3</v>
       </c>
       <c r="C206" s="50" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D206" s="50">
         <v>1</v>
       </c>
       <c r="E206" s="50" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F206" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G206" s="50">
         <v>300600201</v>
       </c>
       <c r="H206" s="50" t="s">
-        <v>449</v>
-      </c>
-      <c r="J206" s="50">
-        <v>100</v>
+        <v>453</v>
+      </c>
+      <c r="J206" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="K206" s="50">
         <v>300600201</v>
       </c>
       <c r="M206" s="50" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="207">
@@ -10122,31 +10146,31 @@
         <v>3</v>
       </c>
       <c r="C207" s="50" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D207" s="50">
         <v>1</v>
       </c>
       <c r="E207" s="50" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F207" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G207" s="50">
         <v>300600301</v>
       </c>
       <c r="H207" s="50" t="s">
-        <v>451</v>
-      </c>
-      <c r="J207" s="50">
-        <v>100</v>
+        <v>455</v>
+      </c>
+      <c r="J207" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="K207" s="50">
         <v>300600301</v>
       </c>
       <c r="M207" s="50" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="208">
@@ -10157,7 +10181,7 @@
         <v>3</v>
       </c>
       <c r="C208" s="50" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D208" s="50">
         <v>1</v>
@@ -10175,7 +10199,7 @@
         <v>300600102</v>
       </c>
       <c r="I208" s="50" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="J208" s="50">
         <v>200</v>
@@ -10184,7 +10208,7 @@
         <v>300610011</v>
       </c>
       <c r="M208" s="50" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="209">
@@ -10195,7 +10219,7 @@
         <v>3</v>
       </c>
       <c r="C209" s="50" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D209" s="50">
         <v>1</v>
@@ -10219,7 +10243,7 @@
         <v>300610012</v>
       </c>
       <c r="M209" s="50" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="210">
@@ -10230,7 +10254,7 @@
         <v>3</v>
       </c>
       <c r="C210" s="50" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D210" s="50">
         <v>1</v>
@@ -10254,7 +10278,7 @@
         <v>300610013</v>
       </c>
       <c r="M210" s="50" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="211">
@@ -10265,7 +10289,7 @@
         <v>3</v>
       </c>
       <c r="C211" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D211" s="50">
         <v>1</v>
@@ -10283,7 +10307,7 @@
         <v>300600102</v>
       </c>
       <c r="I211" s="50" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="J211" s="50">
         <v>200</v>
@@ -10292,7 +10316,7 @@
         <v>300610021</v>
       </c>
       <c r="M211" s="50" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="212">
@@ -10303,7 +10327,7 @@
         <v>3</v>
       </c>
       <c r="C212" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D212" s="50">
         <v>1</v>
@@ -10327,7 +10351,7 @@
         <v>300610022</v>
       </c>
       <c r="M212" s="50" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="213">
@@ -10338,7 +10362,7 @@
         <v>3</v>
       </c>
       <c r="C213" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D213" s="50">
         <v>1</v>
@@ -10362,7 +10386,7 @@
         <v>300610023</v>
       </c>
       <c r="M213" s="50" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="214">
@@ -10373,7 +10397,7 @@
         <v>3</v>
       </c>
       <c r="C214" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D214" s="50">
         <v>1</v>
@@ -10391,7 +10415,7 @@
         <v>300600102</v>
       </c>
       <c r="I214" s="50" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="J214" s="50">
         <v>200</v>
@@ -10400,7 +10424,7 @@
         <v>300610031</v>
       </c>
       <c r="M214" s="50" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="215">
@@ -10411,7 +10435,7 @@
         <v>3</v>
       </c>
       <c r="C215" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D215" s="50">
         <v>1</v>
@@ -10435,7 +10459,7 @@
         <v>300610032</v>
       </c>
       <c r="M215" s="50" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="216">
@@ -10446,7 +10470,7 @@
         <v>3</v>
       </c>
       <c r="C216" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D216" s="50">
         <v>1</v>
@@ -10470,7 +10494,7 @@
         <v>300610033</v>
       </c>
       <c r="M216" s="50" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="217">
@@ -10481,7 +10505,7 @@
         <v>3</v>
       </c>
       <c r="C217" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D217" s="50">
         <v>1</v>
@@ -10499,7 +10523,7 @@
         <v>300600102</v>
       </c>
       <c r="I217" s="50" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="J217" s="50">
         <v>200</v>
@@ -10508,7 +10532,7 @@
         <v>300610041</v>
       </c>
       <c r="M217" s="50" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="218">
@@ -10519,7 +10543,7 @@
         <v>3</v>
       </c>
       <c r="C218" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D218" s="50">
         <v>1</v>
@@ -10543,7 +10567,7 @@
         <v>300610042</v>
       </c>
       <c r="M218" s="50" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="219">
@@ -10554,7 +10578,7 @@
         <v>3</v>
       </c>
       <c r="C219" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D219" s="50">
         <v>1</v>
@@ -10578,7 +10602,7 @@
         <v>300610043</v>
       </c>
       <c r="M219" s="50" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="220">
@@ -10589,7 +10613,7 @@
         <v>3</v>
       </c>
       <c r="C220" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D220" s="50">
         <v>1</v>
@@ -10607,7 +10631,7 @@
         <v>300600102</v>
       </c>
       <c r="I220" s="50" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="J220" s="50">
         <v>200</v>
@@ -10616,7 +10640,7 @@
         <v>300610051</v>
       </c>
       <c r="M220" s="50" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="221">
@@ -10627,7 +10651,7 @@
         <v>3</v>
       </c>
       <c r="C221" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D221" s="50">
         <v>1</v>
@@ -10651,7 +10675,7 @@
         <v>300610052</v>
       </c>
       <c r="M221" s="50" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="222">
@@ -10662,7 +10686,7 @@
         <v>3</v>
       </c>
       <c r="C222" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" s="50">
         <v>1</v>
@@ -10686,7 +10710,7 @@
         <v>300610053</v>
       </c>
       <c r="M222" s="50" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="223">
@@ -10697,13 +10721,13 @@
         <v>3</v>
       </c>
       <c r="C223" s="50" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D223" s="50">
         <v>1</v>
       </c>
       <c r="E223" s="50" t="s">
-        <v>126</v>
+        <v>478</v>
       </c>
       <c r="F223" s="50" t="s">
         <v>82</v>
@@ -10721,7 +10745,7 @@
         <v>300700000</v>
       </c>
       <c r="M223" s="50" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="224">
@@ -10732,13 +10756,13 @@
         <v>3</v>
       </c>
       <c r="C224" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D224" s="50">
         <v>1</v>
       </c>
       <c r="E224" s="50" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="F224" s="50" t="s">
         <v>71</v>
@@ -10756,7 +10780,7 @@
         <v>300700001</v>
       </c>
       <c r="M224" s="50" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="225">
@@ -10767,13 +10791,13 @@
         <v>3</v>
       </c>
       <c r="C225" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D225" s="50">
         <v>1</v>
       </c>
       <c r="E225" s="50" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F225" s="50" t="s">
         <v>71</v>
@@ -10791,7 +10815,7 @@
         <v>300700002</v>
       </c>
       <c r="M225" s="50" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="226">
@@ -10802,13 +10826,13 @@
         <v>3</v>
       </c>
       <c r="C226" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D226" s="50">
         <v>1</v>
       </c>
       <c r="E226" s="50" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F226" s="50" t="s">
         <v>71</v>
@@ -10826,7 +10850,7 @@
         <v>300700003</v>
       </c>
       <c r="M226" s="50" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="227">
@@ -10837,13 +10861,13 @@
         <v>3</v>
       </c>
       <c r="C227" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D227" s="50">
         <v>1</v>
       </c>
       <c r="E227" s="50" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F227" s="50" t="s">
         <v>71</v>
@@ -10861,7 +10885,7 @@
         <v>300700004</v>
       </c>
       <c r="M227" s="50" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="228">
@@ -10872,22 +10896,22 @@
         <v>3</v>
       </c>
       <c r="C228" s="50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D228" s="50">
         <v>1</v>
       </c>
       <c r="E228" s="50" t="s">
-        <v>126</v>
+        <v>478</v>
       </c>
       <c r="F228" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G228" s="50">
         <v>300700101</v>
       </c>
       <c r="H228" s="50" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="J228" s="50">
         <v>100</v>
@@ -10896,7 +10920,7 @@
         <v>300700101</v>
       </c>
       <c r="M228" s="50" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="229">
@@ -10907,16 +10931,16 @@
         <v>3</v>
       </c>
       <c r="C229" s="50" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D229" s="50">
         <v>1</v>
       </c>
       <c r="E229" s="50" t="s">
-        <v>126</v>
+        <v>478</v>
       </c>
       <c r="F229" s="50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G229" s="50">
         <v>300700102</v>
@@ -10931,7 +10955,7 @@
         <v>300700102</v>
       </c>
       <c r="M229" s="50" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="230">
@@ -10942,22 +10966,22 @@
         <v>3</v>
       </c>
       <c r="C230" s="50" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D230" s="50">
         <v>1</v>
       </c>
       <c r="E230" s="50" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="F230" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G230" s="50">
         <v>300700201</v>
       </c>
       <c r="H230" s="50" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="J230" s="50">
         <v>100</v>
@@ -10966,7 +10990,7 @@
         <v>300700201</v>
       </c>
       <c r="M230" s="50" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231">
@@ -10977,22 +11001,22 @@
         <v>3</v>
       </c>
       <c r="C231" s="50" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D231" s="50">
         <v>1</v>
       </c>
       <c r="E231" s="50" t="s">
-        <v>126</v>
+        <v>478</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G231" s="50">
         <v>300700301</v>
       </c>
       <c r="H231" s="50" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="J231" s="50">
         <v>100</v>
@@ -11001,7 +11025,7 @@
         <v>300700301</v>
       </c>
       <c r="M231" s="50" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232">
@@ -11012,7 +11036,7 @@
         <v>3</v>
       </c>
       <c r="C232" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D232" s="50">
         <v>1</v>
@@ -11030,7 +11054,7 @@
         <v>300700102</v>
       </c>
       <c r="I232" s="50" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="J232" s="50">
         <v>200</v>
@@ -11039,7 +11063,7 @@
         <v>300710011</v>
       </c>
       <c r="M232" s="50" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233">
@@ -11050,7 +11074,7 @@
         <v>3</v>
       </c>
       <c r="C233" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D233" s="50">
         <v>1</v>
@@ -11074,7 +11098,7 @@
         <v>300710012</v>
       </c>
       <c r="M233" s="50" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234">
@@ -11085,7 +11109,7 @@
         <v>3</v>
       </c>
       <c r="C234" s="50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D234" s="50">
         <v>1</v>
@@ -11109,7 +11133,7 @@
         <v>300710013</v>
       </c>
       <c r="M234" s="50" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235">
@@ -11120,7 +11144,7 @@
         <v>3</v>
       </c>
       <c r="C235" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D235" s="50">
         <v>1</v>
@@ -11138,7 +11162,7 @@
         <v>300700102</v>
       </c>
       <c r="I235" s="50" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="J235" s="50">
         <v>200</v>
@@ -11147,7 +11171,7 @@
         <v>300710021</v>
       </c>
       <c r="M235" s="50" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236">
@@ -11158,7 +11182,7 @@
         <v>3</v>
       </c>
       <c r="C236" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D236" s="50">
         <v>1</v>
@@ -11182,7 +11206,7 @@
         <v>300710022</v>
       </c>
       <c r="M236" s="50" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237">
@@ -11193,7 +11217,7 @@
         <v>3</v>
       </c>
       <c r="C237" s="50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D237" s="50">
         <v>1</v>
@@ -11217,7 +11241,7 @@
         <v>300710023</v>
       </c>
       <c r="M237" s="50" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238">
@@ -11228,7 +11252,7 @@
         <v>3</v>
       </c>
       <c r="C238" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D238" s="50">
         <v>1</v>
@@ -11246,7 +11270,7 @@
         <v>300700102</v>
       </c>
       <c r="I238" s="50" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="J238" s="50">
         <v>200</v>
@@ -11255,7 +11279,7 @@
         <v>300710031</v>
       </c>
       <c r="M238" s="50" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239">
@@ -11266,7 +11290,7 @@
         <v>3</v>
       </c>
       <c r="C239" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D239" s="50">
         <v>1</v>
@@ -11290,7 +11314,7 @@
         <v>300710032</v>
       </c>
       <c r="M239" s="50" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240">
@@ -11301,7 +11325,7 @@
         <v>3</v>
       </c>
       <c r="C240" s="50" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D240" s="50">
         <v>1</v>
@@ -11325,7 +11349,7 @@
         <v>300710033</v>
       </c>
       <c r="M240" s="50" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241">
@@ -11336,7 +11360,7 @@
         <v>3</v>
       </c>
       <c r="C241" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D241" s="50">
         <v>1</v>
@@ -11354,7 +11378,7 @@
         <v>300700102</v>
       </c>
       <c r="I241" s="50" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="J241" s="50">
         <v>200</v>
@@ -11363,7 +11387,7 @@
         <v>300710041</v>
       </c>
       <c r="M241" s="50" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242">
@@ -11374,7 +11398,7 @@
         <v>3</v>
       </c>
       <c r="C242" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D242" s="50">
         <v>1</v>
@@ -11398,7 +11422,7 @@
         <v>300710042</v>
       </c>
       <c r="M242" s="50" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="243">
@@ -11409,7 +11433,7 @@
         <v>3</v>
       </c>
       <c r="C243" s="50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D243" s="50">
         <v>1</v>
@@ -11433,7 +11457,7 @@
         <v>300710043</v>
       </c>
       <c r="M243" s="50" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="244">
@@ -11462,7 +11486,7 @@
         <v>98</v>
       </c>
       <c r="J244" s="50" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="K244" s="50">
         <v>100300007</v>
@@ -11471,48 +11495,87 @@
         <v>900000022</v>
       </c>
       <c r="M244" s="50" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="51">
+      <c r="A245" s="50">
         <v>100300008</v>
       </c>
-      <c r="B245" s="51">
+      <c r="B245" s="50">
         <v>4</v>
       </c>
-      <c r="C245" s="51" t="s">
+      <c r="C245" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="D245" s="51">
+      <c r="D245" s="50">
         <v>9</v>
       </c>
-      <c r="E245" s="51" t="s">
+      <c r="E245" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="F245" s="51" t="s">
+      <c r="F245" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="G245" s="51">
+      <c r="G245" s="50">
         <v>100300008</v>
       </c>
-      <c r="H245" s="51" t="s">
-        <v>509</v>
-      </c>
-      <c r="I245" s="51" t="s">
-        <v>510</v>
-      </c>
-      <c r="J245" s="51" t="s">
-        <v>511</v>
-      </c>
-      <c r="K245" s="51">
+      <c r="H245" s="50" t="s">
+        <v>514</v>
+      </c>
+      <c r="I245" s="50" t="s">
+        <v>515</v>
+      </c>
+      <c r="J245" s="50" t="s">
+        <v>516</v>
+      </c>
+      <c r="K245" s="50">
         <v>100300008</v>
       </c>
-      <c r="L245" s="51">
+      <c r="L245" s="50">
         <v>900000022</v>
       </c>
-      <c r="M245" s="49" t="s">
-        <v>512</v>
+      <c r="M245" s="50" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="50">
+        <v>100300009</v>
+      </c>
+      <c r="B246" s="50">
+        <v>4</v>
+      </c>
+      <c r="C246" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="D246" s="50">
+        <v>4</v>
+      </c>
+      <c r="E246" s="50">
+        <v>-480</v>
+      </c>
+      <c r="F246" s="50">
+        <v>-160</v>
+      </c>
+      <c r="G246" s="50">
+        <v>100300009</v>
+      </c>
+      <c r="H246" s="50" t="s">
+        <v>518</v>
+      </c>
+      <c r="I246" s="50"/>
+      <c r="J246" s="50" t="s">
+        <v>519</v>
+      </c>
+      <c r="K246" s="50">
+        <v>100300009</v>
+      </c>
+      <c r="L246" s="50">
+        <v>900000022</v>
+      </c>
+      <c r="M246" s="50" t="s">
+        <v>520</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M247"/>
+  <dimension ref="A1:M253"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="J10" s="50" t="inlineStr">
         <is>
-          <t>1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,11000,12000,</t>
+          <t>500,1000,2000,3000,4000,5000,6000,7000,8000,9000,10000,12000,</t>
         </is>
       </c>
       <c r="K10" s="50" t="n">
@@ -2280,41 +2280,41 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="50" t="n">
         <v>100200011</v>
       </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="50" t="inlineStr">
         <is>
           <t>ui_research_7</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="D23" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="50" t="n">
         <v>-300</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="50" t="n">
         <v>-700</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="50" t="n">
         <v>100200011</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="50" t="inlineStr">
         <is>
           <t>100200004,100300007</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="50" t="n">
         <v>1000</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="50" t="n">
         <v>100200011</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="50" t="inlineStr">
         <is>
           <t>挑战100勇士通关获得声望(前置=征服通关获得声望100200004 + 是魔王就挑战100勇士出现概率研究100300007)</t>
         </is>
@@ -2676,7 +2676,7 @@
         <v>-480</v>
       </c>
       <c r="F31" s="50" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="G31" s="50" t="n">
         <v>100310103</v>
@@ -2718,7 +2718,7 @@
         <v>-480</v>
       </c>
       <c r="F32" s="50" t="n">
-        <v>320</v>
+        <v>640</v>
       </c>
       <c r="G32" s="50" t="n">
         <v>100310104</v>
@@ -2760,7 +2760,7 @@
         <v>-480</v>
       </c>
       <c r="F33" s="50" t="n">
-        <v>480</v>
+        <v>960</v>
       </c>
       <c r="G33" s="50" t="n">
         <v>100310105</v>
@@ -2802,7 +2802,7 @@
         <v>-480</v>
       </c>
       <c r="F34" s="50" t="n">
-        <v>640</v>
+        <v>1280</v>
       </c>
       <c r="G34" s="50" t="n">
         <v>100310106</v>
@@ -2844,7 +2844,7 @@
         <v>-480</v>
       </c>
       <c r="F35" s="50" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="G35" s="50" t="n">
         <v>100310107</v>
@@ -2886,7 +2886,7 @@
         <v>-480</v>
       </c>
       <c r="F36" s="50" t="n">
-        <v>960</v>
+        <v>1920</v>
       </c>
       <c r="G36" s="50" t="n">
         <v>100310108</v>
@@ -2928,7 +2928,7 @@
         <v>-480</v>
       </c>
       <c r="F37" s="50" t="n">
-        <v>1120</v>
+        <v>2240</v>
       </c>
       <c r="G37" s="50" t="n">
         <v>100310109</v>
@@ -2970,7 +2970,7 @@
         <v>-480</v>
       </c>
       <c r="F38" s="50" t="n">
-        <v>1280</v>
+        <v>2560</v>
       </c>
       <c r="G38" s="50" t="n">
         <v>100310110</v>
@@ -3008,15 +3008,11 @@
       <c r="D39" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
-      </c>
-      <c r="F39" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E39" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F39" s="50" t="n">
+        <v>0</v>
       </c>
       <c r="G39" s="50" t="n">
         <v>100310112</v>
@@ -3051,15 +3047,11 @@
       <c r="D40" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
-      </c>
-      <c r="F40" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="E40" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F40" s="50" t="n">
+        <v>320</v>
       </c>
       <c r="G40" s="50" t="n">
         <v>100310113</v>
@@ -3098,15 +3090,11 @@
       <c r="D41" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
-      </c>
-      <c r="F41" s="50" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="E41" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F41" s="50" t="n">
+        <v>640</v>
       </c>
       <c r="G41" s="50" t="n">
         <v>100310114</v>
@@ -3145,15 +3133,11 @@
       <c r="D42" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
-      </c>
-      <c r="F42" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
+      <c r="E42" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F42" s="50" t="n">
+        <v>960</v>
       </c>
       <c r="G42" s="50" t="n">
         <v>100310115</v>
@@ -3192,15 +3176,11 @@
       <c r="D43" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E43" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
-      </c>
-      <c r="F43" s="50" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
+      <c r="E43" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F43" s="50" t="n">
+        <v>1280</v>
       </c>
       <c r="G43" s="50" t="n">
         <v>100310116</v>
@@ -3239,15 +3219,11 @@
       <c r="D44" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
-      </c>
-      <c r="F44" s="50" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="E44" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F44" s="50" t="n">
+        <v>1600</v>
       </c>
       <c r="G44" s="50" t="n">
         <v>100310117</v>
@@ -3286,15 +3262,11 @@
       <c r="D45" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E45" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
-      </c>
-      <c r="F45" s="50" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
+      <c r="E45" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F45" s="50" t="n">
+        <v>1920</v>
       </c>
       <c r="G45" s="50" t="n">
         <v>100310118</v>
@@ -3333,15 +3305,11 @@
       <c r="D46" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="50" t="inlineStr">
-        <is>
-          <t>-158</t>
-        </is>
-      </c>
-      <c r="F46" s="50" t="inlineStr">
-        <is>
-          <t>1118</t>
-        </is>
+      <c r="E46" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F46" s="50" t="n">
+        <v>2240</v>
       </c>
       <c r="G46" s="50" t="n">
         <v>100310119</v>
@@ -3380,15 +3348,11 @@
       <c r="D47" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
-      </c>
-      <c r="F47" s="50" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
+      <c r="E47" s="50" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F47" s="50" t="n">
+        <v>2560</v>
       </c>
       <c r="G47" s="50" t="n">
         <v>100310120</v>
@@ -3427,15 +3391,11 @@
       <c r="D48" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F48" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
+      <c r="E48" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F48" s="50" t="n">
+        <v>-320</v>
       </c>
       <c r="G48" s="50" t="n">
         <v>100310130</v>
@@ -3446,10 +3406,8 @@
           <t>World1ConquerCompleteCount1:1</t>
         </is>
       </c>
-      <c r="J48" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J48" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="K48" s="50" t="n">
         <v>100310130</v>
@@ -3475,15 +3433,11 @@
       <c r="D49" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F49" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E49" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F49" s="50" t="n">
+        <v>0</v>
       </c>
       <c r="G49" s="50" t="n">
         <v>100310131</v>
@@ -3498,10 +3452,8 @@
           <t>World1ConquerCompleteCount2:1</t>
         </is>
       </c>
-      <c r="J49" s="50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="J49" s="50" t="n">
+        <v>200</v>
       </c>
       <c r="K49" s="50" t="n">
         <v>100310131</v>
@@ -3527,15 +3479,11 @@
       <c r="D50" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F50" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="E50" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F50" s="50" t="n">
+        <v>320</v>
       </c>
       <c r="G50" s="50" t="n">
         <v>100310132</v>
@@ -3550,10 +3498,8 @@
           <t>World1ConquerCompleteCount3:1</t>
         </is>
       </c>
-      <c r="J50" s="50" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="J50" s="50" t="n">
+        <v>1000</v>
       </c>
       <c r="K50" s="50" t="n">
         <v>100310132</v>
@@ -3579,15 +3525,11 @@
       <c r="D51" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E51" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F51" s="50" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="E51" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F51" s="50" t="n">
+        <v>640</v>
       </c>
       <c r="G51" s="50" t="n">
         <v>100310133</v>
@@ -3602,10 +3544,8 @@
           <t>World1ConquerCompleteCount4:1</t>
         </is>
       </c>
-      <c r="J51" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J51" s="50" t="n">
+        <v>2000</v>
       </c>
       <c r="K51" s="50" t="n">
         <v>100310133</v>
@@ -3631,15 +3571,11 @@
       <c r="D52" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E52" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F52" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
+      <c r="E52" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F52" s="50" t="n">
+        <v>960</v>
       </c>
       <c r="G52" s="50" t="n">
         <v>100310134</v>
@@ -3654,10 +3590,8 @@
           <t>World1ConquerCompleteCount5:1</t>
         </is>
       </c>
-      <c r="J52" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J52" s="50" t="n">
+        <v>4000</v>
       </c>
       <c r="K52" s="50" t="n">
         <v>100310134</v>
@@ -3683,15 +3617,11 @@
       <c r="D53" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E53" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F53" s="50" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
+      <c r="E53" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F53" s="50" t="n">
+        <v>1280</v>
       </c>
       <c r="G53" s="50" t="n">
         <v>100310135</v>
@@ -3706,10 +3636,8 @@
           <t>World1ConquerCompleteCount6:1</t>
         </is>
       </c>
-      <c r="J53" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J53" s="50" t="n">
+        <v>8000</v>
       </c>
       <c r="K53" s="50" t="n">
         <v>100310135</v>
@@ -3735,15 +3663,11 @@
       <c r="D54" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E54" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F54" s="50" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="E54" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F54" s="50" t="n">
+        <v>1600</v>
       </c>
       <c r="G54" s="50" t="n">
         <v>100310136</v>
@@ -3758,10 +3682,8 @@
           <t>World1ConquerCompleteCount7:1</t>
         </is>
       </c>
-      <c r="J54" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J54" s="50" t="n">
+        <v>16000</v>
       </c>
       <c r="K54" s="50" t="n">
         <v>100310136</v>
@@ -3787,15 +3709,11 @@
       <c r="D55" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F55" s="50" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
+      <c r="E55" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F55" s="50" t="n">
+        <v>1920</v>
       </c>
       <c r="G55" s="50" t="n">
         <v>100310137</v>
@@ -3810,10 +3728,8 @@
           <t>World1ConquerCompleteCount8:1</t>
         </is>
       </c>
-      <c r="J55" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J55" s="50" t="n">
+        <v>32000</v>
       </c>
       <c r="K55" s="50" t="n">
         <v>100310137</v>
@@ -3839,15 +3755,11 @@
       <c r="D56" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F56" s="50" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
+      <c r="E56" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F56" s="50" t="n">
+        <v>2240</v>
       </c>
       <c r="G56" s="50" t="n">
         <v>100310138</v>
@@ -3862,10 +3774,8 @@
           <t>World1ConquerCompleteCount9:1</t>
         </is>
       </c>
-      <c r="J56" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J56" s="50" t="n">
+        <v>64000</v>
       </c>
       <c r="K56" s="50" t="n">
         <v>100310138</v>
@@ -3891,15 +3801,11 @@
       <c r="D57" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F57" s="50" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
+      <c r="E57" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F57" s="50" t="n">
+        <v>2560</v>
       </c>
       <c r="G57" s="50" t="n">
         <v>100310139</v>
@@ -3914,10 +3820,8 @@
           <t>World1ConquerCompleteCount10:1</t>
         </is>
       </c>
-      <c r="J57" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J57" s="50" t="n">
+        <v>128000</v>
       </c>
       <c r="K57" s="50" t="n">
         <v>100310139</v>
@@ -3943,15 +3847,11 @@
       <c r="D58" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F58" s="50" t="inlineStr">
-        <is>
-          <t>-160</t>
-        </is>
+      <c r="E58" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F58" s="50" t="n">
+        <v>-320</v>
       </c>
       <c r="G58" s="50" t="n">
         <v>100310140</v>
@@ -3961,10 +3861,8 @@
           <t>100310130</t>
         </is>
       </c>
-      <c r="J58" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J58" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="K58" s="50" t="n">
         <v>100310140</v>
@@ -3990,15 +3888,11 @@
       <c r="D59" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F59" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E59" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F59" s="50" t="n">
+        <v>0</v>
       </c>
       <c r="G59" s="50" t="n">
         <v>100310141</v>
@@ -4008,10 +3902,8 @@
           <t>100310131</t>
         </is>
       </c>
-      <c r="J59" s="50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="J59" s="50" t="n">
+        <v>200</v>
       </c>
       <c r="K59" s="50" t="n">
         <v>100310141</v>
@@ -4037,15 +3929,11 @@
       <c r="D60" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F60" s="50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="E60" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F60" s="50" t="n">
+        <v>320</v>
       </c>
       <c r="G60" s="50" t="n">
         <v>100310142</v>
@@ -4055,10 +3943,8 @@
           <t>100310132</t>
         </is>
       </c>
-      <c r="J60" s="50" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="J60" s="50" t="n">
+        <v>1000</v>
       </c>
       <c r="K60" s="50" t="n">
         <v>100310142</v>
@@ -4084,15 +3970,11 @@
       <c r="D61" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F61" s="50" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="E61" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F61" s="50" t="n">
+        <v>640</v>
       </c>
       <c r="G61" s="50" t="n">
         <v>100310143</v>
@@ -4102,10 +3984,8 @@
           <t>100310133</t>
         </is>
       </c>
-      <c r="J61" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J61" s="50" t="n">
+        <v>2000</v>
       </c>
       <c r="K61" s="50" t="n">
         <v>100310143</v>
@@ -4131,15 +4011,11 @@
       <c r="D62" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F62" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
+      <c r="E62" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F62" s="50" t="n">
+        <v>960</v>
       </c>
       <c r="G62" s="50" t="n">
         <v>100310144</v>
@@ -4149,10 +4025,8 @@
           <t>100310134</t>
         </is>
       </c>
-      <c r="J62" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J62" s="50" t="n">
+        <v>4000</v>
       </c>
       <c r="K62" s="50" t="n">
         <v>100310144</v>
@@ -4178,15 +4052,11 @@
       <c r="D63" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F63" s="50" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
+      <c r="E63" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F63" s="50" t="n">
+        <v>1280</v>
       </c>
       <c r="G63" s="50" t="n">
         <v>100310145</v>
@@ -4196,10 +4066,8 @@
           <t>100310135</t>
         </is>
       </c>
-      <c r="J63" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J63" s="50" t="n">
+        <v>8000</v>
       </c>
       <c r="K63" s="50" t="n">
         <v>100310145</v>
@@ -4225,15 +4093,11 @@
       <c r="D64" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E64" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F64" s="50" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="E64" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F64" s="50" t="n">
+        <v>1600</v>
       </c>
       <c r="G64" s="50" t="n">
         <v>100310146</v>
@@ -4243,10 +4107,8 @@
           <t>100310136</t>
         </is>
       </c>
-      <c r="J64" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J64" s="50" t="n">
+        <v>16000</v>
       </c>
       <c r="K64" s="50" t="n">
         <v>100310146</v>
@@ -4272,15 +4134,11 @@
       <c r="D65" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F65" s="50" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
+      <c r="E65" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F65" s="50" t="n">
+        <v>1920</v>
       </c>
       <c r="G65" s="50" t="n">
         <v>100310147</v>
@@ -4290,10 +4148,8 @@
           <t>100310137</t>
         </is>
       </c>
-      <c r="J65" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J65" s="50" t="n">
+        <v>32000</v>
       </c>
       <c r="K65" s="50" t="n">
         <v>100310147</v>
@@ -4319,15 +4175,11 @@
       <c r="D66" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E66" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F66" s="50" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
+      <c r="E66" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F66" s="50" t="n">
+        <v>2240</v>
       </c>
       <c r="G66" s="50" t="n">
         <v>100310148</v>
@@ -4337,10 +4189,8 @@
           <t>100310138</t>
         </is>
       </c>
-      <c r="J66" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J66" s="50" t="n">
+        <v>64000</v>
       </c>
       <c r="K66" s="50" t="n">
         <v>100310148</v>
@@ -4366,15 +4216,11 @@
       <c r="D67" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="50" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="F67" s="50" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
+      <c r="E67" s="50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F67" s="50" t="n">
+        <v>2560</v>
       </c>
       <c r="G67" s="50" t="n">
         <v>100310149</v>
@@ -4384,10 +4230,8 @@
           <t>100310139</t>
         </is>
       </c>
-      <c r="J67" s="50" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J67" s="50" t="n">
+        <v>128000</v>
       </c>
       <c r="K67" s="50" t="n">
         <v>100310149</v>
@@ -4836,7 +4680,7 @@
       </c>
       <c r="F77" s="50" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G77" s="50" t="n">
@@ -4849,7 +4693,7 @@
       </c>
       <c r="J77" s="50" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="K77" s="50" t="n">
@@ -4878,12 +4722,12 @@
       </c>
       <c r="E78" s="50" t="inlineStr">
         <is>
-          <t>-500</t>
+          <t>-700</t>
         </is>
       </c>
       <c r="F78" s="50" t="inlineStr">
         <is>
-          <t>-156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G78" s="50" t="n">
@@ -5884,7 +5728,7 @@
         </is>
       </c>
       <c r="J99" s="50" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K99" s="50" t="n">
         <v>300110011</v>
@@ -5923,7 +5767,7 @@
         <v>300110011</v>
       </c>
       <c r="J100" s="50" t="n">
-        <v>500</v>
+        <v>1250</v>
       </c>
       <c r="K100" s="50" t="n">
         <v>300110012</v>
@@ -5962,7 +5806,7 @@
         <v>300110012</v>
       </c>
       <c r="J101" s="50" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="K101" s="50" t="n">
         <v>300110013</v>
@@ -6006,7 +5850,7 @@
         </is>
       </c>
       <c r="J102" s="50" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K102" s="50" t="n">
         <v>300110021</v>
@@ -6045,7 +5889,7 @@
         <v>300110021</v>
       </c>
       <c r="J103" s="50" t="n">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K103" s="50" t="n">
         <v>300110022</v>
@@ -6084,7 +5928,7 @@
         <v>300110022</v>
       </c>
       <c r="J104" s="50" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K104" s="50" t="n">
         <v>300110023</v>
@@ -6128,7 +5972,7 @@
         </is>
       </c>
       <c r="J105" s="50" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="K105" s="50" t="n">
         <v>300110031</v>
@@ -6167,7 +6011,7 @@
         <v>300110031</v>
       </c>
       <c r="J106" s="50" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="K106" s="50" t="n">
         <v>300110032</v>
@@ -6206,7 +6050,7 @@
         <v>300110032</v>
       </c>
       <c r="J107" s="50" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K107" s="50" t="n">
         <v>300110033</v>
@@ -6250,7 +6094,7 @@
         </is>
       </c>
       <c r="J108" s="50" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="K108" s="50" t="n">
         <v>300110041</v>
@@ -6289,7 +6133,7 @@
         <v>300110041</v>
       </c>
       <c r="J109" s="50" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="K109" s="50" t="n">
         <v>300110042</v>
@@ -6328,7 +6172,7 @@
         <v>300110042</v>
       </c>
       <c r="J110" s="50" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K110" s="50" t="n">
         <v>300110043</v>
@@ -6779,7 +6623,7 @@
         </is>
       </c>
       <c r="J120" s="50" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="K120" s="50" t="n">
         <v>300210011</v>
@@ -6818,7 +6662,7 @@
         <v>300210011</v>
       </c>
       <c r="J121" s="50" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="K121" s="50" t="n">
         <v>300210012</v>
@@ -6857,7 +6701,7 @@
         <v>300210012</v>
       </c>
       <c r="J122" s="50" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="K122" s="50" t="n">
         <v>300210013</v>
@@ -6901,7 +6745,7 @@
         </is>
       </c>
       <c r="J123" s="50" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="K123" s="50" t="n">
         <v>300210021</v>
@@ -6940,7 +6784,7 @@
         <v>300210021</v>
       </c>
       <c r="J124" s="50" t="n">
-        <v>500</v>
+        <v>125</v>
       </c>
       <c r="K124" s="50" t="n">
         <v>300210022</v>
@@ -6979,7 +6823,7 @@
         <v>300210022</v>
       </c>
       <c r="J125" s="50" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="K125" s="50" t="n">
         <v>300210023</v>
@@ -7023,7 +6867,7 @@
         </is>
       </c>
       <c r="J126" s="50" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K126" s="50" t="n">
         <v>300210031</v>
@@ -7062,7 +6906,7 @@
         <v>300210031</v>
       </c>
       <c r="J127" s="50" t="n">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K127" s="50" t="n">
         <v>300210032</v>
@@ -7102,7 +6946,7 @@
       </c>
       <c r="I128" s="50" t="n"/>
       <c r="J128" s="50" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K128" s="50" t="n">
         <v>300210033</v>
@@ -7146,7 +6990,7 @@
         </is>
       </c>
       <c r="J129" s="50" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K129" s="50" t="n">
         <v>300210041</v>
@@ -7186,7 +7030,7 @@
       </c>
       <c r="I130" s="50" t="n"/>
       <c r="J130" s="50" t="n">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K130" s="50" t="n">
         <v>300210042</v>
@@ -7226,7 +7070,7 @@
       </c>
       <c r="I131" s="50" t="n"/>
       <c r="J131" s="50" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="K131" s="50" t="n">
         <v>300210043</v>
@@ -7685,7 +7529,7 @@
         </is>
       </c>
       <c r="J141" s="50" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="K141" s="50" t="n">
         <v>300310011</v>
@@ -7724,7 +7568,7 @@
         <v>300310011</v>
       </c>
       <c r="J142" s="50" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="K142" s="50" t="n">
         <v>300310012</v>
@@ -7763,7 +7607,7 @@
         <v>300310012</v>
       </c>
       <c r="J143" s="50" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="K143" s="50" t="n">
         <v>300310013</v>
@@ -7807,7 +7651,7 @@
         </is>
       </c>
       <c r="J144" s="50" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="K144" s="50" t="n">
         <v>300310021</v>
@@ -7846,7 +7690,7 @@
         <v>300310021</v>
       </c>
       <c r="J145" s="50" t="n">
-        <v>5000</v>
+        <v>1250</v>
       </c>
       <c r="K145" s="50" t="n">
         <v>300310022</v>
@@ -7885,7 +7729,7 @@
         <v>300310022</v>
       </c>
       <c r="J146" s="50" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="K146" s="50" t="n">
         <v>300310023</v>
@@ -7929,7 +7773,7 @@
         </is>
       </c>
       <c r="J147" s="50" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="K147" s="50" t="n">
         <v>300310031</v>
@@ -7968,7 +7812,7 @@
         <v>300310031</v>
       </c>
       <c r="J148" s="50" t="n">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="K148" s="50" t="n">
         <v>300310032</v>
@@ -8007,7 +7851,7 @@
         <v>300310032</v>
       </c>
       <c r="J149" s="50" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K149" s="50" t="n">
         <v>300310033</v>
@@ -8051,7 +7895,7 @@
         </is>
       </c>
       <c r="J150" s="50" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K150" s="50" t="n">
         <v>300310041</v>
@@ -8171,8 +8015,10 @@
       <c r="H153" s="50" t="n">
         <v>300600000</v>
       </c>
-      <c r="J153" s="50" t="n">
-        <v>100</v>
+      <c r="J153" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K153" s="50" t="n">
         <v>300400000</v>
@@ -8205,7 +8051,7 @@
       </c>
       <c r="F154" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="G154" s="50" t="n">
@@ -8214,8 +8060,10 @@
       <c r="H154" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="J154" s="50" t="n">
-        <v>100</v>
+      <c r="J154" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="K154" s="50" t="n">
         <v>300400001</v>
@@ -8257,8 +8105,10 @@
       <c r="H155" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="J155" s="50" t="n">
-        <v>100</v>
+      <c r="J155" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K155" s="50" t="n">
         <v>300400002</v>
@@ -8300,8 +8150,10 @@
       <c r="H156" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="J156" s="50" t="n">
-        <v>100</v>
+      <c r="J156" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K156" s="50" t="n">
         <v>300400003</v>
@@ -8343,8 +8195,10 @@
       <c r="H157" s="50" t="n">
         <v>300400000</v>
       </c>
-      <c r="J157" s="50" t="n">
-        <v>100</v>
+      <c r="J157" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K157" s="50" t="n">
         <v>300400004</v>
@@ -8357,14 +8211,14 @@
     </row>
     <row r="158">
       <c r="A158" s="50" t="n">
-        <v>300400005</v>
+        <v>300400101</v>
       </c>
       <c r="B158" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C158" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D158" s="50" t="n">
@@ -8372,87 +8226,91 @@
       </c>
       <c r="E158" s="50" t="inlineStr">
         <is>
-          <t>-2100</t>
+          <t>-2399</t>
         </is>
       </c>
       <c r="F158" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G158" s="50" t="n">
-        <v>300400005</v>
-      </c>
-      <c r="H158" s="50" t="n">
-        <v>300400000</v>
-      </c>
-      <c r="J158" s="50" t="n">
-        <v>100</v>
+        <v>300400101</v>
+      </c>
+      <c r="H158" s="50" t="inlineStr">
+        <is>
+          <t>300400001|300400002|300400003|300400004|</t>
+        </is>
+      </c>
+      <c r="J158" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K158" s="50" t="n">
-        <v>300400005</v>
+        <v>300400101</v>
       </c>
       <c r="M158" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="50" t="n">
+        <v>300400102</v>
+      </c>
+      <c r="B159" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C159" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_34</t>
+        </is>
+      </c>
+      <c r="D159" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" s="50" t="inlineStr">
+        <is>
+          <t>-2400</t>
+        </is>
+      </c>
+      <c r="F159" s="50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="G159" s="50" t="n">
+        <v>300400102</v>
+      </c>
+      <c r="H159" s="50" t="n">
         <v>300400101</v>
       </c>
-      <c r="B159" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="C159" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_33</t>
-        </is>
-      </c>
-      <c r="D159" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" s="50" t="inlineStr">
-        <is>
-          <t>-2400</t>
-        </is>
-      </c>
-      <c r="F159" s="50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="G159" s="50" t="n">
-        <v>300400101</v>
-      </c>
-      <c r="H159" s="50" t="inlineStr">
-        <is>
-          <t>300400001|300400002|300400003|300400004|300400005|</t>
-        </is>
-      </c>
-      <c r="J159" s="50" t="n">
-        <v>100</v>
+      <c r="J159" s="50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="K159" s="50" t="n">
-        <v>300400101</v>
+        <v>300400102</v>
       </c>
       <c r="M159" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="50" t="n">
-        <v>300400102</v>
+        <v>300400201</v>
       </c>
       <c r="B160" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C160" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_41</t>
         </is>
       </c>
       <c r="D160" s="50" t="n">
@@ -8460,42 +8318,46 @@
       </c>
       <c r="E160" s="50" t="inlineStr">
         <is>
-          <t>-2400</t>
+          <t>-2250</t>
         </is>
       </c>
       <c r="F160" s="50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G160" s="50" t="n">
-        <v>300400102</v>
-      </c>
-      <c r="H160" s="50" t="n">
-        <v>300400101</v>
-      </c>
-      <c r="J160" s="50" t="n">
-        <v>100</v>
+        <v>300400201</v>
+      </c>
+      <c r="H160" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300400000,</t>
+        </is>
+      </c>
+      <c r="J160" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K160" s="50" t="n">
-        <v>300400102</v>
+        <v>300400201</v>
       </c>
       <c r="M160" s="50" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="50" t="n">
-        <v>300400201</v>
+        <v>300400301</v>
       </c>
       <c r="B161" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C161" s="50" t="inlineStr">
         <is>
-          <t>ui_research_41</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D161" s="50" t="n">
@@ -8503,7 +8365,7 @@
       </c>
       <c r="E161" s="50" t="inlineStr">
         <is>
-          <t>-2250</t>
+          <t>-2400</t>
         </is>
       </c>
       <c r="F161" s="50" t="inlineStr">
@@ -8512,73 +8374,74 @@
         </is>
       </c>
       <c r="G161" s="50" t="n">
-        <v>300400201</v>
+        <v>300400301</v>
       </c>
       <c r="H161" s="50" t="inlineStr">
         <is>
-          <t>100200001,300400000,</t>
-        </is>
-      </c>
-      <c r="J161" s="50" t="n">
-        <v>100</v>
+          <t>300400000,</t>
+        </is>
+      </c>
+      <c r="J161" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K161" s="50" t="n">
-        <v>300400201</v>
+        <v>300400301</v>
       </c>
       <c r="M161" s="50" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="50" t="n">
-        <v>300400301</v>
+        <v>300410011</v>
       </c>
       <c r="B162" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C162" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D162" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E162" s="50" t="inlineStr">
-        <is>
-          <t>-2400</t>
-        </is>
-      </c>
-      <c r="F162" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
+      <c r="E162" s="50" t="n">
+        <v>-2720</v>
+      </c>
+      <c r="F162" s="50" t="n">
+        <v>760</v>
       </c>
       <c r="G162" s="50" t="n">
-        <v>300400301</v>
-      </c>
-      <c r="H162" s="50" t="inlineStr">
-        <is>
-          <t>300400000,</t>
+        <v>300410011</v>
+      </c>
+      <c r="H162" s="50" t="n">
+        <v>300400102</v>
+      </c>
+      <c r="I162" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount4001:99</t>
         </is>
       </c>
       <c r="J162" s="50" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K162" s="50" t="n">
-        <v>300400301</v>
+        <v>300410011</v>
       </c>
       <c r="M162" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>孕育战之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="50" t="n">
-        <v>300410011</v>
+        <v>300410012</v>
       </c>
       <c r="B163" s="50" t="n">
         <v>3</v>
@@ -8595,34 +8458,29 @@
         <v>-2720</v>
       </c>
       <c r="F163" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G163" s="50" t="n">
+        <v>300410012</v>
+      </c>
+      <c r="H163" s="50" t="n">
         <v>300410011</v>
       </c>
-      <c r="H163" s="50" t="n">
-        <v>300400102</v>
-      </c>
-      <c r="I163" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount4001:99</t>
-        </is>
-      </c>
       <c r="J163" s="50" t="n">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="K163" s="50" t="n">
-        <v>300410011</v>
+        <v>300410012</v>
       </c>
       <c r="M163" s="50" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x1</t>
+          <t>孕育战之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="50" t="n">
-        <v>300410012</v>
+        <v>300410013</v>
       </c>
       <c r="B164" s="50" t="n">
         <v>3</v>
@@ -8639,68 +8497,73 @@
         <v>-2720</v>
       </c>
       <c r="F164" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G164" s="50" t="n">
+        <v>300410013</v>
+      </c>
+      <c r="H164" s="50" t="n">
         <v>300410012</v>
       </c>
-      <c r="H164" s="50" t="n">
-        <v>300410011</v>
-      </c>
       <c r="J164" s="50" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="K164" s="50" t="n">
-        <v>300410012</v>
+        <v>300410013</v>
       </c>
       <c r="M164" s="50" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x5</t>
+          <t>孕育战之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="50" t="n">
-        <v>300410013</v>
+        <v>300410021</v>
       </c>
       <c r="B165" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C165" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_45</t>
         </is>
       </c>
       <c r="D165" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E165" s="50" t="n">
-        <v>-2720</v>
+        <v>-2560</v>
       </c>
       <c r="F165" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G165" s="50" t="n">
-        <v>300410013</v>
+        <v>300410021</v>
       </c>
       <c r="H165" s="50" t="n">
-        <v>300410012</v>
+        <v>300400102</v>
+      </c>
+      <c r="I165" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount4002:99</t>
+        </is>
       </c>
       <c r="J165" s="50" t="n">
         <v>1000</v>
       </c>
       <c r="K165" s="50" t="n">
-        <v>300410013</v>
+        <v>300410021</v>
       </c>
       <c r="M165" s="50" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x10</t>
+          <t>孕育愈之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="50" t="n">
-        <v>300410021</v>
+        <v>300410022</v>
       </c>
       <c r="B166" s="50" t="n">
         <v>3</v>
@@ -8717,34 +8580,29 @@
         <v>-2560</v>
       </c>
       <c r="F166" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G166" s="50" t="n">
+        <v>300410022</v>
+      </c>
+      <c r="H166" s="50" t="n">
         <v>300410021</v>
       </c>
-      <c r="H166" s="50" t="n">
-        <v>300400102</v>
-      </c>
-      <c r="I166" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount4002:99</t>
-        </is>
-      </c>
       <c r="J166" s="50" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="K166" s="50" t="n">
-        <v>300410021</v>
+        <v>300410022</v>
       </c>
       <c r="M166" s="50" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x1</t>
+          <t>孕育愈之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="50" t="n">
-        <v>300410022</v>
+        <v>300410023</v>
       </c>
       <c r="B167" s="50" t="n">
         <v>3</v>
@@ -8761,68 +8619,73 @@
         <v>-2560</v>
       </c>
       <c r="F167" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G167" s="50" t="n">
+        <v>300410023</v>
+      </c>
+      <c r="H167" s="50" t="n">
         <v>300410022</v>
       </c>
-      <c r="H167" s="50" t="n">
-        <v>300410021</v>
-      </c>
       <c r="J167" s="50" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="K167" s="50" t="n">
-        <v>300410022</v>
+        <v>300410023</v>
       </c>
       <c r="M167" s="50" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x5</t>
+          <t>孕育愈之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="50" t="n">
-        <v>300410023</v>
+        <v>300410031</v>
       </c>
       <c r="B168" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C168" s="50" t="inlineStr">
         <is>
-          <t>ui_research_45</t>
+          <t>ui_research_52</t>
         </is>
       </c>
       <c r="D168" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E168" s="50" t="n">
-        <v>-2560</v>
+        <v>-2400</v>
       </c>
       <c r="F168" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G168" s="50" t="n">
-        <v>300410023</v>
+        <v>300410031</v>
       </c>
       <c r="H168" s="50" t="n">
-        <v>300410022</v>
+        <v>300400102</v>
+      </c>
+      <c r="I168" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount4003:99</t>
+        </is>
       </c>
       <c r="J168" s="50" t="n">
         <v>1000</v>
       </c>
       <c r="K168" s="50" t="n">
-        <v>300410023</v>
+        <v>300410031</v>
       </c>
       <c r="M168" s="50" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x10</t>
+          <t>孕育惑之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="50" t="n">
-        <v>300410031</v>
+        <v>300410032</v>
       </c>
       <c r="B169" s="50" t="n">
         <v>3</v>
@@ -8839,34 +8702,29 @@
         <v>-2400</v>
       </c>
       <c r="F169" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G169" s="50" t="n">
+        <v>300410032</v>
+      </c>
+      <c r="H169" s="50" t="n">
         <v>300410031</v>
       </c>
-      <c r="H169" s="50" t="n">
-        <v>300400102</v>
-      </c>
-      <c r="I169" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount4003:99</t>
-        </is>
-      </c>
       <c r="J169" s="50" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="K169" s="50" t="n">
-        <v>300410031</v>
+        <v>300410032</v>
       </c>
       <c r="M169" s="50" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x1</t>
+          <t>孕育惑之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="50" t="n">
-        <v>300410032</v>
+        <v>300410033</v>
       </c>
       <c r="B170" s="50" t="n">
         <v>3</v>
@@ -8883,68 +8741,73 @@
         <v>-2400</v>
       </c>
       <c r="F170" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G170" s="50" t="n">
+        <v>300410033</v>
+      </c>
+      <c r="H170" s="50" t="n">
         <v>300410032</v>
       </c>
-      <c r="H170" s="50" t="n">
-        <v>300410031</v>
-      </c>
       <c r="J170" s="50" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="K170" s="50" t="n">
-        <v>300410032</v>
+        <v>300410033</v>
       </c>
       <c r="M170" s="50" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x5</t>
+          <t>孕育惑之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="50" t="n">
-        <v>300410033</v>
+        <v>300410041</v>
       </c>
       <c r="B171" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C171" s="50" t="inlineStr">
         <is>
-          <t>ui_research_52</t>
+          <t>ui_research_49</t>
         </is>
       </c>
       <c r="D171" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E171" s="50" t="n">
-        <v>-2400</v>
+        <v>-2240</v>
       </c>
       <c r="F171" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G171" s="50" t="n">
-        <v>300410033</v>
+        <v>300410041</v>
       </c>
       <c r="H171" s="50" t="n">
-        <v>300410032</v>
+        <v>300400102</v>
+      </c>
+      <c r="I171" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount4004:99</t>
+        </is>
       </c>
       <c r="J171" s="50" t="n">
         <v>1000</v>
       </c>
       <c r="K171" s="50" t="n">
-        <v>300410033</v>
+        <v>300410041</v>
       </c>
       <c r="M171" s="50" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x10</t>
+          <t>孕育奥之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="50" t="n">
-        <v>300410041</v>
+        <v>300410042</v>
       </c>
       <c r="B172" s="50" t="n">
         <v>3</v>
@@ -8961,34 +8824,29 @@
         <v>-2240</v>
       </c>
       <c r="F172" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G172" s="50" t="n">
+        <v>300410042</v>
+      </c>
+      <c r="H172" s="50" t="n">
         <v>300410041</v>
       </c>
-      <c r="H172" s="50" t="n">
-        <v>300400102</v>
-      </c>
-      <c r="I172" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount4004:99</t>
-        </is>
-      </c>
       <c r="J172" s="50" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="K172" s="50" t="n">
-        <v>300410041</v>
+        <v>300410042</v>
       </c>
       <c r="M172" s="50" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x1</t>
+          <t>孕育奥之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="50" t="n">
-        <v>300410042</v>
+        <v>300410043</v>
       </c>
       <c r="B173" s="50" t="n">
         <v>3</v>
@@ -9005,240 +8863,261 @@
         <v>-2240</v>
       </c>
       <c r="F173" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G173" s="50" t="n">
+        <v>300410043</v>
+      </c>
+      <c r="H173" s="50" t="n">
         <v>300410042</v>
       </c>
-      <c r="H173" s="50" t="n">
-        <v>300410041</v>
-      </c>
       <c r="J173" s="50" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="K173" s="50" t="n">
-        <v>300410042</v>
+        <v>300410043</v>
       </c>
       <c r="M173" s="50" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x5</t>
+          <t>孕育奥之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="50" t="n">
-        <v>300410043</v>
+        <v>300500000</v>
       </c>
       <c r="B174" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C174" s="50" t="inlineStr">
         <is>
-          <t>ui_research_49</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D174" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E174" s="50" t="n">
-        <v>-2240</v>
-      </c>
-      <c r="F174" s="50" t="n">
-        <v>1080</v>
+      <c r="E174" s="50" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="F174" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G174" s="50" t="n">
-        <v>300410043</v>
+        <v>300500000</v>
       </c>
       <c r="H174" s="50" t="n">
-        <v>300410042</v>
-      </c>
-      <c r="J174" s="50" t="n">
-        <v>1000</v>
+        <v>300700000</v>
+      </c>
+      <c r="J174" s="50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="K174" s="50" t="n">
-        <v>300410043</v>
+        <v>300500000</v>
       </c>
       <c r="M174" s="50" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x10</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="50" t="n">
-        <v>300410051</v>
+        <v>300500001</v>
       </c>
       <c r="B175" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C175" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D175" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E175" s="50" t="n">
-        <v>-2080</v>
-      </c>
-      <c r="F175" s="50" t="n">
-        <v>760</v>
+      <c r="E175" s="50" t="inlineStr">
+        <is>
+          <t>2175</t>
+        </is>
+      </c>
+      <c r="F175" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G175" s="50" t="n">
-        <v>300410051</v>
+        <v>300500001</v>
       </c>
       <c r="H175" s="50" t="n">
-        <v>300400102</v>
-      </c>
-      <c r="I175" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount4005:99</t>
-        </is>
-      </c>
-      <c r="J175" s="50" t="n">
-        <v>200</v>
+        <v>300500000</v>
+      </c>
+      <c r="J175" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K175" s="50" t="n">
-        <v>300410051</v>
+        <v>300500001</v>
       </c>
       <c r="M175" s="50" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x1</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="50" t="n">
-        <v>300410052</v>
+        <v>300500002</v>
       </c>
       <c r="B176" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C176" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D176" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E176" s="50" t="n">
-        <v>-2080</v>
-      </c>
-      <c r="F176" s="50" t="n">
-        <v>920</v>
+      <c r="E176" s="50" t="inlineStr">
+        <is>
+          <t>2325</t>
+        </is>
+      </c>
+      <c r="F176" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G176" s="50" t="n">
-        <v>300410052</v>
+        <v>300500002</v>
       </c>
       <c r="H176" s="50" t="n">
-        <v>300410051</v>
-      </c>
-      <c r="J176" s="50" t="n">
-        <v>500</v>
+        <v>300500000</v>
+      </c>
+      <c r="J176" s="50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="K176" s="50" t="n">
-        <v>300410052</v>
+        <v>300500002</v>
       </c>
       <c r="M176" s="50" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x5</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="50" t="n">
-        <v>300410053</v>
+        <v>300500003</v>
       </c>
       <c r="B177" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C177" s="50" t="inlineStr">
         <is>
-          <t>ui_research_51</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D177" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E177" s="50" t="n">
-        <v>-2080</v>
-      </c>
-      <c r="F177" s="50" t="n">
-        <v>1080</v>
+      <c r="E177" s="50" t="inlineStr">
+        <is>
+          <t>2475</t>
+        </is>
+      </c>
+      <c r="F177" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G177" s="50" t="n">
-        <v>300410053</v>
+        <v>300500003</v>
       </c>
       <c r="H177" s="50" t="n">
-        <v>300410052</v>
-      </c>
-      <c r="J177" s="50" t="n">
-        <v>1000</v>
+        <v>300500000</v>
+      </c>
+      <c r="J177" s="50" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
       </c>
       <c r="K177" s="50" t="n">
-        <v>300410053</v>
+        <v>300500003</v>
       </c>
       <c r="M177" s="50" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x10</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="50" t="n">
+        <v>300500004</v>
+      </c>
+      <c r="B178" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C178" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_47</t>
+        </is>
+      </c>
+      <c r="D178" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" s="50" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="F178" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G178" s="50" t="n">
+        <v>300500004</v>
+      </c>
+      <c r="H178" s="50" t="n">
         <v>300500000</v>
       </c>
-      <c r="B178" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="C178" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_40</t>
-        </is>
-      </c>
-      <c r="D178" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" s="50" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="F178" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G178" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="H178" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="J178" s="50" t="n">
-        <v>100</v>
+      <c r="J178" s="50" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
       </c>
       <c r="K178" s="50" t="n">
-        <v>300500000</v>
+        <v>300500004</v>
       </c>
       <c r="M178" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="50" t="n">
-        <v>300500001</v>
+        <v>300500101</v>
       </c>
       <c r="B179" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C179" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D179" s="50" t="n">
@@ -9246,42 +9125,46 @@
       </c>
       <c r="E179" s="50" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F179" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G179" s="50" t="n">
-        <v>300500001</v>
-      </c>
-      <c r="H179" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="J179" s="50" t="n">
-        <v>100</v>
+        <v>300500101</v>
+      </c>
+      <c r="H179" s="50" t="inlineStr">
+        <is>
+          <t>300500001|300500002|300500003|300500004|</t>
+        </is>
+      </c>
+      <c r="J179" s="50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="K179" s="50" t="n">
-        <v>300500001</v>
+        <v>300500101</v>
       </c>
       <c r="M179" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="50" t="n">
-        <v>300500002</v>
+        <v>300500102</v>
       </c>
       <c r="B180" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C180" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D180" s="50" t="n">
@@ -9289,42 +9172,44 @@
       </c>
       <c r="E180" s="50" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F180" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G180" s="50" t="n">
-        <v>300500002</v>
+        <v>300500102</v>
       </c>
       <c r="H180" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="J180" s="50" t="n">
-        <v>100</v>
+        <v>300500101</v>
+      </c>
+      <c r="J180" s="50" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
       </c>
       <c r="K180" s="50" t="n">
-        <v>300500002</v>
+        <v>300500102</v>
       </c>
       <c r="M180" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="50" t="n">
-        <v>300500003</v>
+        <v>300500201</v>
       </c>
       <c r="B181" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C181" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_40</t>
         </is>
       </c>
       <c r="D181" s="50" t="n">
@@ -9332,42 +9217,46 @@
       </c>
       <c r="E181" s="50" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="F181" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G181" s="50" t="n">
-        <v>300500003</v>
-      </c>
-      <c r="H181" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="J181" s="50" t="n">
-        <v>100</v>
+        <v>300500201</v>
+      </c>
+      <c r="H181" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300500000,</t>
+        </is>
+      </c>
+      <c r="J181" s="50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="K181" s="50" t="n">
-        <v>300500003</v>
+        <v>300500201</v>
       </c>
       <c r="M181" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="50" t="n">
-        <v>300500004</v>
+        <v>300500301</v>
       </c>
       <c r="B182" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C182" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D182" s="50" t="n">
@@ -9375,753 +9264,759 @@
       </c>
       <c r="E182" s="50" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F182" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G182" s="50" t="n">
-        <v>300500004</v>
-      </c>
-      <c r="H182" s="50" t="n">
-        <v>300500000</v>
-      </c>
-      <c r="J182" s="50" t="n">
-        <v>100</v>
+        <v>300500301</v>
+      </c>
+      <c r="H182" s="50" t="inlineStr">
+        <is>
+          <t>300500000,</t>
+        </is>
+      </c>
+      <c r="J182" s="50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="K182" s="50" t="n">
-        <v>300500004</v>
+        <v>300500301</v>
       </c>
       <c r="M182" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="50" t="n">
-        <v>300500101</v>
+        <v>300510011</v>
       </c>
       <c r="B183" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C183" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D183" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E183" s="50" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="F183" s="50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="E183" s="50" t="n">
+        <v>2160</v>
+      </c>
+      <c r="F183" s="50" t="n">
+        <v>760</v>
       </c>
       <c r="G183" s="50" t="n">
-        <v>300500101</v>
-      </c>
-      <c r="H183" s="50" t="inlineStr">
-        <is>
-          <t>300500001|300500002|300500003|300500004|</t>
+        <v>300510011</v>
+      </c>
+      <c r="H183" s="50" t="n">
+        <v>300500102</v>
+      </c>
+      <c r="I183" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount5001:99</t>
         </is>
       </c>
       <c r="J183" s="50" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="K183" s="50" t="n">
-        <v>300500101</v>
+        <v>300510011</v>
       </c>
       <c r="M183" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>孕育牛头人战士x1</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="50" t="n">
-        <v>300500102</v>
+        <v>300510012</v>
       </c>
       <c r="B184" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C184" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D184" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E184" s="50" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="F184" s="50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="E184" s="50" t="n">
+        <v>2160</v>
+      </c>
+      <c r="F184" s="50" t="n">
+        <v>920</v>
       </c>
       <c r="G184" s="50" t="n">
-        <v>300500102</v>
+        <v>300510012</v>
       </c>
       <c r="H184" s="50" t="n">
-        <v>300500101</v>
+        <v>300510011</v>
       </c>
       <c r="J184" s="50" t="n">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="K184" s="50" t="n">
-        <v>300500102</v>
+        <v>300510012</v>
       </c>
       <c r="M184" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>孕育牛头人战士x5</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="50" t="n">
-        <v>300500201</v>
+        <v>300510013</v>
       </c>
       <c r="B185" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C185" s="50" t="inlineStr">
         <is>
-          <t>ui_research_40</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D185" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E185" s="50" t="inlineStr">
-        <is>
-          <t>2550</t>
-        </is>
-      </c>
-      <c r="F185" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
+      <c r="E185" s="50" t="n">
+        <v>2160</v>
+      </c>
+      <c r="F185" s="50" t="n">
+        <v>1080</v>
       </c>
       <c r="G185" s="50" t="n">
-        <v>300500201</v>
-      </c>
-      <c r="H185" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300500000,</t>
-        </is>
+        <v>300510013</v>
+      </c>
+      <c r="H185" s="50" t="n">
+        <v>300510012</v>
       </c>
       <c r="J185" s="50" t="n">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="K185" s="50" t="n">
-        <v>300500201</v>
+        <v>300510013</v>
       </c>
       <c r="M185" s="50" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人战士x10</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="50" t="n">
-        <v>300500301</v>
+        <v>300510021</v>
       </c>
       <c r="B186" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C186" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D186" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E186" s="50" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="F186" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
+      <c r="E186" s="50" t="n">
+        <v>2320</v>
+      </c>
+      <c r="F186" s="50" t="n">
+        <v>760</v>
       </c>
       <c r="G186" s="50" t="n">
-        <v>300500301</v>
-      </c>
-      <c r="H186" s="50" t="inlineStr">
-        <is>
-          <t>300500000,</t>
+        <v>300510021</v>
+      </c>
+      <c r="H186" s="50" t="n">
+        <v>300500102</v>
+      </c>
+      <c r="I186" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount5002:99</t>
         </is>
       </c>
       <c r="J186" s="50" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="K186" s="50" t="n">
-        <v>300500301</v>
+        <v>300510021</v>
       </c>
       <c r="M186" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>孕育牛头人投手x1</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="50" t="n">
-        <v>300510011</v>
+        <v>300510022</v>
       </c>
       <c r="B187" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C187" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D187" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E187" s="50" t="n">
-        <v>2160</v>
+        <v>2320</v>
       </c>
       <c r="F187" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G187" s="50" t="n">
-        <v>300510011</v>
+        <v>300510022</v>
       </c>
       <c r="H187" s="50" t="n">
-        <v>300500102</v>
-      </c>
-      <c r="I187" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount5001:99</t>
-        </is>
+        <v>300510021</v>
       </c>
       <c r="J187" s="50" t="n">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="K187" s="50" t="n">
-        <v>300510011</v>
+        <v>300510022</v>
       </c>
       <c r="M187" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x1</t>
+          <t>孕育牛头人投手x5</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="50" t="n">
-        <v>300510012</v>
+        <v>300510023</v>
       </c>
       <c r="B188" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C188" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D188" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E188" s="50" t="n">
-        <v>2160</v>
+        <v>2320</v>
       </c>
       <c r="F188" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G188" s="50" t="n">
-        <v>300510012</v>
+        <v>300510023</v>
       </c>
       <c r="H188" s="50" t="n">
-        <v>300510011</v>
+        <v>300510022</v>
       </c>
       <c r="J188" s="50" t="n">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="K188" s="50" t="n">
-        <v>300510012</v>
+        <v>300510023</v>
       </c>
       <c r="M188" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x5</t>
+          <t>孕育牛头人投手x10</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="50" t="n">
-        <v>300510013</v>
+        <v>300510031</v>
       </c>
       <c r="B189" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C189" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D189" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E189" s="50" t="n">
-        <v>2160</v>
+        <v>2480</v>
       </c>
       <c r="F189" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G189" s="50" t="n">
-        <v>300510013</v>
+        <v>300510031</v>
       </c>
       <c r="H189" s="50" t="n">
-        <v>300510012</v>
+        <v>300500102</v>
+      </c>
+      <c r="I189" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount5003:99</t>
+        </is>
       </c>
       <c r="J189" s="50" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="K189" s="50" t="n">
-        <v>300510013</v>
+        <v>300510031</v>
       </c>
       <c r="M189" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x10</t>
+          <t>孕育牛头人魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="50" t="n">
-        <v>300510021</v>
+        <v>300510032</v>
       </c>
       <c r="B190" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C190" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D190" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E190" s="50" t="n">
-        <v>2320</v>
+        <v>2480</v>
       </c>
       <c r="F190" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G190" s="50" t="n">
-        <v>300510021</v>
+        <v>300510032</v>
       </c>
       <c r="H190" s="50" t="n">
-        <v>300500102</v>
-      </c>
-      <c r="I190" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount5002:99</t>
-        </is>
+        <v>300510031</v>
       </c>
       <c r="J190" s="50" t="n">
-        <v>200</v>
+        <v>20000</v>
       </c>
       <c r="K190" s="50" t="n">
-        <v>300510021</v>
+        <v>300510032</v>
       </c>
       <c r="M190" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x1</t>
+          <t>孕育牛头人魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="50" t="n">
-        <v>300510022</v>
+        <v>300510033</v>
       </c>
       <c r="B191" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C191" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D191" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E191" s="50" t="n">
-        <v>2320</v>
+        <v>2480</v>
       </c>
       <c r="F191" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G191" s="50" t="n">
-        <v>300510022</v>
+        <v>300510033</v>
       </c>
       <c r="H191" s="50" t="n">
-        <v>300510021</v>
+        <v>300510032</v>
       </c>
       <c r="J191" s="50" t="n">
-        <v>500</v>
+        <v>40000</v>
       </c>
       <c r="K191" s="50" t="n">
-        <v>300510022</v>
+        <v>300510033</v>
       </c>
       <c r="M191" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x5</t>
+          <t>孕育牛头人魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="50" t="n">
-        <v>300510023</v>
+        <v>300510041</v>
       </c>
       <c r="B192" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C192" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D192" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E192" s="50" t="n">
-        <v>2320</v>
+        <v>2640</v>
       </c>
       <c r="F192" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G192" s="50" t="n">
-        <v>300510023</v>
+        <v>300510041</v>
       </c>
       <c r="H192" s="50" t="n">
-        <v>300510022</v>
+        <v>300500102</v>
+      </c>
+      <c r="I192" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount5004:99</t>
+        </is>
       </c>
       <c r="J192" s="50" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="K192" s="50" t="n">
-        <v>300510023</v>
+        <v>300510041</v>
       </c>
       <c r="M192" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x10</t>
+          <t>孕育牛头人魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="50" t="n">
-        <v>300510031</v>
+        <v>300510042</v>
       </c>
       <c r="B193" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C193" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D193" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E193" s="50" t="n">
-        <v>2480</v>
+        <v>2640</v>
       </c>
       <c r="F193" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G193" s="50" t="n">
-        <v>300510031</v>
+        <v>300510042</v>
       </c>
       <c r="H193" s="50" t="n">
-        <v>300500102</v>
-      </c>
-      <c r="I193" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount5003:99</t>
-        </is>
+        <v>300510041</v>
       </c>
       <c r="J193" s="50" t="n">
-        <v>200</v>
+        <v>20000</v>
       </c>
       <c r="K193" s="50" t="n">
-        <v>300510031</v>
+        <v>300510042</v>
       </c>
       <c r="M193" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x1</t>
+          <t>孕育牛头人魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="50" t="n">
-        <v>300510032</v>
+        <v>300510043</v>
       </c>
       <c r="B194" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C194" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D194" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E194" s="50" t="n">
-        <v>2480</v>
+        <v>2640</v>
       </c>
       <c r="F194" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G194" s="50" t="n">
-        <v>300510032</v>
+        <v>300510043</v>
       </c>
       <c r="H194" s="50" t="n">
-        <v>300510031</v>
+        <v>300510042</v>
       </c>
       <c r="J194" s="50" t="n">
-        <v>500</v>
+        <v>40000</v>
       </c>
       <c r="K194" s="50" t="n">
-        <v>300510032</v>
+        <v>300510043</v>
       </c>
       <c r="M194" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x5</t>
+          <t>孕育牛头人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="50" t="n">
-        <v>300510033</v>
+        <v>300600000</v>
       </c>
       <c r="B195" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C195" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D195" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E195" s="50" t="n">
-        <v>2480</v>
-      </c>
-      <c r="F195" s="50" t="n">
-        <v>1080</v>
+      <c r="E195" s="50" t="inlineStr">
+        <is>
+          <t>-1600</t>
+        </is>
+      </c>
+      <c r="F195" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G195" s="50" t="n">
-        <v>300510033</v>
+        <v>300600000</v>
       </c>
       <c r="H195" s="50" t="n">
-        <v>300510032</v>
-      </c>
-      <c r="J195" s="50" t="n">
-        <v>1000</v>
+        <v>300300000</v>
+      </c>
+      <c r="J195" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="K195" s="50" t="n">
-        <v>300510033</v>
+        <v>300600000</v>
       </c>
       <c r="M195" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x10</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="50" t="n">
-        <v>300510041</v>
+        <v>300600001</v>
       </c>
       <c r="B196" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C196" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_44</t>
         </is>
       </c>
       <c r="D196" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E196" s="50" t="n">
-        <v>2640</v>
-      </c>
-      <c r="F196" s="50" t="n">
-        <v>760</v>
+      <c r="E196" s="50" t="inlineStr">
+        <is>
+          <t>-1900</t>
+        </is>
+      </c>
+      <c r="F196" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G196" s="50" t="n">
-        <v>300510041</v>
+        <v>300600001</v>
       </c>
       <c r="H196" s="50" t="n">
-        <v>300500102</v>
-      </c>
-      <c r="I196" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount5004:99</t>
-        </is>
-      </c>
-      <c r="J196" s="50" t="n">
-        <v>200</v>
+        <v>300600000</v>
+      </c>
+      <c r="J196" s="50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="K196" s="50" t="n">
-        <v>300510041</v>
+        <v>300600001</v>
       </c>
       <c r="M196" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x1</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="50" t="n">
-        <v>300510042</v>
+        <v>300600002</v>
       </c>
       <c r="B197" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C197" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D197" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E197" s="50" t="n">
-        <v>2640</v>
-      </c>
-      <c r="F197" s="50" t="n">
-        <v>920</v>
+      <c r="E197" s="50" t="inlineStr">
+        <is>
+          <t>-1750</t>
+        </is>
+      </c>
+      <c r="F197" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G197" s="50" t="n">
-        <v>300510042</v>
+        <v>300600002</v>
       </c>
       <c r="H197" s="50" t="n">
-        <v>300510041</v>
-      </c>
-      <c r="J197" s="50" t="n">
-        <v>500</v>
+        <v>300600000</v>
+      </c>
+      <c r="J197" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="K197" s="50" t="n">
-        <v>300510042</v>
+        <v>300600002</v>
       </c>
       <c r="M197" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x5</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="50" t="n">
-        <v>300510043</v>
+        <v>300600003</v>
       </c>
       <c r="B198" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C198" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_54</t>
         </is>
       </c>
       <c r="D198" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E198" s="50" t="n">
-        <v>2640</v>
-      </c>
-      <c r="F198" s="50" t="n">
-        <v>1080</v>
+      <c r="E198" s="50" t="inlineStr">
+        <is>
+          <t>-1600</t>
+        </is>
+      </c>
+      <c r="F198" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G198" s="50" t="n">
-        <v>300510043</v>
+        <v>300600003</v>
       </c>
       <c r="H198" s="50" t="n">
-        <v>300510042</v>
-      </c>
-      <c r="J198" s="50" t="n">
-        <v>1000</v>
+        <v>300600000</v>
+      </c>
+      <c r="J198" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="K198" s="50" t="n">
-        <v>300510043</v>
+        <v>300600003</v>
       </c>
       <c r="M198" s="50" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x10</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="50" t="n">
+        <v>300600004</v>
+      </c>
+      <c r="B199" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C199" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_48</t>
+        </is>
+      </c>
+      <c r="D199" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="50" t="inlineStr">
+        <is>
+          <t>-1450</t>
+        </is>
+      </c>
+      <c r="F199" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G199" s="50" t="n">
+        <v>300600004</v>
+      </c>
+      <c r="H199" s="50" t="n">
         <v>300600000</v>
       </c>
-      <c r="B199" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="C199" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_39</t>
-        </is>
-      </c>
-      <c r="D199" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="50" t="inlineStr">
-        <is>
-          <t>-1600</t>
-        </is>
-      </c>
-      <c r="F199" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G199" s="50" t="n">
-        <v>300600000</v>
-      </c>
-      <c r="H199" s="50" t="n">
-        <v>300300000</v>
-      </c>
       <c r="J199" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="K199" s="50" t="n">
-        <v>300600000</v>
+        <v>300600004</v>
       </c>
       <c r="M199" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="50" t="n">
-        <v>300600001</v>
+        <v>300600005</v>
       </c>
       <c r="B200" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C200" s="50" t="inlineStr">
         <is>
-          <t>ui_research_44</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D200" s="50" t="n">
@@ -10129,7 +10024,7 @@
       </c>
       <c r="E200" s="50" t="inlineStr">
         <is>
-          <t>-1900</t>
+          <t>-1300</t>
         </is>
       </c>
       <c r="F200" s="50" t="inlineStr">
@@ -10138,35 +10033,35 @@
         </is>
       </c>
       <c r="G200" s="50" t="n">
-        <v>300600001</v>
+        <v>300600005</v>
       </c>
       <c r="H200" s="50" t="n">
         <v>300600000</v>
       </c>
       <c r="J200" s="50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="K200" s="50" t="n">
-        <v>300600001</v>
+        <v>300600005</v>
       </c>
       <c r="M200" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="50" t="n">
-        <v>300600002</v>
+        <v>300600101</v>
       </c>
       <c r="B201" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C201" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D201" s="50" t="n">
@@ -10174,44 +10069,46 @@
       </c>
       <c r="E201" s="50" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F201" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G201" s="50" t="n">
-        <v>300600002</v>
-      </c>
-      <c r="H201" s="50" t="n">
-        <v>300600000</v>
+        <v>300600101</v>
+      </c>
+      <c r="H201" s="50" t="inlineStr">
+        <is>
+          <t>300600001|300600002|300600003|300600004|300600005</t>
+        </is>
       </c>
       <c r="J201" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="K201" s="50" t="n">
-        <v>300600002</v>
+        <v>300600101</v>
       </c>
       <c r="M201" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="50" t="n">
-        <v>300600003</v>
+        <v>300600102</v>
       </c>
       <c r="B202" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C202" s="50" t="inlineStr">
         <is>
-          <t>ui_research_54</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D202" s="50" t="n">
@@ -10224,39 +10121,39 @@
       </c>
       <c r="F202" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G202" s="50" t="n">
-        <v>300600003</v>
+        <v>300600102</v>
       </c>
       <c r="H202" s="50" t="n">
-        <v>300600000</v>
+        <v>300600101</v>
       </c>
       <c r="J202" s="50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="K202" s="50" t="n">
-        <v>300600003</v>
+        <v>300600102</v>
       </c>
       <c r="M202" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="50" t="n">
-        <v>300600004</v>
+        <v>300600201</v>
       </c>
       <c r="B203" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C203" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_39</t>
         </is>
       </c>
       <c r="D203" s="50" t="n">
@@ -10269,39 +10166,41 @@
       </c>
       <c r="F203" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G203" s="50" t="n">
-        <v>300600004</v>
-      </c>
-      <c r="H203" s="50" t="n">
-        <v>300600000</v>
+        <v>300600201</v>
+      </c>
+      <c r="H203" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300600000,</t>
+        </is>
       </c>
       <c r="J203" s="50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="K203" s="50" t="n">
-        <v>300600004</v>
+        <v>300600201</v>
       </c>
       <c r="M203" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="50" t="n">
-        <v>300600005</v>
+        <v>300600301</v>
       </c>
       <c r="B204" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C204" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D204" s="50" t="n">
@@ -10309,883 +10208,881 @@
       </c>
       <c r="E204" s="50" t="inlineStr">
         <is>
-          <t>-1300</t>
+          <t>-1600</t>
         </is>
       </c>
       <c r="F204" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G204" s="50" t="n">
-        <v>300600005</v>
-      </c>
-      <c r="H204" s="50" t="n">
-        <v>300600000</v>
+        <v>300600301</v>
+      </c>
+      <c r="H204" s="50" t="inlineStr">
+        <is>
+          <t>300600000,</t>
+        </is>
       </c>
       <c r="J204" s="50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="K204" s="50" t="n">
-        <v>300600005</v>
+        <v>300600301</v>
       </c>
       <c r="M204" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="50" t="n">
-        <v>300600101</v>
+        <v>300610011</v>
       </c>
       <c r="B205" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C205" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_44</t>
         </is>
       </c>
       <c r="D205" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E205" s="50" t="inlineStr">
-        <is>
-          <t>-1600</t>
-        </is>
-      </c>
-      <c r="F205" s="50" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
+      <c r="E205" s="50" t="n">
+        <v>-1920</v>
+      </c>
+      <c r="F205" s="50" t="n">
+        <v>760</v>
       </c>
       <c r="G205" s="50" t="n">
-        <v>300600101</v>
-      </c>
-      <c r="H205" s="50" t="inlineStr">
-        <is>
-          <t>300600001|300600002|300600003|300600004|300600005</t>
-        </is>
-      </c>
-      <c r="J205" s="50" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+        <v>300610011</v>
+      </c>
+      <c r="H205" s="50" t="n">
+        <v>300600102</v>
+      </c>
+      <c r="I205" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount6001:99</t>
+        </is>
+      </c>
+      <c r="J205" s="50" t="n">
+        <v>250</v>
       </c>
       <c r="K205" s="50" t="n">
-        <v>300600101</v>
+        <v>300610011</v>
       </c>
       <c r="M205" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>孕育哥布林刺客x1</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="50" t="n">
-        <v>300600102</v>
+        <v>300610012</v>
       </c>
       <c r="B206" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C206" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_44</t>
         </is>
       </c>
       <c r="D206" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E206" s="50" t="inlineStr">
-        <is>
-          <t>-1600</t>
-        </is>
-      </c>
-      <c r="F206" s="50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="E206" s="50" t="n">
+        <v>-1920</v>
+      </c>
+      <c r="F206" s="50" t="n">
+        <v>920</v>
       </c>
       <c r="G206" s="50" t="n">
-        <v>300600102</v>
+        <v>300610012</v>
       </c>
       <c r="H206" s="50" t="n">
-        <v>300600101</v>
-      </c>
-      <c r="J206" s="50" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
+        <v>300610011</v>
+      </c>
+      <c r="J206" s="50" t="n">
+        <v>1250</v>
       </c>
       <c r="K206" s="50" t="n">
-        <v>300600102</v>
+        <v>300610012</v>
       </c>
       <c r="M206" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>孕育哥布林刺客x5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="50" t="n">
-        <v>300600201</v>
+        <v>300610013</v>
       </c>
       <c r="B207" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C207" s="50" t="inlineStr">
         <is>
-          <t>ui_research_39</t>
+          <t>ui_research_44</t>
         </is>
       </c>
       <c r="D207" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E207" s="50" t="inlineStr">
-        <is>
-          <t>-1450</t>
-        </is>
-      </c>
-      <c r="F207" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
+      <c r="E207" s="50" t="n">
+        <v>-1920</v>
+      </c>
+      <c r="F207" s="50" t="n">
+        <v>1080</v>
       </c>
       <c r="G207" s="50" t="n">
-        <v>300600201</v>
-      </c>
-      <c r="H207" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300600000,</t>
-        </is>
-      </c>
-      <c r="J207" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>300610013</v>
+      </c>
+      <c r="H207" s="50" t="n">
+        <v>300610012</v>
+      </c>
+      <c r="J207" s="50" t="n">
+        <v>2500</v>
       </c>
       <c r="K207" s="50" t="n">
-        <v>300600201</v>
+        <v>300610013</v>
       </c>
       <c r="M207" s="50" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育哥布林刺客x10</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="50" t="n">
-        <v>300600301</v>
+        <v>300610021</v>
       </c>
       <c r="B208" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C208" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D208" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E208" s="50" t="inlineStr">
-        <is>
-          <t>-1600</t>
-        </is>
-      </c>
-      <c r="F208" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
+      <c r="E208" s="50" t="n">
+        <v>-1760</v>
+      </c>
+      <c r="F208" s="50" t="n">
+        <v>760</v>
       </c>
       <c r="G208" s="50" t="n">
-        <v>300600301</v>
-      </c>
-      <c r="H208" s="50" t="inlineStr">
-        <is>
-          <t>300600000,</t>
-        </is>
-      </c>
-      <c r="J208" s="50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+        <v>300610021</v>
+      </c>
+      <c r="H208" s="50" t="n">
+        <v>300600102</v>
+      </c>
+      <c r="I208" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount6002:99</t>
+        </is>
+      </c>
+      <c r="J208" s="50" t="n">
+        <v>500</v>
       </c>
       <c r="K208" s="50" t="n">
-        <v>300600301</v>
+        <v>300610021</v>
       </c>
       <c r="M208" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>孕育哥布林弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="50" t="n">
-        <v>300610011</v>
+        <v>300610022</v>
       </c>
       <c r="B209" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C209" s="50" t="inlineStr">
         <is>
-          <t>ui_research_44</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D209" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E209" s="50" t="n">
-        <v>-1920</v>
+        <v>-1760</v>
       </c>
       <c r="F209" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G209" s="50" t="n">
-        <v>300610011</v>
+        <v>300610022</v>
       </c>
       <c r="H209" s="50" t="n">
-        <v>300600102</v>
-      </c>
-      <c r="I209" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount6001:99</t>
-        </is>
+        <v>300610021</v>
       </c>
       <c r="J209" s="50" t="n">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="K209" s="50" t="n">
-        <v>300610011</v>
+        <v>300610022</v>
       </c>
       <c r="M209" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x1</t>
+          <t>孕育哥布林弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="50" t="n">
-        <v>300610012</v>
+        <v>300610023</v>
       </c>
       <c r="B210" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C210" s="50" t="inlineStr">
         <is>
-          <t>ui_research_44</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D210" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E210" s="50" t="n">
-        <v>-1920</v>
+        <v>-1760</v>
       </c>
       <c r="F210" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G210" s="50" t="n">
-        <v>300610012</v>
+        <v>300610023</v>
       </c>
       <c r="H210" s="50" t="n">
-        <v>300610011</v>
+        <v>300610022</v>
       </c>
       <c r="J210" s="50" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="K210" s="50" t="n">
-        <v>300610012</v>
+        <v>300610023</v>
       </c>
       <c r="M210" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x5</t>
+          <t>孕育哥布林弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="50" t="n">
-        <v>300610013</v>
+        <v>300610031</v>
       </c>
       <c r="B211" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C211" s="50" t="inlineStr">
         <is>
-          <t>ui_research_44</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D211" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E211" s="50" t="n">
-        <v>-1920</v>
+        <v>-1600</v>
       </c>
       <c r="F211" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G211" s="50" t="n">
-        <v>300610013</v>
+        <v>300610031</v>
       </c>
       <c r="H211" s="50" t="n">
-        <v>300610012</v>
+        <v>300600102</v>
+      </c>
+      <c r="I211" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount6003:99</t>
+        </is>
       </c>
       <c r="J211" s="50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K211" s="50" t="n">
-        <v>300610013</v>
+        <v>300610031</v>
       </c>
       <c r="M211" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x10</t>
+          <t>孕育哥布林敢死队x1</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="50" t="n">
-        <v>300610021</v>
+        <v>300610032</v>
       </c>
       <c r="B212" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C212" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D212" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E212" s="50" t="n">
-        <v>-1760</v>
+        <v>-1600</v>
       </c>
       <c r="F212" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G212" s="50" t="n">
-        <v>300610021</v>
+        <v>300610032</v>
       </c>
       <c r="H212" s="50" t="n">
-        <v>300600102</v>
-      </c>
-      <c r="I212" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount6002:99</t>
-        </is>
+        <v>300610031</v>
       </c>
       <c r="J212" s="50" t="n">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="K212" s="50" t="n">
-        <v>300610021</v>
+        <v>300610032</v>
       </c>
       <c r="M212" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x1</t>
+          <t>孕育哥布林敢死队x5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="50" t="n">
-        <v>300610022</v>
+        <v>300610033</v>
       </c>
       <c r="B213" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C213" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D213" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E213" s="50" t="n">
-        <v>-1760</v>
+        <v>-1600</v>
       </c>
       <c r="F213" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G213" s="50" t="n">
-        <v>300610022</v>
+        <v>300610033</v>
       </c>
       <c r="H213" s="50" t="n">
-        <v>300610021</v>
+        <v>300610032</v>
       </c>
       <c r="J213" s="50" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="K213" s="50" t="n">
-        <v>300610022</v>
+        <v>300610033</v>
       </c>
       <c r="M213" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x5</t>
+          <t>孕育哥布林敢死队x10</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="50" t="n">
-        <v>300610023</v>
+        <v>300610041</v>
       </c>
       <c r="B214" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C214" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D214" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E214" s="50" t="n">
-        <v>-1760</v>
+        <v>-1440</v>
       </c>
       <c r="F214" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G214" s="50" t="n">
-        <v>300610023</v>
+        <v>300610041</v>
       </c>
       <c r="H214" s="50" t="n">
-        <v>300610022</v>
+        <v>300600102</v>
+      </c>
+      <c r="I214" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount6004:99</t>
+        </is>
       </c>
       <c r="J214" s="50" t="n">
         <v>1000</v>
       </c>
       <c r="K214" s="50" t="n">
-        <v>300610023</v>
+        <v>300610041</v>
       </c>
       <c r="M214" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x10</t>
+          <t>孕育哥布林魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="50" t="n">
-        <v>300610031</v>
+        <v>300610042</v>
       </c>
       <c r="B215" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C215" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D215" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E215" s="50" t="n">
-        <v>-1600</v>
+        <v>-1440</v>
       </c>
       <c r="F215" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G215" s="50" t="n">
-        <v>300610031</v>
+        <v>300610042</v>
       </c>
       <c r="H215" s="50" t="n">
-        <v>300600102</v>
-      </c>
-      <c r="I215" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount6003:99</t>
-        </is>
+        <v>300610041</v>
       </c>
       <c r="J215" s="50" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="K215" s="50" t="n">
-        <v>300610031</v>
+        <v>300610042</v>
       </c>
       <c r="M215" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x1</t>
+          <t>孕育哥布林魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="50" t="n">
-        <v>300610032</v>
+        <v>300610043</v>
       </c>
       <c r="B216" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C216" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D216" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E216" s="50" t="n">
-        <v>-1600</v>
+        <v>-1440</v>
       </c>
       <c r="F216" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G216" s="50" t="n">
-        <v>300610032</v>
+        <v>300610043</v>
       </c>
       <c r="H216" s="50" t="n">
-        <v>300610031</v>
+        <v>300610042</v>
       </c>
       <c r="J216" s="50" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="K216" s="50" t="n">
-        <v>300610032</v>
+        <v>300610043</v>
       </c>
       <c r="M216" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x5</t>
+          <t>孕育哥布林魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="50" t="n">
-        <v>300610033</v>
+        <v>300610051</v>
       </c>
       <c r="B217" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C217" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D217" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E217" s="50" t="n">
-        <v>-1600</v>
+        <v>-1280</v>
       </c>
       <c r="F217" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G217" s="50" t="n">
-        <v>300610033</v>
+        <v>300610051</v>
       </c>
       <c r="H217" s="50" t="n">
-        <v>300610032</v>
+        <v>300600102</v>
+      </c>
+      <c r="I217" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount6005:99</t>
+        </is>
       </c>
       <c r="J217" s="50" t="n">
         <v>1000</v>
       </c>
       <c r="K217" s="50" t="n">
-        <v>300610033</v>
+        <v>300610051</v>
       </c>
       <c r="M217" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x10</t>
+          <t>孕育哥布林魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="50" t="n">
-        <v>300610041</v>
+        <v>300610052</v>
       </c>
       <c r="B218" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C218" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D218" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E218" s="50" t="n">
-        <v>-1440</v>
+        <v>-1280</v>
       </c>
       <c r="F218" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G218" s="50" t="n">
-        <v>300610041</v>
+        <v>300610052</v>
       </c>
       <c r="H218" s="50" t="n">
-        <v>300600102</v>
-      </c>
-      <c r="I218" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount6004:99</t>
-        </is>
+        <v>300610051</v>
       </c>
       <c r="J218" s="50" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="K218" s="50" t="n">
-        <v>300610041</v>
+        <v>300610052</v>
       </c>
       <c r="M218" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x1</t>
+          <t>孕育哥布林魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="50" t="n">
-        <v>300610042</v>
+        <v>300610053</v>
       </c>
       <c r="B219" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C219" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D219" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E219" s="50" t="n">
-        <v>-1440</v>
+        <v>-1280</v>
       </c>
       <c r="F219" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G219" s="50" t="n">
-        <v>300610042</v>
+        <v>300610053</v>
       </c>
       <c r="H219" s="50" t="n">
-        <v>300610041</v>
+        <v>300610052</v>
       </c>
       <c r="J219" s="50" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="K219" s="50" t="n">
-        <v>300610042</v>
+        <v>300610053</v>
       </c>
       <c r="M219" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x5</t>
+          <t>孕育哥布林魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="50" t="n">
-        <v>300610043</v>
+        <v>300700000</v>
       </c>
       <c r="B220" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C220" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_38</t>
         </is>
       </c>
       <c r="D220" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E220" s="50" t="n">
-        <v>-1440</v>
-      </c>
-      <c r="F220" s="50" t="n">
-        <v>1080</v>
+      <c r="E220" s="50" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="F220" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G220" s="50" t="n">
-        <v>300610043</v>
+        <v>300700000</v>
       </c>
       <c r="H220" s="50" t="n">
-        <v>300610042</v>
-      </c>
-      <c r="J220" s="50" t="n">
-        <v>1000</v>
+        <v>300100000</v>
+      </c>
+      <c r="J220" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K220" s="50" t="n">
-        <v>300610043</v>
+        <v>300700000</v>
       </c>
       <c r="M220" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x10</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="50" t="n">
-        <v>300610051</v>
+        <v>300700001</v>
       </c>
       <c r="B221" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C221" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D221" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E221" s="50" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="F221" s="50" t="n">
-        <v>760</v>
+      <c r="E221" s="50" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="F221" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G221" s="50" t="n">
-        <v>300610051</v>
+        <v>300700001</v>
       </c>
       <c r="H221" s="50" t="n">
-        <v>300600102</v>
-      </c>
-      <c r="I221" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount6005:99</t>
-        </is>
-      </c>
-      <c r="J221" s="50" t="n">
-        <v>200</v>
+        <v>300700000</v>
+      </c>
+      <c r="J221" s="50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="K221" s="50" t="n">
-        <v>300610051</v>
+        <v>300700001</v>
       </c>
       <c r="M221" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x1</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="50" t="n">
-        <v>300610052</v>
+        <v>300700002</v>
       </c>
       <c r="B222" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C222" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D222" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E222" s="50" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="F222" s="50" t="n">
-        <v>920</v>
+      <c r="E222" s="50" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="F222" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G222" s="50" t="n">
-        <v>300610052</v>
+        <v>300700002</v>
       </c>
       <c r="H222" s="50" t="n">
-        <v>300610051</v>
-      </c>
-      <c r="J222" s="50" t="n">
-        <v>500</v>
+        <v>300700000</v>
+      </c>
+      <c r="J222" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K222" s="50" t="n">
-        <v>300610052</v>
+        <v>300700002</v>
       </c>
       <c r="M222" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x5</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="50" t="n">
-        <v>300610053</v>
+        <v>300700003</v>
       </c>
       <c r="B223" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C223" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D223" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E223" s="50" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="F223" s="50" t="n">
-        <v>1080</v>
+      <c r="E223" s="50" t="inlineStr">
+        <is>
+          <t>1675</t>
+        </is>
+      </c>
+      <c r="F223" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G223" s="50" t="n">
-        <v>300610053</v>
+        <v>300700003</v>
       </c>
       <c r="H223" s="50" t="n">
-        <v>300610052</v>
-      </c>
-      <c r="J223" s="50" t="n">
-        <v>1000</v>
+        <v>300700000</v>
+      </c>
+      <c r="J223" s="50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="K223" s="50" t="n">
-        <v>300610053</v>
+        <v>300700003</v>
       </c>
       <c r="M223" s="50" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x10</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="50" t="n">
+        <v>300700004</v>
+      </c>
+      <c r="B224" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C224" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_47</t>
+        </is>
+      </c>
+      <c r="D224" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" s="50" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="F224" s="50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G224" s="50" t="n">
+        <v>300700004</v>
+      </c>
+      <c r="H224" s="50" t="n">
         <v>300700000</v>
       </c>
-      <c r="B224" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="C224" s="50" t="inlineStr">
-        <is>
-          <t>ui_research_38</t>
-        </is>
-      </c>
-      <c r="D224" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E224" s="50" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="F224" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G224" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="H224" s="50" t="n">
-        <v>300100000</v>
-      </c>
-      <c r="J224" s="50" t="n">
-        <v>100</v>
+      <c r="J224" s="50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="K224" s="50" t="n">
-        <v>300700000</v>
+        <v>300700004</v>
       </c>
       <c r="M224" s="50" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="50" t="n">
-        <v>300700001</v>
+        <v>300700101</v>
       </c>
       <c r="B225" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C225" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_33</t>
         </is>
       </c>
       <c r="D225" s="50" t="n">
@@ -11193,42 +11090,46 @@
       </c>
       <c r="E225" s="50" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F225" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G225" s="50" t="n">
-        <v>300700001</v>
-      </c>
-      <c r="H225" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="J225" s="50" t="n">
-        <v>100</v>
+        <v>300700101</v>
+      </c>
+      <c r="H225" s="50" t="inlineStr">
+        <is>
+          <t>300700001|300700002|300700003|300700004|</t>
+        </is>
+      </c>
+      <c r="J225" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K225" s="50" t="n">
-        <v>300700001</v>
+        <v>300700101</v>
       </c>
       <c r="M225" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="50" t="n">
-        <v>300700002</v>
+        <v>300700102</v>
       </c>
       <c r="B226" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C226" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_34</t>
         </is>
       </c>
       <c r="D226" s="50" t="n">
@@ -11236,42 +11137,44 @@
       </c>
       <c r="E226" s="50" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F226" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="G226" s="50" t="n">
-        <v>300700002</v>
+        <v>300700102</v>
       </c>
       <c r="H226" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="J226" s="50" t="n">
-        <v>100</v>
+        <v>300700101</v>
+      </c>
+      <c r="J226" s="50" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="K226" s="50" t="n">
-        <v>300700002</v>
+        <v>300700102</v>
       </c>
       <c r="M226" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="50" t="n">
-        <v>300700003</v>
+        <v>300700201</v>
       </c>
       <c r="B227" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C227" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_38</t>
         </is>
       </c>
       <c r="D227" s="50" t="n">
@@ -11279,42 +11182,46 @@
       </c>
       <c r="E227" s="50" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="F227" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G227" s="50" t="n">
-        <v>300700003</v>
-      </c>
-      <c r="H227" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="J227" s="50" t="n">
-        <v>100</v>
+        <v>300700201</v>
+      </c>
+      <c r="H227" s="50" t="inlineStr">
+        <is>
+          <t>100200001,300700000,</t>
+        </is>
+      </c>
+      <c r="J227" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K227" s="50" t="n">
-        <v>300700003</v>
+        <v>300700201</v>
       </c>
       <c r="M227" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="50" t="n">
-        <v>300700004</v>
+        <v>300700301</v>
       </c>
       <c r="B228" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C228" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_58</t>
         </is>
       </c>
       <c r="D228" s="50" t="n">
@@ -11322,843 +11229,1075 @@
       </c>
       <c r="E228" s="50" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F228" s="50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="G228" s="50" t="n">
-        <v>300700004</v>
-      </c>
-      <c r="H228" s="50" t="n">
-        <v>300700000</v>
-      </c>
-      <c r="J228" s="50" t="n">
-        <v>100</v>
+        <v>300700301</v>
+      </c>
+      <c r="H228" s="50" t="inlineStr">
+        <is>
+          <t>300700000,</t>
+        </is>
+      </c>
+      <c r="J228" s="50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="K228" s="50" t="n">
-        <v>300700004</v>
+        <v>300700301</v>
       </c>
       <c r="M228" s="50" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>奖励-可获取兽人装备</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="50" t="n">
-        <v>300700101</v>
+        <v>300710011</v>
       </c>
       <c r="B229" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C229" s="50" t="inlineStr">
         <is>
-          <t>ui_research_33</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D229" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E229" s="50" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="F229" s="50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="E229" s="50" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F229" s="50" t="n">
+        <v>760</v>
       </c>
       <c r="G229" s="50" t="n">
-        <v>300700101</v>
-      </c>
-      <c r="H229" s="50" t="inlineStr">
-        <is>
-          <t>300700001|300700002|300700003|300700004|</t>
+        <v>300710011</v>
+      </c>
+      <c r="H229" s="50" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="I229" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount7001:99</t>
         </is>
       </c>
       <c r="J229" s="50" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K229" s="50" t="n">
-        <v>300700101</v>
+        <v>300710011</v>
       </c>
       <c r="M229" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>孕育兽人战士x1</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="50" t="n">
-        <v>300700102</v>
+        <v>300710012</v>
       </c>
       <c r="B230" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C230" s="50" t="inlineStr">
         <is>
-          <t>ui_research_34</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D230" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E230" s="50" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="F230" s="50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+      <c r="E230" s="50" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F230" s="50" t="n">
+        <v>920</v>
       </c>
       <c r="G230" s="50" t="n">
-        <v>300700102</v>
+        <v>300710012</v>
       </c>
       <c r="H230" s="50" t="n">
-        <v>300700101</v>
+        <v>300710011</v>
       </c>
       <c r="J230" s="50" t="n">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="K230" s="50" t="n">
-        <v>300700102</v>
+        <v>300710012</v>
       </c>
       <c r="M230" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>孕育兽人战士x5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="50" t="n">
-        <v>300700201</v>
+        <v>300710013</v>
       </c>
       <c r="B231" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C231" s="50" t="inlineStr">
         <is>
-          <t>ui_research_38</t>
+          <t>ui_research_43</t>
         </is>
       </c>
       <c r="D231" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E231" s="50" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-      <c r="F231" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
+      <c r="E231" s="50" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F231" s="50" t="n">
+        <v>1080</v>
       </c>
       <c r="G231" s="50" t="n">
-        <v>300700201</v>
-      </c>
-      <c r="H231" s="50" t="inlineStr">
-        <is>
-          <t>100200001,300700000,</t>
-        </is>
+        <v>300710013</v>
+      </c>
+      <c r="H231" s="50" t="n">
+        <v>300710012</v>
       </c>
       <c r="J231" s="50" t="n">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="K231" s="50" t="n">
-        <v>300700201</v>
+        <v>300710013</v>
       </c>
       <c r="M231" s="50" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人战士x10</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="50" t="n">
-        <v>300700301</v>
+        <v>300710021</v>
       </c>
       <c r="B232" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C232" s="50" t="inlineStr">
         <is>
-          <t>ui_research_58</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D232" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E232" s="50" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="F232" s="50" t="inlineStr">
-        <is>
-          <t>-200</t>
-        </is>
+      <c r="E232" s="50" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F232" s="50" t="n">
+        <v>760</v>
       </c>
       <c r="G232" s="50" t="n">
-        <v>300700301</v>
-      </c>
-      <c r="H232" s="50" t="inlineStr">
-        <is>
-          <t>300700000,</t>
+        <v>300710021</v>
+      </c>
+      <c r="H232" s="50" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="I232" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount7002:99</t>
         </is>
       </c>
       <c r="J232" s="50" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="K232" s="50" t="n">
-        <v>300700301</v>
+        <v>300710021</v>
       </c>
       <c r="M232" s="50" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>孕育兽人弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="50" t="n">
-        <v>300710011</v>
+        <v>300710022</v>
       </c>
       <c r="B233" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C233" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D233" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E233" s="50" t="n">
-        <v>1360</v>
+        <v>1520</v>
       </c>
       <c r="F233" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G233" s="50" t="n">
-        <v>300710011</v>
+        <v>300710022</v>
       </c>
       <c r="H233" s="50" t="n">
-        <v>300700102</v>
-      </c>
-      <c r="I233" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount7001:99</t>
-        </is>
+        <v>300710021</v>
       </c>
       <c r="J233" s="50" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="K233" s="50" t="n">
-        <v>300710011</v>
+        <v>300710022</v>
       </c>
       <c r="M233" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人战士x1</t>
+          <t>孕育兽人弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="50" t="n">
-        <v>300710012</v>
+        <v>300710023</v>
       </c>
       <c r="B234" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C234" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_42</t>
         </is>
       </c>
       <c r="D234" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E234" s="50" t="n">
-        <v>1360</v>
+        <v>1520</v>
       </c>
       <c r="F234" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G234" s="50" t="n">
-        <v>300710012</v>
+        <v>300710023</v>
       </c>
       <c r="H234" s="50" t="n">
-        <v>300710011</v>
+        <v>300710022</v>
       </c>
       <c r="J234" s="50" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="K234" s="50" t="n">
-        <v>300710012</v>
+        <v>300710023</v>
       </c>
       <c r="M234" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人战士x5</t>
+          <t>孕育兽人弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="50" t="n">
-        <v>300710013</v>
+        <v>300710031</v>
       </c>
       <c r="B235" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C235" s="50" t="inlineStr">
         <is>
-          <t>ui_research_43</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D235" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E235" s="50" t="n">
-        <v>1360</v>
+        <v>1680</v>
       </c>
       <c r="F235" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G235" s="50" t="n">
-        <v>300710013</v>
+        <v>300710031</v>
       </c>
       <c r="H235" s="50" t="n">
-        <v>300710012</v>
+        <v>300700102</v>
+      </c>
+      <c r="I235" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount7003:99</t>
+        </is>
       </c>
       <c r="J235" s="50" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="K235" s="50" t="n">
-        <v>300710013</v>
+        <v>300710031</v>
       </c>
       <c r="M235" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人战士x10</t>
+          <t>孕育兽人魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="50" t="n">
-        <v>300710021</v>
+        <v>300710032</v>
       </c>
       <c r="B236" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C236" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D236" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E236" s="50" t="n">
-        <v>1520</v>
+        <v>1680</v>
       </c>
       <c r="F236" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G236" s="50" t="n">
-        <v>300710021</v>
+        <v>300710032</v>
       </c>
       <c r="H236" s="50" t="n">
-        <v>300700102</v>
-      </c>
-      <c r="I236" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount7002:99</t>
-        </is>
+        <v>300710031</v>
       </c>
       <c r="J236" s="50" t="n">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="K236" s="50" t="n">
-        <v>300710021</v>
+        <v>300710032</v>
       </c>
       <c r="M236" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x1</t>
+          <t>孕育兽人魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="50" t="n">
-        <v>300710022</v>
+        <v>300710033</v>
       </c>
       <c r="B237" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C237" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_48</t>
         </is>
       </c>
       <c r="D237" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E237" s="50" t="n">
-        <v>1520</v>
+        <v>1680</v>
       </c>
       <c r="F237" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G237" s="50" t="n">
-        <v>300710022</v>
+        <v>300710033</v>
       </c>
       <c r="H237" s="50" t="n">
-        <v>300710021</v>
+        <v>300710032</v>
       </c>
       <c r="J237" s="50" t="n">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="K237" s="50" t="n">
-        <v>300710022</v>
+        <v>300710033</v>
       </c>
       <c r="M237" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x5</t>
+          <t>孕育兽人魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="50" t="n">
-        <v>300710023</v>
+        <v>300710041</v>
       </c>
       <c r="B238" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C238" s="50" t="inlineStr">
         <is>
-          <t>ui_research_42</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D238" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E238" s="50" t="n">
-        <v>1520</v>
+        <v>1840</v>
       </c>
       <c r="F238" s="50" t="n">
-        <v>1080</v>
+        <v>760</v>
       </c>
       <c r="G238" s="50" t="n">
-        <v>300710023</v>
+        <v>300710041</v>
       </c>
       <c r="H238" s="50" t="n">
-        <v>300710022</v>
+        <v>300700102</v>
+      </c>
+      <c r="I238" s="50" t="inlineStr">
+        <is>
+          <t>GashaponCreatureDrawCount7004:99</t>
+        </is>
       </c>
       <c r="J238" s="50" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="K238" s="50" t="n">
-        <v>300710023</v>
+        <v>300710041</v>
       </c>
       <c r="M238" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x10</t>
+          <t>孕育兽人魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="50" t="n">
-        <v>300710031</v>
+        <v>300710042</v>
       </c>
       <c r="B239" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C239" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D239" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E239" s="50" t="n">
-        <v>1680</v>
+        <v>1840</v>
       </c>
       <c r="F239" s="50" t="n">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="G239" s="50" t="n">
-        <v>300710031</v>
+        <v>300710042</v>
       </c>
       <c r="H239" s="50" t="n">
-        <v>300700102</v>
-      </c>
-      <c r="I239" s="50" t="inlineStr">
-        <is>
-          <t>GashaponCreatureDrawCount7003:99</t>
-        </is>
+        <v>300710041</v>
       </c>
       <c r="J239" s="50" t="n">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="K239" s="50" t="n">
-        <v>300710031</v>
+        <v>300710042</v>
       </c>
       <c r="M239" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x1</t>
+          <t>孕育兽人魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="50" t="n">
-        <v>300710032</v>
+        <v>300710043</v>
       </c>
       <c r="B240" s="50" t="n">
         <v>3</v>
       </c>
       <c r="C240" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_47</t>
         </is>
       </c>
       <c r="D240" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E240" s="50" t="n">
-        <v>1680</v>
+        <v>1840</v>
       </c>
       <c r="F240" s="50" t="n">
-        <v>920</v>
+        <v>1080</v>
       </c>
       <c r="G240" s="50" t="n">
-        <v>300710032</v>
+        <v>300710043</v>
       </c>
       <c r="H240" s="50" t="n">
-        <v>300710031</v>
+        <v>300710042</v>
       </c>
       <c r="J240" s="50" t="n">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="K240" s="50" t="n">
-        <v>300710032</v>
+        <v>300710043</v>
       </c>
       <c r="M240" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x5</t>
+          <t>孕育兽人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="50" t="n">
-        <v>300710033</v>
+        <v>100300007</v>
       </c>
       <c r="B241" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C241" s="50" t="inlineStr">
         <is>
-          <t>ui_research_48</t>
+          <t>ui_research_9</t>
         </is>
       </c>
       <c r="D241" s="50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E241" s="50" t="n">
-        <v>1680</v>
+        <v>-160</v>
       </c>
       <c r="F241" s="50" t="n">
-        <v>1080</v>
+        <v>-320</v>
       </c>
       <c r="G241" s="50" t="n">
-        <v>300710033</v>
-      </c>
-      <c r="H241" s="50" t="n">
-        <v>300710032</v>
-      </c>
-      <c r="J241" s="50" t="n">
-        <v>1000</v>
+        <v>100300007</v>
+      </c>
+      <c r="H241" s="50" t="inlineStr">
+        <is>
+          <t>100310112</t>
+        </is>
+      </c>
+      <c r="J241" s="50" t="inlineStr">
+        <is>
+          <t>100,200,400,800,1500,2500,4000,6000,9000,15000</t>
+        </is>
       </c>
       <c r="K241" s="50" t="n">
-        <v>300710033</v>
+        <v>100300007</v>
+      </c>
+      <c r="L241" s="50" t="n">
+        <v>900000022</v>
       </c>
       <c r="M241" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x10</t>
+          <t>是魔王就挑战100勇士-出现概率+10%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="50" t="n">
-        <v>300710041</v>
+        <v>100300008</v>
       </c>
       <c r="B242" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C242" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_11</t>
         </is>
       </c>
       <c r="D242" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E242" s="50" t="n">
-        <v>1840</v>
-      </c>
-      <c r="F242" s="50" t="n">
-        <v>760</v>
+        <v>9</v>
+      </c>
+      <c r="E242" s="50" t="inlineStr">
+        <is>
+          <t>-800</t>
+        </is>
+      </c>
+      <c r="F242" s="50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G242" s="50" t="n">
-        <v>300710041</v>
-      </c>
-      <c r="H242" s="50" t="n">
-        <v>300700102</v>
+        <v>100300008</v>
+      </c>
+      <c r="H242" s="50" t="inlineStr">
+        <is>
+          <t>100310102</t>
+        </is>
       </c>
       <c r="I242" s="50" t="inlineStr">
         <is>
-          <t>GashaponCreatureDrawCount7004:99</t>
-        </is>
-      </c>
-      <c r="J242" s="50" t="n">
-        <v>200</v>
+          <t>AnyWorldInfiniteUnlocked</t>
+        </is>
+      </c>
+      <c r="J242" s="50" t="inlineStr">
+        <is>
+          <t>100,200,400,800,1500,2500,4000,6000,9000</t>
+        </is>
       </c>
       <c r="K242" s="50" t="n">
-        <v>300710041</v>
+        <v>100300008</v>
+      </c>
+      <c r="L242" s="50" t="n">
+        <v>900000022</v>
       </c>
       <c r="M242" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x1</t>
+          <t>无尽模式-出现概率+10%/级</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="50" t="n">
-        <v>300710042</v>
+        <v>100300009</v>
       </c>
       <c r="B243" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C243" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_9</t>
         </is>
       </c>
       <c r="D243" s="50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E243" s="50" t="n">
-        <v>1840</v>
+        <v>-480</v>
       </c>
       <c r="F243" s="50" t="n">
-        <v>920</v>
+        <v>-320</v>
       </c>
       <c r="G243" s="50" t="n">
-        <v>300710042</v>
-      </c>
-      <c r="H243" s="50" t="n">
-        <v>300710041</v>
-      </c>
-      <c r="J243" s="50" t="n">
-        <v>500</v>
+        <v>100300009</v>
+      </c>
+      <c r="H243" s="50" t="inlineStr">
+        <is>
+          <t>100300007</t>
+        </is>
+      </c>
+      <c r="I243" s="50" t="n"/>
+      <c r="J243" s="50" t="inlineStr">
+        <is>
+          <t>100,200,400,800</t>
+        </is>
       </c>
       <c r="K243" s="50" t="n">
-        <v>300710042</v>
+        <v>100300009</v>
+      </c>
+      <c r="L243" s="50" t="n">
+        <v>900000022</v>
       </c>
       <c r="M243" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x5</t>
+          <t>真勇者挑战(挑战100勇士-BOSS挑战)出现概率+10%/级(基础10%,满级50%)</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="50" t="n">
-        <v>300710043</v>
+        <v>100310150</v>
       </c>
       <c r="B244" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C244" s="50" t="inlineStr">
         <is>
-          <t>ui_research_47</t>
+          <t>ui_research_94</t>
         </is>
       </c>
       <c r="D244" s="50" t="n">
         <v>1</v>
       </c>
       <c r="E244" s="50" t="n">
-        <v>1840</v>
+        <v>160</v>
       </c>
       <c r="F244" s="50" t="n">
-        <v>1080</v>
+        <v>-140</v>
       </c>
       <c r="G244" s="50" t="n">
-        <v>300710043</v>
-      </c>
-      <c r="H244" s="50" t="n">
-        <v>300710042</v>
-      </c>
+        <v>100310150</v>
+      </c>
+      <c r="H244" s="50" t="n"/>
       <c r="J244" s="50" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="K244" s="50" t="n">
-        <v>300710043</v>
+        <v>100310150</v>
       </c>
       <c r="M244" s="50" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x10</t>
+          <t>剑与魔法-难度1-0倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="50" t="n">
-        <v>100300007</v>
+        <v>100310151</v>
       </c>
       <c r="B245" s="50" t="n">
         <v>4</v>
       </c>
       <c r="C245" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_94</t>
         </is>
       </c>
       <c r="D245" s="50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E245" s="50" t="n">
-        <v>-160</v>
+        <v>160</v>
       </c>
       <c r="F245" s="50" t="n">
-        <v>-160</v>
+        <v>180</v>
       </c>
       <c r="G245" s="50" t="n">
-        <v>100300007</v>
+        <v>100310151</v>
       </c>
       <c r="H245" s="50" t="inlineStr">
         <is>
           <t>100310112</t>
         </is>
       </c>
-      <c r="J245" s="50" t="inlineStr">
-        <is>
-          <t>100,200,400,800,1500,2500,4000,6000,9000,15000</t>
-        </is>
+      <c r="J245" s="50" t="n">
+        <v>100</v>
       </c>
       <c r="K245" s="50" t="n">
-        <v>100300007</v>
-      </c>
-      <c r="L245" s="50" t="n">
-        <v>900000022</v>
+        <v>100310151</v>
       </c>
       <c r="M245" s="50" t="inlineStr">
         <is>
-          <t>是魔王就挑战100勇士-出现概率+10%</t>
+          <t>剑与魔法-难度2-0倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="50" t="n">
-        <v>100300008</v>
+        <v>100310152</v>
       </c>
       <c r="B246" s="50" t="n">
         <v>4</v>
       </c>
       <c r="C246" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_94</t>
         </is>
       </c>
       <c r="D246" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="E246" s="50" t="inlineStr">
-        <is>
-          <t>-800</t>
-        </is>
-      </c>
-      <c r="F246" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E246" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F246" s="50" t="n">
+        <v>500</v>
       </c>
       <c r="G246" s="50" t="n">
-        <v>100300008</v>
+        <v>100310152</v>
       </c>
       <c r="H246" s="50" t="inlineStr">
         <is>
-          <t>100310102</t>
-        </is>
-      </c>
-      <c r="I246" s="50" t="inlineStr">
-        <is>
-          <t>AnyWorldInfiniteUnlocked</t>
-        </is>
-      </c>
-      <c r="J246" s="50" t="inlineStr">
-        <is>
-          <t>100,200,400,800,1500,2500,4000,6000,9000</t>
-        </is>
+          <t>100310113</t>
+        </is>
+      </c>
+      <c r="J246" s="50" t="n">
+        <v>500</v>
       </c>
       <c r="K246" s="50" t="n">
-        <v>100300008</v>
-      </c>
-      <c r="L246" s="50" t="n">
-        <v>900000022</v>
+        <v>100310152</v>
       </c>
       <c r="M246" s="50" t="inlineStr">
         <is>
-          <t>无尽模式-出现概率+10%/级</t>
+          <t>剑与魔法-难度3-0倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="50" t="n">
-        <v>100300009</v>
+        <v>100310153</v>
       </c>
       <c r="B247" s="50" t="n">
         <v>4</v>
       </c>
       <c r="C247" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_94</t>
         </is>
       </c>
       <c r="D247" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F247" s="50" t="n">
+        <v>820</v>
+      </c>
+      <c r="G247" s="50" t="n">
+        <v>100310153</v>
+      </c>
+      <c r="H247" s="50" t="inlineStr">
+        <is>
+          <t>100310114</t>
+        </is>
+      </c>
+      <c r="J247" s="50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K247" s="50" t="n">
+        <v>100310153</v>
+      </c>
+      <c r="M247" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度4-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="50" t="n">
+        <v>100310154</v>
+      </c>
+      <c r="B248" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="E247" s="50" t="n">
-        <v>-480</v>
-      </c>
-      <c r="F247" s="50" t="n">
-        <v>-160</v>
-      </c>
-      <c r="G247" s="50" t="n">
-        <v>100300009</v>
-      </c>
-      <c r="H247" s="50" t="inlineStr">
-        <is>
-          <t>100300007</t>
-        </is>
-      </c>
-      <c r="I247" s="50" t="n"/>
-      <c r="J247" s="50" t="inlineStr">
-        <is>
-          <t>100,200,400,800</t>
-        </is>
-      </c>
-      <c r="K247" s="50" t="n">
-        <v>100300009</v>
-      </c>
-      <c r="L247" s="50" t="n">
-        <v>900000022</v>
-      </c>
-      <c r="M247" s="50" t="inlineStr">
-        <is>
-          <t>真勇者挑战(挑战100勇士-BOSS挑战)出现概率+10%/级(基础10%,满级50%)</t>
+      <c r="C248" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D248" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F248" s="50" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G248" s="50" t="n">
+        <v>100310154</v>
+      </c>
+      <c r="H248" s="50" t="inlineStr">
+        <is>
+          <t>100310115</t>
+        </is>
+      </c>
+      <c r="J248" s="50" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K248" s="50" t="n">
+        <v>100310154</v>
+      </c>
+      <c r="M248" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度5-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="50" t="n">
+        <v>100310155</v>
+      </c>
+      <c r="B249" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C249" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D249" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F249" s="50" t="n">
+        <v>1460</v>
+      </c>
+      <c r="G249" s="50" t="n">
+        <v>100310155</v>
+      </c>
+      <c r="H249" s="50" t="inlineStr">
+        <is>
+          <t>100310116</t>
+        </is>
+      </c>
+      <c r="J249" s="50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K249" s="50" t="n">
+        <v>100310155</v>
+      </c>
+      <c r="M249" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度6-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="50" t="n">
+        <v>100310156</v>
+      </c>
+      <c r="B250" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C250" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D250" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F250" s="50" t="n">
+        <v>1780</v>
+      </c>
+      <c r="G250" s="50" t="n">
+        <v>100310156</v>
+      </c>
+      <c r="H250" s="50" t="inlineStr">
+        <is>
+          <t>100310117</t>
+        </is>
+      </c>
+      <c r="J250" s="50" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K250" s="50" t="n">
+        <v>100310156</v>
+      </c>
+      <c r="M250" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度7-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="50" t="n">
+        <v>100310157</v>
+      </c>
+      <c r="B251" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C251" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D251" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F251" s="50" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G251" s="50" t="n">
+        <v>100310157</v>
+      </c>
+      <c r="H251" s="50" t="inlineStr">
+        <is>
+          <t>100310118</t>
+        </is>
+      </c>
+      <c r="J251" s="50" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K251" s="50" t="n">
+        <v>100310157</v>
+      </c>
+      <c r="M251" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度8-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="50" t="n">
+        <v>100310158</v>
+      </c>
+      <c r="B252" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C252" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D252" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F252" s="50" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G252" s="50" t="n">
+        <v>100310158</v>
+      </c>
+      <c r="H252" s="50" t="inlineStr">
+        <is>
+          <t>100310119</t>
+        </is>
+      </c>
+      <c r="J252" s="50" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K252" s="50" t="n">
+        <v>100310158</v>
+      </c>
+      <c r="M252" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度9-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="50" t="n">
+        <v>100310159</v>
+      </c>
+      <c r="B253" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C253" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_94</t>
+        </is>
+      </c>
+      <c r="D253" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" s="50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F253" s="50" t="n">
+        <v>2740</v>
+      </c>
+      <c r="G253" s="50" t="n">
+        <v>100310159</v>
+      </c>
+      <c r="H253" s="50" t="inlineStr">
+        <is>
+          <t>100310120</t>
+        </is>
+      </c>
+      <c r="J253" s="50" t="n">
+        <v>64000</v>
+      </c>
+      <c r="K253" s="50" t="n">
+        <v>100310159</v>
+      </c>
+      <c r="M253" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度10-0倍速游戏</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M253"/>
+  <dimension ref="A1:M262"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -2634,7 +2634,7 @@
         <v>-480</v>
       </c>
       <c r="F30" s="50" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G30" s="50" t="n">
         <v>100310102</v>
@@ -2676,14 +2676,14 @@
         <v>-480</v>
       </c>
       <c r="F31" s="50" t="n">
-        <v>320</v>
+        <v>430</v>
       </c>
       <c r="G31" s="50" t="n">
         <v>100310103</v>
       </c>
       <c r="H31" s="50" t="inlineStr">
         <is>
-          <t>100310102,100310113</t>
+          <t>100310113</t>
         </is>
       </c>
       <c r="I31" s="50" t="n"/>
@@ -2718,14 +2718,14 @@
         <v>-480</v>
       </c>
       <c r="F32" s="50" t="n">
-        <v>640</v>
+        <v>770</v>
       </c>
       <c r="G32" s="50" t="n">
         <v>100310104</v>
       </c>
       <c r="H32" s="50" t="inlineStr">
         <is>
-          <t>100310103,100310114</t>
+          <t>100310114</t>
         </is>
       </c>
       <c r="I32" s="50" t="n"/>
@@ -2760,14 +2760,14 @@
         <v>-480</v>
       </c>
       <c r="F33" s="50" t="n">
-        <v>960</v>
+        <v>1110</v>
       </c>
       <c r="G33" s="50" t="n">
         <v>100310105</v>
       </c>
       <c r="H33" s="50" t="inlineStr">
         <is>
-          <t>100310104,100310115</t>
+          <t>100310115</t>
         </is>
       </c>
       <c r="I33" s="50" t="n"/>
@@ -2802,14 +2802,14 @@
         <v>-480</v>
       </c>
       <c r="F34" s="50" t="n">
-        <v>1280</v>
+        <v>1450</v>
       </c>
       <c r="G34" s="50" t="n">
         <v>100310106</v>
       </c>
       <c r="H34" s="50" t="inlineStr">
         <is>
-          <t>100310105,100310116</t>
+          <t>100310116</t>
         </is>
       </c>
       <c r="I34" s="50" t="n"/>
@@ -2844,14 +2844,14 @@
         <v>-480</v>
       </c>
       <c r="F35" s="50" t="n">
-        <v>1600</v>
+        <v>1790</v>
       </c>
       <c r="G35" s="50" t="n">
         <v>100310107</v>
       </c>
       <c r="H35" s="50" t="inlineStr">
         <is>
-          <t>100310106,100310117</t>
+          <t>100310117</t>
         </is>
       </c>
       <c r="I35" s="50" t="n"/>
@@ -2886,14 +2886,14 @@
         <v>-480</v>
       </c>
       <c r="F36" s="50" t="n">
-        <v>1920</v>
+        <v>2130</v>
       </c>
       <c r="G36" s="50" t="n">
         <v>100310108</v>
       </c>
       <c r="H36" s="50" t="inlineStr">
         <is>
-          <t>100310107,100310118</t>
+          <t>100310118</t>
         </is>
       </c>
       <c r="I36" s="50" t="n"/>
@@ -2928,14 +2928,14 @@
         <v>-480</v>
       </c>
       <c r="F37" s="50" t="n">
-        <v>2240</v>
+        <v>2470</v>
       </c>
       <c r="G37" s="50" t="n">
         <v>100310109</v>
       </c>
       <c r="H37" s="50" t="inlineStr">
         <is>
-          <t>100310108,100310119</t>
+          <t>100310119</t>
         </is>
       </c>
       <c r="I37" s="50" t="n"/>
@@ -2970,14 +2970,14 @@
         <v>-480</v>
       </c>
       <c r="F38" s="50" t="n">
-        <v>2560</v>
+        <v>2810</v>
       </c>
       <c r="G38" s="50" t="n">
         <v>100310110</v>
       </c>
       <c r="H38" s="50" t="inlineStr">
         <is>
-          <t>100310109,100310120</t>
+          <t>100310120</t>
         </is>
       </c>
       <c r="I38" s="50" t="n"/>
@@ -3051,7 +3051,7 @@
         <v>-160</v>
       </c>
       <c r="F40" s="50" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="G40" s="50" t="n">
         <v>100310113</v>
@@ -3094,7 +3094,7 @@
         <v>-160</v>
       </c>
       <c r="F41" s="50" t="n">
-        <v>640</v>
+        <v>680</v>
       </c>
       <c r="G41" s="50" t="n">
         <v>100310114</v>
@@ -3137,7 +3137,7 @@
         <v>-160</v>
       </c>
       <c r="F42" s="50" t="n">
-        <v>960</v>
+        <v>1020</v>
       </c>
       <c r="G42" s="50" t="n">
         <v>100310115</v>
@@ -3180,7 +3180,7 @@
         <v>-160</v>
       </c>
       <c r="F43" s="50" t="n">
-        <v>1280</v>
+        <v>1360</v>
       </c>
       <c r="G43" s="50" t="n">
         <v>100310116</v>
@@ -3223,7 +3223,7 @@
         <v>-160</v>
       </c>
       <c r="F44" s="50" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G44" s="50" t="n">
         <v>100310117</v>
@@ -3266,7 +3266,7 @@
         <v>-160</v>
       </c>
       <c r="F45" s="50" t="n">
-        <v>1920</v>
+        <v>2040</v>
       </c>
       <c r="G45" s="50" t="n">
         <v>100310118</v>
@@ -3309,7 +3309,7 @@
         <v>-160</v>
       </c>
       <c r="F46" s="50" t="n">
-        <v>2240</v>
+        <v>2380</v>
       </c>
       <c r="G46" s="50" t="n">
         <v>100310119</v>
@@ -3352,7 +3352,7 @@
         <v>-160</v>
       </c>
       <c r="F47" s="50" t="n">
-        <v>2560</v>
+        <v>2720</v>
       </c>
       <c r="G47" s="50" t="n">
         <v>100310120</v>
@@ -3395,7 +3395,7 @@
         <v>160</v>
       </c>
       <c r="F48" s="50" t="n">
-        <v>-320</v>
+        <v>-340</v>
       </c>
       <c r="G48" s="50" t="n">
         <v>100310130</v>
@@ -3483,7 +3483,7 @@
         <v>160</v>
       </c>
       <c r="F50" s="50" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="G50" s="50" t="n">
         <v>100310132</v>
@@ -3529,7 +3529,7 @@
         <v>160</v>
       </c>
       <c r="F51" s="50" t="n">
-        <v>640</v>
+        <v>680</v>
       </c>
       <c r="G51" s="50" t="n">
         <v>100310133</v>
@@ -3575,7 +3575,7 @@
         <v>160</v>
       </c>
       <c r="F52" s="50" t="n">
-        <v>960</v>
+        <v>1020</v>
       </c>
       <c r="G52" s="50" t="n">
         <v>100310134</v>
@@ -3621,7 +3621,7 @@
         <v>160</v>
       </c>
       <c r="F53" s="50" t="n">
-        <v>1280</v>
+        <v>1360</v>
       </c>
       <c r="G53" s="50" t="n">
         <v>100310135</v>
@@ -3667,7 +3667,7 @@
         <v>160</v>
       </c>
       <c r="F54" s="50" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G54" s="50" t="n">
         <v>100310136</v>
@@ -3713,7 +3713,7 @@
         <v>160</v>
       </c>
       <c r="F55" s="50" t="n">
-        <v>1920</v>
+        <v>2040</v>
       </c>
       <c r="G55" s="50" t="n">
         <v>100310137</v>
@@ -3759,7 +3759,7 @@
         <v>160</v>
       </c>
       <c r="F56" s="50" t="n">
-        <v>2240</v>
+        <v>2380</v>
       </c>
       <c r="G56" s="50" t="n">
         <v>100310138</v>
@@ -3805,7 +3805,7 @@
         <v>160</v>
       </c>
       <c r="F57" s="50" t="n">
-        <v>2560</v>
+        <v>2720</v>
       </c>
       <c r="G57" s="50" t="n">
         <v>100310139</v>
@@ -3851,7 +3851,7 @@
         <v>480</v>
       </c>
       <c r="F58" s="50" t="n">
-        <v>-320</v>
+        <v>-340</v>
       </c>
       <c r="G58" s="50" t="n">
         <v>100310140</v>
@@ -3933,7 +3933,7 @@
         <v>480</v>
       </c>
       <c r="F60" s="50" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="G60" s="50" t="n">
         <v>100310142</v>
@@ -3974,7 +3974,7 @@
         <v>480</v>
       </c>
       <c r="F61" s="50" t="n">
-        <v>640</v>
+        <v>680</v>
       </c>
       <c r="G61" s="50" t="n">
         <v>100310143</v>
@@ -4015,7 +4015,7 @@
         <v>480</v>
       </c>
       <c r="F62" s="50" t="n">
-        <v>960</v>
+        <v>1020</v>
       </c>
       <c r="G62" s="50" t="n">
         <v>100310144</v>
@@ -4056,7 +4056,7 @@
         <v>480</v>
       </c>
       <c r="F63" s="50" t="n">
-        <v>1280</v>
+        <v>1360</v>
       </c>
       <c r="G63" s="50" t="n">
         <v>100310145</v>
@@ -4097,7 +4097,7 @@
         <v>480</v>
       </c>
       <c r="F64" s="50" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G64" s="50" t="n">
         <v>100310146</v>
@@ -4138,7 +4138,7 @@
         <v>480</v>
       </c>
       <c r="F65" s="50" t="n">
-        <v>1920</v>
+        <v>2040</v>
       </c>
       <c r="G65" s="50" t="n">
         <v>100310147</v>
@@ -4179,7 +4179,7 @@
         <v>480</v>
       </c>
       <c r="F66" s="50" t="n">
-        <v>2240</v>
+        <v>2380</v>
       </c>
       <c r="G66" s="50" t="n">
         <v>100310148</v>
@@ -4220,7 +4220,7 @@
         <v>480</v>
       </c>
       <c r="F67" s="50" t="n">
-        <v>2560</v>
+        <v>2720</v>
       </c>
       <c r="G67" s="50" t="n">
         <v>100310149</v>
@@ -11763,17 +11763,17 @@
         <v>10</v>
       </c>
       <c r="E241" s="50" t="n">
-        <v>-160</v>
+        <v>-800</v>
       </c>
       <c r="F241" s="50" t="n">
-        <v>-320</v>
+        <v>-90</v>
       </c>
       <c r="G241" s="50" t="n">
         <v>100300007</v>
       </c>
       <c r="H241" s="50" t="inlineStr">
         <is>
-          <t>100310112</t>
+          <t>100310160</t>
         </is>
       </c>
       <c r="J241" s="50" t="inlineStr">
@@ -11808,15 +11808,11 @@
       <c r="D242" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="E242" s="50" t="inlineStr">
-        <is>
-          <t>-800</t>
-        </is>
-      </c>
-      <c r="F242" s="50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E242" s="50" t="n">
+        <v>-800</v>
+      </c>
+      <c r="F242" s="50" t="n">
+        <v>90</v>
       </c>
       <c r="G242" s="50" t="n">
         <v>100300008</v>
@@ -11826,11 +11822,7 @@
           <t>100310102</t>
         </is>
       </c>
-      <c r="I242" s="50" t="inlineStr">
-        <is>
-          <t>AnyWorldInfiniteUnlocked</t>
-        </is>
-      </c>
+      <c r="I242" s="50" t="n"/>
       <c r="J242" s="50" t="inlineStr">
         <is>
           <t>100,200,400,800,1500,2500,4000,6000,9000</t>
@@ -11864,10 +11856,10 @@
         <v>4</v>
       </c>
       <c r="E243" s="50" t="n">
-        <v>-480</v>
+        <v>-1120</v>
       </c>
       <c r="F243" s="50" t="n">
-        <v>-320</v>
+        <v>-90</v>
       </c>
       <c r="G243" s="50" t="n">
         <v>100300009</v>
@@ -11914,7 +11906,7 @@
         <v>160</v>
       </c>
       <c r="F244" s="50" t="n">
-        <v>-140</v>
+        <v>-160</v>
       </c>
       <c r="G244" s="50" t="n">
         <v>100310150</v>
@@ -11992,7 +11984,7 @@
         <v>160</v>
       </c>
       <c r="F246" s="50" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="G246" s="50" t="n">
         <v>100310152</v>
@@ -12033,7 +12025,7 @@
         <v>160</v>
       </c>
       <c r="F247" s="50" t="n">
-        <v>820</v>
+        <v>860</v>
       </c>
       <c r="G247" s="50" t="n">
         <v>100310153</v>
@@ -12074,7 +12066,7 @@
         <v>160</v>
       </c>
       <c r="F248" s="50" t="n">
-        <v>1140</v>
+        <v>1200</v>
       </c>
       <c r="G248" s="50" t="n">
         <v>100310154</v>
@@ -12115,7 +12107,7 @@
         <v>160</v>
       </c>
       <c r="F249" s="50" t="n">
-        <v>1460</v>
+        <v>1540</v>
       </c>
       <c r="G249" s="50" t="n">
         <v>100310155</v>
@@ -12156,7 +12148,7 @@
         <v>160</v>
       </c>
       <c r="F250" s="50" t="n">
-        <v>1780</v>
+        <v>1880</v>
       </c>
       <c r="G250" s="50" t="n">
         <v>100310156</v>
@@ -12197,7 +12189,7 @@
         <v>160</v>
       </c>
       <c r="F251" s="50" t="n">
-        <v>2100</v>
+        <v>2220</v>
       </c>
       <c r="G251" s="50" t="n">
         <v>100310157</v>
@@ -12238,7 +12230,7 @@
         <v>160</v>
       </c>
       <c r="F252" s="50" t="n">
-        <v>2420</v>
+        <v>2560</v>
       </c>
       <c r="G252" s="50" t="n">
         <v>100310158</v>
@@ -12279,7 +12271,7 @@
         <v>160</v>
       </c>
       <c r="F253" s="50" t="n">
-        <v>2740</v>
+        <v>2900</v>
       </c>
       <c r="G253" s="50" t="n">
         <v>100310159</v>
@@ -12298,6 +12290,375 @@
       <c r="M253" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-难度10-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="50" t="n">
+        <v>100310160</v>
+      </c>
+      <c r="B254" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C254" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D254" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" s="50" t="n">
+        <v>-480</v>
+      </c>
+      <c r="F254" s="50" t="n">
+        <v>-90</v>
+      </c>
+      <c r="G254" s="50" t="n">
+        <v>100310160</v>
+      </c>
+      <c r="H254" s="50" t="inlineStr">
+        <is>
+          <t>100310112</t>
+        </is>
+      </c>
+      <c r="J254" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="K254" s="50" t="n">
+        <v>100310160</v>
+      </c>
+      <c r="M254" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度2</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="50" t="n">
+        <v>100310161</v>
+      </c>
+      <c r="B255" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C255" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D255" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E255" s="50" t="n">
+        <v>-480</v>
+      </c>
+      <c r="F255" s="50" t="n">
+        <v>250</v>
+      </c>
+      <c r="G255" s="50" t="n">
+        <v>100310161</v>
+      </c>
+      <c r="H255" s="50" t="inlineStr">
+        <is>
+          <t>100310113</t>
+        </is>
+      </c>
+      <c r="J255" s="50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K255" s="50" t="n">
+        <v>100310161</v>
+      </c>
+      <c r="M255" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度3</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="50" t="n">
+        <v>100310162</v>
+      </c>
+      <c r="B256" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C256" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D256" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" s="50" t="n">
+        <v>-480</v>
+      </c>
+      <c r="F256" s="50" t="n">
+        <v>590</v>
+      </c>
+      <c r="G256" s="50" t="n">
+        <v>100310162</v>
+      </c>
+      <c r="H256" s="50" t="inlineStr">
+        <is>
+          <t>100310114</t>
+        </is>
+      </c>
+      <c r="J256" s="50" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K256" s="50" t="n">
+        <v>100310162</v>
+      </c>
+      <c r="M256" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度4</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="50" t="n">
+        <v>100310163</v>
+      </c>
+      <c r="B257" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C257" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D257" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" s="50" t="n">
+        <v>-480</v>
+      </c>
+      <c r="F257" s="50" t="n">
+        <v>930</v>
+      </c>
+      <c r="G257" s="50" t="n">
+        <v>100310163</v>
+      </c>
+      <c r="H257" s="50" t="inlineStr">
+        <is>
+          <t>100310115</t>
+        </is>
+      </c>
+      <c r="J257" s="50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K257" s="50" t="n">
+        <v>100310163</v>
+      </c>
+      <c r="M257" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度5</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="50" t="n">
+        <v>100310164</v>
+      </c>
+      <c r="B258" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C258" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D258" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" s="50" t="n">
+        <v>-480</v>
+      </c>
+      <c r="F258" s="50" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G258" s="50" t="n">
+        <v>100310164</v>
+      </c>
+      <c r="H258" s="50" t="inlineStr">
+        <is>
+          <t>100310116</t>
+        </is>
+      </c>
+      <c r="J258" s="50" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K258" s="50" t="n">
+        <v>100310164</v>
+      </c>
+      <c r="M258" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度6</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="50" t="n">
+        <v>100310165</v>
+      </c>
+      <c r="B259" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C259" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D259" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="50" t="n">
+        <v>-480</v>
+      </c>
+      <c r="F259" s="50" t="n">
+        <v>1610</v>
+      </c>
+      <c r="G259" s="50" t="n">
+        <v>100310165</v>
+      </c>
+      <c r="H259" s="50" t="inlineStr">
+        <is>
+          <t>100310117</t>
+        </is>
+      </c>
+      <c r="J259" s="50" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K259" s="50" t="n">
+        <v>100310165</v>
+      </c>
+      <c r="M259" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度7</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="50" t="n">
+        <v>100310166</v>
+      </c>
+      <c r="B260" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C260" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D260" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="50" t="n">
+        <v>-480</v>
+      </c>
+      <c r="F260" s="50" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G260" s="50" t="n">
+        <v>100310166</v>
+      </c>
+      <c r="H260" s="50" t="inlineStr">
+        <is>
+          <t>100310118</t>
+        </is>
+      </c>
+      <c r="J260" s="50" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K260" s="50" t="n">
+        <v>100310166</v>
+      </c>
+      <c r="M260" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度8</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="50" t="n">
+        <v>100310167</v>
+      </c>
+      <c r="B261" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C261" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D261" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="50" t="n">
+        <v>-480</v>
+      </c>
+      <c r="F261" s="50" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G261" s="50" t="n">
+        <v>100310167</v>
+      </c>
+      <c r="H261" s="50" t="inlineStr">
+        <is>
+          <t>100310119</t>
+        </is>
+      </c>
+      <c r="J261" s="50" t="n">
+        <v>64000</v>
+      </c>
+      <c r="K261" s="50" t="n">
+        <v>100310167</v>
+      </c>
+      <c r="M261" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度9</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="50" t="n">
+        <v>100310168</v>
+      </c>
+      <c r="B262" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C262" s="50" t="inlineStr">
+        <is>
+          <t>ui_research_9</t>
+        </is>
+      </c>
+      <c r="D262" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" s="50" t="n">
+        <v>-480</v>
+      </c>
+      <c r="F262" s="50" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G262" s="50" t="n">
+        <v>100310168</v>
+      </c>
+      <c r="H262" s="50" t="inlineStr">
+        <is>
+          <t>100310120</t>
+        </is>
+      </c>
+      <c r="J262" s="50" t="n">
+        <v>128000</v>
+      </c>
+      <c r="K262" s="50" t="n">
+        <v>100310168</v>
+      </c>
+      <c r="M262" s="50" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度10</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M262"/>
+  <dimension ref="A1:M263"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="37.75" customWidth="1" style="51" min="1" max="1"/>
@@ -4784,7 +4784,7 @@
       <c r="H79" s="50" t="n"/>
       <c r="J79" s="50" t="inlineStr">
         <is>
-          <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000</t>
+          <t>1,50,100,150,200,250,300,350,400,450,500,550,600,650,700,750,800,850,900,950,1000,1500,2000,2500,3000,3500,4000,4500,5000,5500</t>
         </is>
       </c>
       <c r="K79" s="50" t="n">
@@ -12659,6 +12659,49 @@
       <c r="M262" s="50" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度10</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>100300011</v>
+      </c>
+      <c r="B263" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>ui_research_59</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G263" t="n">
+        <v>100300011</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>100300005</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>100300011</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>传送门详情-来袭魔物预览</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_research_info[研究信息].xlsx
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C30" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D30" s="50" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D31" s="50" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D32" s="50" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D33" s="50" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="C34" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D34" s="50" t="n">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C35" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D35" s="50" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="C36" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D36" s="50" t="n">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C37" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D37" s="50" t="n">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C38" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D38" s="50" t="n">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="C58" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D58" s="50" t="n">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="C59" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D59" s="50" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="C60" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D60" s="50" t="n">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="C61" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D61" s="50" t="n">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="C62" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D62" s="50" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="C63" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D63" s="50" t="n">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="C64" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D64" s="50" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C65" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D65" s="50" t="n">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="C66" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D66" s="50" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="C67" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_202</t>
         </is>
       </c>
       <c r="D67" s="50" t="n">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C241" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D241" s="50" t="n">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="C242" s="50" t="inlineStr">
         <is>
-          <t>ui_research_11</t>
+          <t>ui_research_155</t>
         </is>
       </c>
       <c r="D242" s="50" t="n">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="C243" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D243" s="50" t="n">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="C244" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D244" s="50" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C245" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D245" s="50" t="n">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="C246" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D246" s="50" t="n">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="C247" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D247" s="50" t="n">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="C248" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D248" s="50" t="n">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="C249" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D249" s="50" t="n">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="C250" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D250" s="50" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C251" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D251" s="50" t="n">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="C252" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D252" s="50" t="n">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="C253" s="50" t="inlineStr">
         <is>
-          <t>ui_research_94</t>
+          <t>ui_research_201</t>
         </is>
       </c>
       <c r="D253" s="50" t="n">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="C254" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D254" s="50" t="n">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="C255" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D255" s="50" t="n">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="C256" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D256" s="50" t="n">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="C257" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D257" s="50" t="n">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="C258" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D258" s="50" t="n">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="C259" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D259" s="50" t="n">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C260" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D260" s="50" t="n">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="C261" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D261" s="50" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C262" s="50" t="inlineStr">
         <is>
-          <t>ui_research_9</t>
+          <t>ui_research_181</t>
         </is>
       </c>
       <c r="D262" s="50" t="n">
@@ -12663,43 +12663,43 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="n">
+      <c r="A263" s="50" t="n">
         <v>100300011</v>
       </c>
-      <c r="B263" t="n">
-        <v>1</v>
-      </c>
-      <c r="C263" t="inlineStr">
+      <c r="B263" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" s="50" t="inlineStr">
         <is>
           <t>ui_research_59</t>
         </is>
       </c>
-      <c r="D263" t="n">
-        <v>1</v>
-      </c>
-      <c r="E263" t="n">
+      <c r="D263" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="F263" t="n">
+      <c r="F263" s="50" t="n">
         <v>-1000</v>
       </c>
-      <c r="G263" t="n">
+      <c r="G263" s="50" t="n">
         <v>100300011</v>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="H263" s="50" t="inlineStr">
         <is>
           <t>100300005</t>
         </is>
       </c>
-      <c r="J263" t="inlineStr">
+      <c r="J263" s="50" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="K263" t="n">
+      <c r="K263" s="50" t="n">
         <v>100300011</v>
       </c>
-      <c r="M263" t="inlineStr">
+      <c r="M263" s="50" t="inlineStr">
         <is>
           <t>传送门详情-来袭魔物预览</t>
         </is>
